--- a/publication_tables/supplementary/S5_error_grid_summary.xlsx
+++ b/publication_tables/supplementary/S5_error_grid_summary.xlsx
@@ -457,16 +457,16 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.510663538374</v>
+        <v>-0.5108005548617729</v>
       </c>
       <c r="D2" t="n">
-        <v>7.47513527992e-16</v>
+        <v>5.612455273900493e-16</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.510663538374</v>
+        <v>-0.5108005548617731</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.510663538374</v>
+        <v>-0.5108005548617713</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>0.02</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.493904598598</v>
+        <v>-0.4940433590950658</v>
       </c>
       <c r="D3" t="n">
-        <v>2.76938278737e-16</v>
+        <v>7.484290378614565e-16</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.493904598598</v>
+        <v>-0.4940433590950661</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.493904598598</v>
+        <v>-0.4940433590950644</v>
       </c>
     </row>
     <row r="4">
@@ -497,16 +497,16 @@
         <v>0.04</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.477143426441</v>
+        <v>-0.4772829574416459</v>
       </c>
       <c r="D4" t="n">
-        <v>8.58779816583e-16</v>
+        <v>5.636804434967433e-16</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.477143426441</v>
+        <v>-0.4772829574416475</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.477143426441</v>
+        <v>-0.4772829574416457</v>
       </c>
     </row>
     <row r="5">
@@ -517,16 +517,16 @@
         <v>0.06</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.460372028132</v>
+        <v>-0.4605138451668115</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>8.438993393712258e-16</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.460372028132</v>
+        <v>-0.4605138451668136</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.460372028132</v>
+        <v>-0.4605138451668109</v>
       </c>
     </row>
     <row r="6">
@@ -537,16 +537,16 @@
         <v>0.08</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.443596533208</v>
+        <v>-0.4437383094140925</v>
       </c>
       <c r="D6" t="n">
-        <v>4.58877260917e-16</v>
+        <v>9.153263484963472e-16</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.443596533208</v>
+        <v>-0.4437383094140932</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.443596533208</v>
+        <v>-0.4437383094140914</v>
       </c>
     </row>
     <row r="7">
@@ -557,16 +557,16 @@
         <v>0.1</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.426809743195</v>
+        <v>-0.426934733397521</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>7.378320931034774e-16</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.426809743195</v>
+        <v>-0.4269347333975224</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.426809743195</v>
+        <v>-0.4269347333975206</v>
       </c>
     </row>
     <row r="8">
@@ -577,16 +577,16 @@
         <v>0.12</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.409995422878</v>
+        <v>-0.410096481176004</v>
       </c>
       <c r="D8" t="n">
-        <v>2.78171862921e-16</v>
+        <v>3.787616422438323e-16</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.409995422878</v>
+        <v>-0.4100964811760042</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.409995422878</v>
+        <v>-0.4100964811760033</v>
       </c>
     </row>
     <row r="9">
@@ -597,16 +597,16 @@
         <v>0.14</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.393153466695</v>
+        <v>-0.3932281988526271</v>
       </c>
       <c r="D9" t="n">
-        <v>5.6489396577e-16</v>
+        <v>4.299875284949258e-16</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.393153466695</v>
+        <v>-0.3932281988526274</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.393153466695</v>
+        <v>-0.3932281988526265</v>
       </c>
     </row>
     <row r="10">
@@ -617,16 +617,16 @@
         <v>0.16</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.376277612203</v>
+        <v>-0.3763537561232219</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>5.636804434967433e-16</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.376277612203</v>
+        <v>-0.3763537561232235</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.376277612203</v>
+        <v>-0.3763537561232217</v>
       </c>
     </row>
     <row r="11">
@@ -637,16 +637,16 @@
         <v>0.18</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.359391922671</v>
+        <v>-0.3594560529698058</v>
       </c>
       <c r="D11" t="n">
-        <v>5.63680443497e-16</v>
+        <v>8.551840723193144e-16</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.359391922671</v>
+        <v>-0.359456052969807</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.359391922671</v>
+        <v>-0.3594560529698052</v>
       </c>
     </row>
     <row r="12">
@@ -657,16 +657,16 @@
         <v>0.2</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.3424805192</v>
+        <v>-0.342552014677833</v>
       </c>
       <c r="D12" t="n">
-        <v>4.68476698219e-16</v>
+        <v>8.623605679718459e-16</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3424805192</v>
+        <v>-0.3425520146778336</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3424805192</v>
+        <v>-0.3425520146778318</v>
       </c>
     </row>
     <row r="13">
@@ -677,16 +677,16 @@
         <v>0.22</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.325557413461</v>
+        <v>-0.3256322417489974</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.325557413461</v>
+        <v>-0.3256322417489974</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.325557413461</v>
+        <v>-0.3256322417489974</v>
       </c>
     </row>
     <row r="14">
@@ -697,16 +697,16 @@
         <v>0.24</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.308603295232</v>
+        <v>-0.3086671033901043</v>
       </c>
       <c r="D14" t="n">
-        <v>3.71920110306e-16</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.308603295232</v>
+        <v>-0.3086671033901043</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.308603295232</v>
+        <v>-0.3086671033901043</v>
       </c>
     </row>
     <row r="15">
@@ -717,16 +717,16 @@
         <v>0.26</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.291627183023</v>
+        <v>-0.2916835109234391</v>
       </c>
       <c r="D15" t="n">
-        <v>3.73756763996e-16</v>
+        <v>1.041481514324134e-15</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.291627183023</v>
+        <v>-0.2916835109234404</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.291627183023</v>
+        <v>-0.2916835109234377</v>
       </c>
     </row>
     <row r="16">
@@ -737,16 +737,16 @@
         <v>0.28</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.274637424837</v>
+        <v>-0.274681803979738</v>
       </c>
       <c r="D16" t="n">
-        <v>8.48955701808e-16</v>
+        <v>2.806227636950246e-16</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.274637424837</v>
+        <v>-0.2746818039797381</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.274637424837</v>
+        <v>-0.2746818039797372</v>
       </c>
     </row>
     <row r="17">
@@ -757,16 +757,16 @@
         <v>0.3</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.257617371643</v>
+        <v>-0.2576589894861422</v>
       </c>
       <c r="D17" t="n">
-        <v>3.73756763996e-16</v>
+        <v>2.806227636950246e-16</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.257617371643</v>
+        <v>-0.257658989486143</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.257617371643</v>
+        <v>-0.2576589894861421</v>
       </c>
     </row>
     <row r="18">
@@ -777,16 +777,16 @@
         <v>0.32</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.240574030158</v>
+        <v>-0.2406125767079437</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>4.666459889952806e-16</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.240574030158</v>
+        <v>-0.2406125767079441</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.240574030158</v>
+        <v>-0.2406125767079432</v>
       </c>
     </row>
     <row r="19">
@@ -797,16 +797,16 @@
         <v>0.34</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.223512005029</v>
+        <v>-0.223555113768108</v>
       </c>
       <c r="D19" t="n">
-        <v>7.59441782284e-16</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.223512005029</v>
+        <v>-0.223555113768108</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.223512005029</v>
+        <v>-0.223555113768108</v>
       </c>
     </row>
     <row r="20">
@@ -817,16 +817,16 @@
         <v>0.36</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.206435713369</v>
+        <v>-0.2064655517531913</v>
       </c>
       <c r="D20" t="n">
-        <v>9.185003606579999e-16</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.206435713369</v>
+        <v>-0.2064655517531913</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.206435713369</v>
+        <v>-0.2064655517531913</v>
       </c>
     </row>
     <row r="21">
@@ -837,16 +837,16 @@
         <v>0.38</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.189337155835</v>
+        <v>-0.1893510542631479</v>
       </c>
       <c r="D21" t="n">
-        <v>9.364050963430001e-16</v>
+        <v>2.797061926116946e-16</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.189337155835</v>
+        <v>-0.189351054263148</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.189337155835</v>
+        <v>-0.1893510542631471</v>
       </c>
     </row>
     <row r="22">
@@ -857,16 +857,16 @@
         <v>0.4</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.172219209019</v>
+        <v>-0.1722358355147751</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>9.161208824826277e-16</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.172219209019</v>
+        <v>-0.1722358355147762</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.172219209019</v>
+        <v>-0.1722358355147744</v>
       </c>
     </row>
     <row r="23">
@@ -877,16 +877,16 @@
         <v>0.42</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.155095155379</v>
+        <v>-0.1551145016035328</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>4.572889606334765e-16</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.155095155379</v>
+        <v>-0.1551145016035331</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.155095155379</v>
+        <v>-0.1551145016035322</v>
       </c>
     </row>
     <row r="24">
@@ -897,16 +897,16 @@
         <v>0.44</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.137961500018</v>
+        <v>-0.1379667033529335</v>
       </c>
       <c r="D24" t="n">
-        <v>2.82446982885e-16</v>
+        <v>9.168680502141103e-16</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.137961500018</v>
+        <v>-0.1379667033529346</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.137961500018</v>
+        <v>-0.1379667033529328</v>
       </c>
     </row>
     <row r="25">
@@ -917,16 +917,16 @@
         <v>0.46</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.120786003981</v>
+        <v>-0.1207908330321313</v>
       </c>
       <c r="D25" t="n">
-        <v>8.57944651783e-16</v>
+        <v>8.577575631838711e-16</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.120786003981</v>
+        <v>-0.1207908330321326</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.120786003981</v>
+        <v>-0.1207908330321308</v>
       </c>
     </row>
     <row r="26">
@@ -937,16 +937,16 @@
         <v>0.48</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.103597888308</v>
+        <v>-0.1036032524646993</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>3.746717146038985e-16</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.103597888308</v>
+        <v>-0.1036032524646995</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.103597888308</v>
+        <v>-0.1036032524646986</v>
       </c>
     </row>
     <row r="27">
@@ -957,16 +957,16 @@
         <v>0.5</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0864032559918</v>
+        <v>-0.08641146818314818</v>
       </c>
       <c r="D27" t="n">
-        <v>7.48972092361e-16</v>
+        <v>2.798973924375715e-16</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.0864032559918</v>
+        <v>-0.08641146818314827</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.0864032559918</v>
+        <v>-0.08641146818314738</v>
       </c>
     </row>
     <row r="28">
@@ -977,16 +977,16 @@
         <v>0.52</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.06918036047999999</v>
+        <v>-0.06918285254458204</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>2.810799284244346e-16</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.06918036047999999</v>
+        <v>-0.06918285254458212</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.06918036047999999</v>
+        <v>-0.06918285254458123</v>
       </c>
     </row>
     <row r="29">
@@ -997,16 +997,16 @@
         <v>0.54</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0519409239415</v>
+        <v>-0.05193647625848739</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>2.820110052682177e-16</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.0519409239415</v>
+        <v>-0.05193647625848818</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0519409239415</v>
+        <v>-0.0519364762584873</v>
       </c>
     </row>
     <row r="30">
@@ -1017,16 +1017,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0346725433061</v>
+        <v>-0.03466775734336469</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.0346725433061</v>
+        <v>-0.03466775734336469</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.0346725433061</v>
+        <v>-0.03466775734336469</v>
       </c>
     </row>
     <row r="31">
@@ -1037,16 +1037,16 @@
         <v>0.58</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0173868114492</v>
+        <v>-0.01738368084694208</v>
       </c>
       <c r="D31" t="n">
-        <v>5.61883809999e-16</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.0173868114492</v>
+        <v>-0.01738368084694208</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.0173868114492</v>
+        <v>-0.01738368084694208</v>
       </c>
     </row>
     <row r="32">
@@ -1057,16 +1057,16 @@
         <v>0.6</v>
       </c>
       <c r="C32" t="n">
-        <v>-8.41301629268e-05</v>
+        <v>-8.411698949011282e-05</v>
       </c>
       <c r="D32" t="n">
-        <v>6.553556221639999e-16</v>
+        <v>5.617339294324485e-16</v>
       </c>
       <c r="E32" t="n">
-        <v>-8.41301629277e-05</v>
+        <v>-8.411698949029045e-05</v>
       </c>
       <c r="F32" t="n">
-        <v>-8.41301629251e-05</v>
+        <v>-8.411698948851409e-05</v>
       </c>
     </row>
     <row r="33">
@@ -1077,16 +1077,16 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.507113134519</v>
+        <v>-0.5072615289285609</v>
       </c>
       <c r="D33" t="n">
-        <v>0.00351234859411</v>
+        <v>0.003513323390713794</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.512172007261</v>
+        <v>-0.5123510385336694</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.499531544957</v>
+        <v>-0.4997158567151949</v>
       </c>
     </row>
     <row r="34">
@@ -1097,16 +1097,16 @@
         <v>0.02</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.490522537637</v>
+        <v>-0.4906656362700355</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00344653326608</v>
+        <v>0.003447842533111279</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.495494613117</v>
+        <v>-0.4956704378752379</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.483101962595</v>
+        <v>-0.4832812910970441</v>
       </c>
     </row>
     <row r="35">
@@ -1117,16 +1117,16 @@
         <v>0.04</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.473898508659</v>
+        <v>-0.4740401890090357</v>
       </c>
       <c r="D35" t="n">
-        <v>0.00338169053493</v>
+        <v>0.003384273738229338</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.47878424999</v>
+        <v>-0.4789656300417233</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.466636770627</v>
+        <v>-0.4668144245532764</v>
       </c>
     </row>
     <row r="36">
@@ -1137,16 +1137,16 @@
         <v>0.06</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.457238974898</v>
+        <v>-0.4573927630705882</v>
       </c>
       <c r="D36" t="n">
-        <v>0.00331827444233</v>
+        <v>0.003321880112324931</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.462045932171</v>
+        <v>-0.4622441906782049</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.450134050183</v>
+        <v>-0.4503248088245968</v>
       </c>
     </row>
     <row r="37">
@@ -1157,16 +1157,16 @@
         <v>0.08</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.440551420192</v>
+        <v>-0.4406997786237558</v>
       </c>
       <c r="D37" t="n">
-        <v>0.00325336458767</v>
+        <v>0.003257659221198943</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.445279649294</v>
+        <v>-0.4454696542128564</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.433610598173</v>
+        <v>-0.4337894005808893</v>
       </c>
     </row>
     <row r="38">
@@ -1177,16 +1177,16 @@
         <v>0.1</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.423857668292</v>
+        <v>-0.4239719291766073</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00318788935933</v>
+        <v>0.003191454247795029</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.428505167805</v>
+        <v>-0.4286538400386375</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.417082175182</v>
+        <v>-0.4172196239178598</v>
       </c>
     </row>
     <row r="39">
@@ -1197,16 +1197,16 @@
         <v>0.12</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.407126458748</v>
+        <v>-0.4072430357073224</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00312160454849</v>
+        <v>0.003125134257686671</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.411685911963</v>
+        <v>-0.411836623785713</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.400508950353</v>
+        <v>-0.4006487701989698</v>
       </c>
     </row>
     <row r="40">
@@ -1217,16 +1217,16 @@
         <v>0.14</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.390391514284</v>
+        <v>-0.3905088962436412</v>
       </c>
       <c r="D40" t="n">
-        <v>0.00305491309908</v>
+        <v>0.003058234577551114</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.394862525806</v>
+        <v>-0.3950138586876086</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.383933432135</v>
+        <v>-0.3840754781517335</v>
       </c>
     </row>
     <row r="41">
@@ -1237,16 +1237,16 @@
         <v>0.16</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.373642882885</v>
+        <v>-0.3737655002243197</v>
       </c>
       <c r="D41" t="n">
-        <v>0.00298799754208</v>
+        <v>0.002991503943840225</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.378025299352</v>
+        <v>-0.3781818483775261</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.367345679978</v>
+        <v>-0.3674929094405552</v>
       </c>
     </row>
     <row r="42">
@@ -1257,16 +1257,16 @@
         <v>0.18</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.356889909779</v>
+        <v>-0.3570083464945152</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00292095981906</v>
+        <v>0.002925251280778994</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.361183726248</v>
+        <v>-0.361333437123049</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.350753553316</v>
+        <v>-0.3508939083422691</v>
       </c>
     </row>
     <row r="43">
@@ -1277,16 +1277,16 @@
         <v>0.2</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.340117567035</v>
+        <v>-0.3402211967804993</v>
       </c>
       <c r="D43" t="n">
-        <v>0.00285466221882</v>
+        <v>0.00285932276903414</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.344320231429</v>
+        <v>-0.3444518555356177</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.334139477091</v>
+        <v>-0.3342617054775667</v>
       </c>
     </row>
     <row r="44">
@@ -1297,16 +1297,16 @@
         <v>0.22</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.323318396078</v>
+        <v>-0.3233845991065631</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00278932703077</v>
+        <v>0.002792508625205635</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.327426867777</v>
+        <v>-0.3275182415555147</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.31749443185</v>
+        <v>-0.3175765414148648</v>
       </c>
     </row>
     <row r="45">
@@ -1317,16 +1317,16 @@
         <v>0.24</v>
       </c>
       <c r="C45" t="n">
-        <v>-0.306473215861</v>
+        <v>-0.3065366763310576</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00272281816817</v>
+        <v>0.002725928759511533</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.31048560116</v>
+        <v>-0.3105739850437139</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.300800207071</v>
+        <v>-0.3008792802994646</v>
       </c>
     </row>
     <row r="46">
@@ -1337,16 +1337,16 @@
         <v>0.26</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.289613756512</v>
+        <v>-0.2896683175419629</v>
       </c>
       <c r="D46" t="n">
-        <v>0.00265625463362</v>
+        <v>0.002659408551109627</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.293529770034</v>
+        <v>-0.293608726994008</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.284091390214</v>
+        <v>-0.2841609865280441</v>
       </c>
     </row>
     <row r="47">
@@ -1357,16 +1357,16 @@
         <v>0.28</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.272725219022</v>
+        <v>-0.2727862952542964</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0025896796876</v>
+        <v>0.002592956208456144</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.276543770052</v>
+        <v>-0.2766294148290624</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.267352376939</v>
+        <v>-0.2674286075324188</v>
       </c>
     </row>
     <row r="48">
@@ -1377,16 +1377,16 @@
         <v>0.3</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.255820310713</v>
+        <v>-0.2558867105514698</v>
       </c>
       <c r="D48" t="n">
-        <v>0.00252437718218</v>
+        <v>0.002527717211944306</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.259543473607</v>
+        <v>-0.2596354932058036</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.250594186611</v>
+        <v>-0.2506758214936795</v>
       </c>
     </row>
     <row r="49">
@@ -1397,16 +1397,16 @@
         <v>0.32</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.238886504716</v>
+        <v>-0.2389429965058786</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00246000795165</v>
+        <v>0.002463081866137632</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.242509174055</v>
+        <v>-0.2425894532557935</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.233800995436</v>
+        <v>-0.2338708313906164</v>
       </c>
     </row>
     <row r="50">
@@ -1417,16 +1417,16 @@
         <v>0.34</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.221934165588</v>
+        <v>-0.2219772838039265</v>
       </c>
       <c r="D50" t="n">
-        <v>0.00239544512025</v>
+        <v>0.002399126355202407</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.225454330219</v>
+        <v>-0.2255248046593001</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.216987233083</v>
+        <v>-0.2170411706359161</v>
       </c>
     </row>
     <row r="51">
@@ -1437,16 +1437,16 @@
         <v>0.36</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.204953252531</v>
+        <v>-0.2049936778446025</v>
       </c>
       <c r="D51" t="n">
-        <v>0.00233186174875</v>
+        <v>0.002335446921830144</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.20837410108</v>
+        <v>-0.2084417693507721</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.200142131409</v>
+        <v>-0.2001921446809529</v>
       </c>
     </row>
     <row r="52">
@@ -1457,16 +1457,16 @@
         <v>0.38</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.187946360123</v>
+        <v>-0.1879817324572543</v>
       </c>
       <c r="D52" t="n">
-        <v>0.00226871569056</v>
+        <v>0.002271592281942413</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.191266699511</v>
+        <v>-0.1913280272610729</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.183267524255</v>
+        <v>-0.1833122028929131</v>
       </c>
     </row>
     <row r="53">
@@ -1477,16 +1477,16 @@
         <v>0.4</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.170911746109</v>
+        <v>-0.1709498618708589</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00220428304408</v>
+        <v>0.002206680101042226</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.174130136362</v>
+        <v>-0.1741938346653331</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.166367416914</v>
+        <v>-0.16641577254721</v>
       </c>
     </row>
     <row r="54">
@@ -1497,16 +1497,16 @@
         <v>0.42</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.15386218854</v>
+        <v>-0.153891796980696</v>
       </c>
       <c r="D54" t="n">
-        <v>0.00213785230239</v>
+        <v>0.0021380663019069</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.156977280225</v>
+        <v>-0.1570307404281701</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.149457344977</v>
+        <v>-0.1495056637596663</v>
       </c>
     </row>
     <row r="55">
@@ -1517,16 +1517,16 @@
         <v>0.44</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.136785513235</v>
+        <v>-0.1368020283551635</v>
       </c>
       <c r="D55" t="n">
-        <v>0.00206851916301</v>
+        <v>0.002068461458122348</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.139795212128</v>
+        <v>-0.1398323405620658</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.132531744111</v>
+        <v>-0.132564391723089</v>
       </c>
     </row>
     <row r="56">
@@ -1537,16 +1537,16 @@
         <v>0.46</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.119689675212</v>
+        <v>-0.1197079383209672</v>
       </c>
       <c r="D56" t="n">
-        <v>0.00199909731286</v>
+        <v>0.001998894275604395</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.122591880598</v>
+        <v>-0.1226302215508772</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.11558461876</v>
+        <v>-0.1156179000627091</v>
       </c>
     </row>
     <row r="57">
@@ -1557,16 +1557,16 @@
         <v>0.48</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.102585748977</v>
+        <v>-0.1026054983858789</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00192946976895</v>
+        <v>0.001930087138573392</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.105379951221</v>
+        <v>-0.1054192622582413</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.0986282075783</v>
+        <v>-0.09866236292243347</v>
       </c>
     </row>
     <row r="58">
@@ -1577,16 +1577,16 @@
         <v>0.5</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.085465059812</v>
+        <v>-0.08547027403115592</v>
       </c>
       <c r="D58" t="n">
-        <v>0.00186124096961</v>
+        <v>0.001863066076088945</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.088150331108</v>
+        <v>-0.08817345686036493</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.0816540772139</v>
+        <v>-0.08167194756944962</v>
       </c>
     </row>
     <row r="59">
@@ -1597,16 +1597,16 @@
         <v>0.52</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.0682998317123</v>
+        <v>-0.06830775294636497</v>
       </c>
       <c r="D59" t="n">
-        <v>0.00179475364724</v>
+        <v>0.001796337995339835</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.0708732489555</v>
+        <v>-0.07089836788529968</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.0646324563707</v>
+        <v>-0.0646531913108177</v>
       </c>
     </row>
     <row r="60">
@@ -1617,16 +1617,16 @@
         <v>0.54</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0511245189664</v>
+        <v>-0.05113719498457749</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0017281451306</v>
+        <v>0.001729106936331276</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.0535853796963</v>
+        <v>-0.05361594687971927</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.0476009719892</v>
+        <v>-0.04762941817169342</v>
       </c>
     </row>
     <row r="61">
@@ -1637,16 +1637,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.0339332332357</v>
+        <v>-0.03394314189950771</v>
       </c>
       <c r="D61" t="n">
-        <v>0.00165773000383</v>
+        <v>0.001658414166095461</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.0362794535129</v>
+        <v>-0.03630767030186366</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.0305682002136</v>
+        <v>-0.03059259354772426</v>
       </c>
     </row>
     <row r="62">
@@ -1657,16 +1657,16 @@
         <v>0.58</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.0167164964154</v>
+        <v>-0.01672180417184794</v>
       </c>
       <c r="D62" t="n">
-        <v>0.00158346541477</v>
+        <v>0.00158505681306497</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.0189467283068</v>
+        <v>-0.01897161444640005</v>
       </c>
       <c r="F62" t="n">
-        <v>-0.0135238752885</v>
+        <v>-0.01353872845148008</v>
       </c>
     </row>
     <row r="63">
@@ -1677,16 +1677,16 @@
         <v>0.6</v>
       </c>
       <c r="C63" t="n">
-        <v>0.000528336557402</v>
+        <v>0.0005273481490914555</v>
       </c>
       <c r="D63" t="n">
-        <v>0.00150813249993</v>
+        <v>0.001509123647173564</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.00158618283525</v>
+        <v>-0.001605481434973299</v>
       </c>
       <c r="F63" t="n">
-        <v>0.00355157596847</v>
+        <v>0.003543362306651865</v>
       </c>
     </row>
     <row r="64">
@@ -1697,16 +1697,16 @@
         <v>0.62</v>
       </c>
       <c r="C64" t="n">
-        <v>0.017796804359</v>
+        <v>0.01779363201161894</v>
       </c>
       <c r="D64" t="n">
-        <v>0.00143266456705</v>
+        <v>0.001433657333582195</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0157967876987</v>
+        <v>0.01577517779793514</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0206533915986</v>
+        <v>0.02064420423523661</v>
       </c>
     </row>
     <row r="65">
@@ -1717,16 +1717,16 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.502520216037</v>
+        <v>-0.5027108993919266</v>
       </c>
       <c r="D65" t="n">
-        <v>0.00517364007877</v>
+        <v>0.005188324686815236</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.50917543815</v>
+        <v>-0.5093781617519531</v>
       </c>
       <c r="F65" t="n">
-        <v>-0.493293297709</v>
+        <v>-0.4934899558502011</v>
       </c>
     </row>
     <row r="66">
@@ -1737,16 +1737,16 @@
         <v>0.02</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.486110417928</v>
+        <v>-0.4862785778209225</v>
       </c>
       <c r="D66" t="n">
-        <v>0.00507164477117</v>
+        <v>0.005085921216024489</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.492614852623</v>
+        <v>-0.4927954661431508</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.477076267146</v>
+        <v>-0.4772576352851212</v>
       </c>
     </row>
     <row r="67">
@@ -1757,16 +1757,16 @@
         <v>0.04</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.469671466825</v>
+        <v>-0.4698310639605393</v>
       </c>
       <c r="D67" t="n">
-        <v>0.00496942919859</v>
+        <v>0.004982923775557422</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.476025164257</v>
+        <v>-0.4761927900399447</v>
       </c>
       <c r="F67" t="n">
-        <v>-0.460838273625</v>
+        <v>-0.4610086475508099</v>
       </c>
     </row>
     <row r="68">
@@ -1777,16 +1777,16 @@
         <v>0.06</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.453217760582</v>
+        <v>-0.4533642906006592</v>
       </c>
       <c r="D68" t="n">
-        <v>0.00486670928913</v>
+        <v>0.004877003175342055</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.45941558834</v>
+        <v>-0.4595663118022344</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.444581103445</v>
+        <v>-0.4447506498563749</v>
       </c>
     </row>
     <row r="69">
@@ -1797,16 +1797,16 @@
         <v>0.08</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.436726949503</v>
+        <v>-0.4368547532494411</v>
       </c>
       <c r="D69" t="n">
-        <v>0.00475974556067</v>
+        <v>0.00477416650998494</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.442760841826</v>
+        <v>-0.4429015651895378</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.428297963293</v>
+        <v>-0.428444753143717</v>
       </c>
     </row>
     <row r="70">
@@ -1817,16 +1817,16 @@
         <v>0.1</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.420198992757</v>
+        <v>-0.4203154773927751</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0046570522901</v>
+        <v>0.004673916407848842</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.426078707173</v>
+        <v>-0.4262098783603321</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.411973588286</v>
+        <v>-0.4121062926044559</v>
       </c>
     </row>
     <row r="71">
@@ -1837,16 +1837,16 @@
         <v>0.12</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.403641678048</v>
+        <v>-0.4037548495426135</v>
       </c>
       <c r="D71" t="n">
-        <v>0.00455774382204</v>
+        <v>0.004574471313099947</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.409367736296</v>
+        <v>-0.4094982165775711</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.395615444097</v>
+        <v>-0.3957444567347084</v>
       </c>
     </row>
     <row r="72">
@@ -1857,16 +1857,16 @@
         <v>0.14</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.387057350649</v>
+        <v>-0.3871698964213355</v>
       </c>
       <c r="D72" t="n">
-        <v>0.00445813319954</v>
+        <v>0.004475109931392774</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.392630077825</v>
+        <v>-0.3927625196049123</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.379226772732</v>
+        <v>-0.3793555042672105</v>
       </c>
     </row>
     <row r="73">
@@ -1877,16 +1877,16 @@
         <v>0.16</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.370434511616</v>
+        <v>-0.3705515937052916</v>
       </c>
       <c r="D73" t="n">
-        <v>0.00435902999848</v>
+        <v>0.004377056994420805</v>
       </c>
       <c r="E73" t="n">
-        <v>-0.375855491106</v>
+        <v>-0.3760030776029737</v>
       </c>
       <c r="F73" t="n">
-        <v>-0.362794726698</v>
+        <v>-0.3629292972173861</v>
       </c>
     </row>
     <row r="74">
@@ -1897,16 +1897,16 @@
         <v>0.18</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.35377220106</v>
+        <v>-0.3538926991522335</v>
       </c>
       <c r="D74" t="n">
-        <v>0.00426254773278</v>
+        <v>0.004279164058959815</v>
       </c>
       <c r="E74" t="n">
-        <v>-0.35904181511</v>
+        <v>-0.3591906245709175</v>
       </c>
       <c r="F74" t="n">
-        <v>-0.34632405623</v>
+        <v>-0.3464560419905824</v>
       </c>
     </row>
     <row r="75">
@@ -1917,16 +1917,16 @@
         <v>0.2</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.337101283951</v>
+        <v>-0.337188624138945</v>
       </c>
       <c r="D75" t="n">
-        <v>0.00416521242822</v>
+        <v>0.004177413076872547</v>
       </c>
       <c r="E75" t="n">
-        <v>-0.342216355513</v>
+        <v>-0.3423199465075877</v>
       </c>
       <c r="F75" t="n">
-        <v>-0.329847951068</v>
+        <v>-0.3299345549635895</v>
       </c>
     </row>
     <row r="76">
@@ -1937,16 +1937,16 @@
         <v>0.22</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.320390557749</v>
+        <v>-0.32048059341646</v>
       </c>
       <c r="D76" t="n">
-        <v>0.00406372494841</v>
+        <v>0.004075978730141706</v>
       </c>
       <c r="E76" t="n">
-        <v>-0.325338711246</v>
+        <v>-0.3254445705320563</v>
       </c>
       <c r="F76" t="n">
-        <v>-0.313319622121</v>
+        <v>-0.3134090906260472</v>
       </c>
     </row>
     <row r="77">
@@ -1957,16 +1957,16 @@
         <v>0.24</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.303673008442</v>
+        <v>-0.3037643233938535</v>
       </c>
       <c r="D77" t="n">
-        <v>0.00396130421078</v>
+        <v>0.003973587127451641</v>
       </c>
       <c r="E77" t="n">
-        <v>-0.308452929645</v>
+        <v>-0.3085599403097739</v>
       </c>
       <c r="F77" t="n">
-        <v>-0.296788185648</v>
+        <v>-0.2968783501883685</v>
       </c>
     </row>
     <row r="78">
@@ -1977,16 +1977,16 @@
         <v>0.26</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.286941273888</v>
+        <v>-0.2870381435189339</v>
       </c>
       <c r="D78" t="n">
-        <v>0.00385854096566</v>
+        <v>0.003871381273346898</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.291552326071</v>
+        <v>-0.2916651448859113</v>
       </c>
       <c r="F78" t="n">
-        <v>-0.280244412276</v>
+        <v>-0.2803394747989278</v>
       </c>
     </row>
     <row r="79">
@@ -1997,16 +1997,16 @@
         <v>0.28</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.270199699387</v>
+        <v>-0.2702852617911432</v>
       </c>
       <c r="D79" t="n">
-        <v>0.00375830760487</v>
+        <v>0.003773128246316517</v>
       </c>
       <c r="E79" t="n">
-        <v>-0.274647288003</v>
+        <v>-0.2747442673559224</v>
       </c>
       <c r="F79" t="n">
-        <v>-0.263689057589</v>
+        <v>-0.2637673926520643</v>
       </c>
     </row>
     <row r="80">
@@ -2017,16 +2017,16 @@
         <v>0.3</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.253428741853</v>
+        <v>-0.2534888515085615</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00366112106268</v>
+        <v>0.003677842894939701</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.257705455168</v>
+        <v>-0.2577792709337325</v>
       </c>
       <c r="F80" t="n">
-        <v>-0.247095920571</v>
+        <v>-0.2471490164591357</v>
       </c>
     </row>
     <row r="81">
@@ -2037,16 +2037,16 @@
         <v>0.32</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.236614620507</v>
+        <v>-0.2366618354047138</v>
       </c>
       <c r="D81" t="n">
-        <v>0.00356801346637</v>
+        <v>0.003587040587752275</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.240726171277</v>
+        <v>-0.2407930478940035</v>
       </c>
       <c r="F81" t="n">
-        <v>-0.230456355509</v>
+        <v>-0.2304954485863036</v>
       </c>
     </row>
     <row r="82">
@@ -2057,16 +2057,16 @@
         <v>0.34</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.219776667891</v>
+        <v>-0.2198173533797063</v>
       </c>
       <c r="D82" t="n">
-        <v>0.00347739253426</v>
+        <v>0.003496770011761725</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.223728524668</v>
+        <v>-0.2237894851706699</v>
       </c>
       <c r="F82" t="n">
-        <v>-0.213791508376</v>
+        <v>-0.2138217102805404</v>
       </c>
     </row>
     <row r="83">
@@ -2077,16 +2077,16 @@
         <v>0.36</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.202905366425</v>
+        <v>-0.2029523319186776</v>
       </c>
       <c r="D83" t="n">
-        <v>0.00338755226139</v>
+        <v>0.003407627447397529</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.206694911365</v>
+        <v>-0.2067658511960841</v>
       </c>
       <c r="F83" t="n">
-        <v>-0.197088634447</v>
+        <v>-0.19712438125201</v>
       </c>
     </row>
     <row r="84">
@@ -2097,16 +2097,16 @@
         <v>0.38</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.186013419941</v>
+        <v>-0.1860644592481392</v>
       </c>
       <c r="D84" t="n">
-        <v>0.00329886359245</v>
+        <v>0.003315808191461605</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.189652307772</v>
+        <v>-0.1897224988326727</v>
       </c>
       <c r="F84" t="n">
-        <v>-0.180357479596</v>
+        <v>-0.1803976071474125</v>
       </c>
     </row>
     <row r="85">
@@ -2117,16 +2117,16 @@
         <v>0.4</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.169090522267</v>
+        <v>-0.1691315010446024</v>
       </c>
       <c r="D85" t="n">
-        <v>0.00321190342471</v>
+        <v>0.003226045519686783</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.172592670962</v>
+        <v>-0.17265108489942</v>
       </c>
       <c r="F85" t="n">
-        <v>-0.163585637157</v>
+        <v>-0.1636131797724918</v>
       </c>
     </row>
     <row r="86">
@@ -2137,16 +2137,16 @@
         <v>0.42</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.152146741664</v>
+        <v>-0.1521731188574399</v>
       </c>
       <c r="D86" t="n">
-        <v>0.00312216599293</v>
+        <v>0.003138792700398703</v>
       </c>
       <c r="E86" t="n">
-        <v>-0.155510787563</v>
+        <v>-0.1555559342308657</v>
       </c>
       <c r="F86" t="n">
-        <v>-0.146790121314</v>
+        <v>-0.1467977434372196</v>
       </c>
     </row>
     <row r="87">
@@ -2157,16 +2157,16 @@
         <v>0.44</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.135166038079</v>
+        <v>-0.135193501250146</v>
       </c>
       <c r="D87" t="n">
-        <v>0.00303362131277</v>
+        <v>0.003050239476365694</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.138395001167</v>
+        <v>-0.138444464424877</v>
       </c>
       <c r="F87" t="n">
-        <v>-0.129953724851</v>
+        <v>-0.1299578263798056</v>
       </c>
     </row>
     <row r="88">
@@ -2177,16 +2177,16 @@
         <v>0.46</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.118156911773</v>
+        <v>-0.1181840984945763</v>
       </c>
       <c r="D88" t="n">
-        <v>0.00294248685457</v>
+        <v>0.002958219005573808</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.121254510657</v>
+        <v>-0.121302930665145</v>
       </c>
       <c r="F88" t="n">
-        <v>-0.113090466677</v>
+        <v>-0.1130972508286101</v>
       </c>
     </row>
     <row r="89">
@@ -2197,16 +2197,16 @@
         <v>0.48</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.101126384547</v>
+        <v>-0.101152893024739</v>
       </c>
       <c r="D89" t="n">
-        <v>0.00284853023232</v>
+        <v>0.00286264102008927</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.104088883078</v>
+        <v>-0.1041368299935534</v>
       </c>
       <c r="F89" t="n">
-        <v>-0.096212573385</v>
+        <v>-0.09622452834950757</v>
       </c>
     </row>
     <row r="90">
@@ -2217,16 +2217,16 @@
         <v>0.5</v>
       </c>
       <c r="C90" t="n">
-        <v>-0.0840708566701</v>
+        <v>-0.08408502220570054</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0027511445177</v>
+        <v>0.002762629686415539</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.0869020980584</v>
+        <v>-0.08693161844213915</v>
       </c>
       <c r="F90" t="n">
-        <v>-0.0793224497094</v>
+        <v>-0.07932131371571938</v>
       </c>
     </row>
     <row r="91">
@@ -2237,16 +2237,16 @@
         <v>0.52</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.0669939958241</v>
+        <v>-0.06700959571074953</v>
       </c>
       <c r="D91" t="n">
-        <v>0.00265135487745</v>
+        <v>0.002661434929311856</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.0697133137041</v>
+        <v>-0.06975102446263115</v>
       </c>
       <c r="F91" t="n">
-        <v>-0.0624109806794</v>
+        <v>-0.06240778816049009</v>
       </c>
     </row>
     <row r="92">
@@ -2257,16 +2257,16 @@
         <v>0.54</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.0499078846114</v>
+        <v>-0.0499231829918636</v>
       </c>
       <c r="D92" t="n">
-        <v>0.00255011649783</v>
+        <v>0.002560904414690849</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.0525230448662</v>
+        <v>-0.05255928945044097</v>
       </c>
       <c r="F92" t="n">
-        <v>-0.0454877729236</v>
+        <v>-0.04548294018462418</v>
       </c>
     </row>
     <row r="93">
@@ -2277,16 +2277,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.0327928976753</v>
+        <v>-0.03279885901295625</v>
       </c>
       <c r="D93" t="n">
-        <v>0.00245101536635</v>
+        <v>0.00246459307547733</v>
       </c>
       <c r="E93" t="n">
-        <v>-0.0353047554625</v>
+        <v>-0.03533550049162137</v>
       </c>
       <c r="F93" t="n">
-        <v>-0.0285330797961</v>
+        <v>-0.0285147013153022</v>
       </c>
     </row>
     <row r="94">
@@ -2297,16 +2297,16 @@
         <v>0.58</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.015643957365</v>
+        <v>-0.01565313832207531</v>
       </c>
       <c r="D94" t="n">
-        <v>0.00235627907846</v>
+        <v>0.002368733327505192</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.018061690584</v>
+        <v>-0.01809302870387608</v>
       </c>
       <c r="F94" t="n">
-        <v>-0.0115407867316</v>
+        <v>-0.01152698946072039</v>
       </c>
     </row>
     <row r="95">
@@ -2317,16 +2317,16 @@
         <v>0.6</v>
       </c>
       <c r="C95" t="n">
-        <v>0.00151336346903</v>
+        <v>0.001499821636650544</v>
       </c>
       <c r="D95" t="n">
-        <v>0.00226039046181</v>
+        <v>0.002271996195440526</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.000807172564885</v>
+        <v>-0.0008416166949807291</v>
       </c>
       <c r="F95" t="n">
-        <v>0.00545807631907</v>
+        <v>0.005465138939195313</v>
       </c>
     </row>
     <row r="96">
@@ -2337,16 +2337,16 @@
         <v>0.62</v>
       </c>
       <c r="C96" t="n">
-        <v>0.0186949556112</v>
+        <v>0.01868760501453259</v>
       </c>
       <c r="D96" t="n">
-        <v>0.00215744738468</v>
+        <v>0.002170079204148703</v>
       </c>
       <c r="E96" t="n">
-        <v>0.0164595691278</v>
+        <v>0.0164295371787837</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0224588187907</v>
+        <v>0.02247665418352707</v>
       </c>
     </row>
     <row r="97">
@@ -2357,16 +2357,16 @@
         <v>0.64</v>
       </c>
       <c r="C97" t="n">
-        <v>0.0359036103595</v>
+        <v>0.03590101607762701</v>
       </c>
       <c r="D97" t="n">
-        <v>0.00205399975712</v>
+        <v>0.002068877591908077</v>
       </c>
       <c r="E97" t="n">
-        <v>0.0337556736442</v>
+        <v>0.03373443022499778</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0394894655805</v>
+        <v>0.03951721108095629</v>
       </c>
     </row>
     <row r="98">
@@ -2377,16 +2377,16 @@
         <v>0</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.498224919349</v>
+        <v>-0.4984300174323141</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0042555043046</v>
+        <v>0.004255407347020085</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.50457101866</v>
+        <v>-0.5048242489232173</v>
       </c>
       <c r="F98" t="n">
-        <v>-0.490161239873</v>
+        <v>-0.4903388284431713</v>
       </c>
     </row>
     <row r="99">
@@ -2397,16 +2397,16 @@
         <v>0.02</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.482003407178</v>
+        <v>-0.4822062269103852</v>
       </c>
       <c r="D99" t="n">
-        <v>0.00418808162957</v>
+        <v>0.004189580363956094</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.48829267946</v>
+        <v>-0.4885422005971769</v>
       </c>
       <c r="F99" t="n">
-        <v>-0.474055591125</v>
+        <v>-0.4742294795538555</v>
       </c>
     </row>
     <row r="100">
@@ -2417,16 +2417,16 @@
         <v>0.04</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.465756383519</v>
+        <v>-0.4659658072411607</v>
       </c>
       <c r="D100" t="n">
-        <v>0.00412362105232</v>
+        <v>0.004127009744080336</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.471982522122</v>
+        <v>-0.4722427614556519</v>
       </c>
       <c r="F100" t="n">
-        <v>-0.457917160825</v>
+        <v>-0.458095942729047</v>
       </c>
     </row>
     <row r="101">
@@ -2437,16 +2437,16 @@
         <v>0.06</v>
       </c>
       <c r="C101" t="n">
-        <v>-0.449489052692</v>
+        <v>-0.4497018392738964</v>
       </c>
       <c r="D101" t="n">
-        <v>0.00406257547664</v>
+        <v>0.004067547393742221</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.455656783331</v>
+        <v>-0.4559233536103333</v>
       </c>
       <c r="F101" t="n">
-        <v>-0.441752339953</v>
+        <v>-0.4419333260357048</v>
       </c>
     </row>
     <row r="102">
@@ -2457,16 +2457,16 @@
         <v>0.08</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.43320170822</v>
+        <v>-0.4333861661547975</v>
       </c>
       <c r="D102" t="n">
-        <v>0.00400066731243</v>
+        <v>0.004012909072946983</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.439313217761</v>
+        <v>-0.4395653587464547</v>
       </c>
       <c r="F102" t="n">
-        <v>-0.425577596672</v>
+        <v>-0.4257374511583922</v>
       </c>
     </row>
     <row r="103">
@@ -2477,16 +2477,16 @@
         <v>0.1</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.416851138401</v>
+        <v>-0.4170354730814347</v>
       </c>
       <c r="D103" t="n">
-        <v>0.00393817036177</v>
+        <v>0.003950645841224835</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.422903881061</v>
+        <v>-0.4231538920621798</v>
       </c>
       <c r="F103" t="n">
-        <v>-0.409362869354</v>
+        <v>-0.409523119279636</v>
       </c>
     </row>
     <row r="104">
@@ -2497,16 +2497,16 @@
         <v>0.12</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.400478205048</v>
+        <v>-0.4006470313424049</v>
       </c>
       <c r="D104" t="n">
-        <v>0.00387185265435</v>
+        <v>0.00388156491846103</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.406464399377</v>
+        <v>-0.4066842197608249</v>
       </c>
       <c r="F104" t="n">
-        <v>-0.393137030623</v>
+        <v>-0.3933030914539044</v>
       </c>
     </row>
     <row r="105">
@@ -2517,16 +2517,16 @@
         <v>0.14</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.384072530381</v>
+        <v>-0.3842202395076669</v>
       </c>
       <c r="D105" t="n">
-        <v>0.00380227768995</v>
+        <v>0.003811663976120596</v>
       </c>
       <c r="E105" t="n">
-        <v>-0.389975210427</v>
+        <v>-0.3901848228366163</v>
       </c>
       <c r="F105" t="n">
-        <v>-0.376904883796</v>
+        <v>-0.3770709761117912</v>
       </c>
     </row>
     <row r="106">
@@ -2537,16 +2537,16 @@
         <v>0.16</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.367632328769</v>
+        <v>-0.367772311948048</v>
       </c>
       <c r="D106" t="n">
-        <v>0.00373223924954</v>
+        <v>0.003742264636831584</v>
       </c>
       <c r="E106" t="n">
-        <v>-0.3734641062</v>
+        <v>-0.3736639405902373</v>
       </c>
       <c r="F106" t="n">
-        <v>-0.360661187633</v>
+        <v>-0.3608194747493654</v>
       </c>
     </row>
     <row r="107">
@@ -2557,16 +2557,16 @@
         <v>0.18</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.351172721158</v>
+        <v>-0.3513001725569004</v>
       </c>
       <c r="D107" t="n">
-        <v>0.00366411665586</v>
+        <v>0.003671071326348716</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.356924704319</v>
+        <v>-0.3571098145347369</v>
       </c>
       <c r="F107" t="n">
-        <v>-0.344393432555</v>
+        <v>-0.3445548808892216</v>
       </c>
     </row>
     <row r="108">
@@ -2577,16 +2577,16 @@
         <v>0.2</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.334672315705</v>
+        <v>-0.3347793279274833</v>
       </c>
       <c r="D108" t="n">
-        <v>0.0035925562406</v>
+        <v>0.003603598256515815</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.340333350883</v>
+        <v>-0.340494810455561</v>
       </c>
       <c r="F108" t="n">
-        <v>-0.328106914684</v>
+        <v>-0.3282366825234853</v>
       </c>
     </row>
     <row r="109">
@@ -2597,16 +2597,16 @@
         <v>0.22</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.318124154547</v>
+        <v>-0.3182285263103771</v>
       </c>
       <c r="D109" t="n">
-        <v>0.00352674326374</v>
+        <v>0.003538324123963358</v>
       </c>
       <c r="E109" t="n">
-        <v>-0.323700456452</v>
+        <v>-0.3238586481247605</v>
       </c>
       <c r="F109" t="n">
-        <v>-0.311758413724</v>
+        <v>-0.3118823299254814</v>
       </c>
     </row>
     <row r="110">
@@ -2617,16 +2617,16 @@
         <v>0.24</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.301553907379</v>
+        <v>-0.3016558791194638</v>
       </c>
       <c r="D110" t="n">
-        <v>0.00346332145799</v>
+        <v>0.003474213068775637</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.307054916444</v>
+        <v>-0.3072090581846316</v>
       </c>
       <c r="F110" t="n">
-        <v>-0.295379491722</v>
+        <v>-0.2955014375574407</v>
       </c>
     </row>
     <row r="111">
@@ -2637,16 +2637,16 @@
         <v>0.26</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.284940126427</v>
+        <v>-0.285040440853061</v>
       </c>
       <c r="D111" t="n">
-        <v>0.00339800722822</v>
+        <v>0.003409278965064444</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.290368483044</v>
+        <v>-0.290520359696357</v>
       </c>
       <c r="F111" t="n">
-        <v>-0.278951430177</v>
+        <v>-0.2790702706239738</v>
       </c>
     </row>
     <row r="112">
@@ -2657,16 +2657,16 @@
         <v>0.28</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.268280722972</v>
+        <v>-0.2683905674531624</v>
       </c>
       <c r="D112" t="n">
-        <v>0.00332677083196</v>
+        <v>0.003339155010353995</v>
       </c>
       <c r="E112" t="n">
-        <v>-0.273618143127</v>
+        <v>-0.2737807667160936</v>
       </c>
       <c r="F112" t="n">
-        <v>-0.262469584112</v>
+        <v>-0.2625991010097799</v>
       </c>
     </row>
     <row r="113">
@@ -2677,16 +2677,16 @@
         <v>0.3</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.251609088047</v>
+        <v>-0.2516845447955472</v>
       </c>
       <c r="D113" t="n">
-        <v>0.00325606996622</v>
+        <v>0.003267316052215299</v>
       </c>
       <c r="E113" t="n">
-        <v>-0.256861906162</v>
+        <v>-0.2569780684671841</v>
       </c>
       <c r="F113" t="n">
-        <v>-0.245980872904</v>
+        <v>-0.2460704215167011</v>
       </c>
     </row>
     <row r="114">
@@ -2697,16 +2697,16 @@
         <v>0.32</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.234893032654</v>
+        <v>-0.2349719554397355</v>
       </c>
       <c r="D114" t="n">
-        <v>0.00318459383653</v>
+        <v>0.003195339632553184</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.240050511657</v>
+        <v>-0.2401702695692025</v>
       </c>
       <c r="F114" t="n">
-        <v>-0.229443183447</v>
+        <v>-0.2295384535711396</v>
       </c>
     </row>
     <row r="115">
@@ -2717,16 +2717,16 @@
         <v>0.34</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.218165406058</v>
+        <v>-0.2182482059056992</v>
       </c>
       <c r="D115" t="n">
-        <v>0.00311238241381</v>
+        <v>0.003124026837522275</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.223225234833</v>
+        <v>-0.223347929149023</v>
       </c>
       <c r="F115" t="n">
-        <v>-0.21289982137</v>
+        <v>-0.212997135683465</v>
       </c>
     </row>
     <row r="116">
@@ -2737,16 +2737,16 @@
         <v>0.36</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.201425587371</v>
+        <v>-0.201510292822196</v>
       </c>
       <c r="D116" t="n">
-        <v>0.00304146163503</v>
+        <v>0.003053697129121972</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.20638524239</v>
+        <v>-0.2065089870086485</v>
       </c>
       <c r="F116" t="n">
-        <v>-0.196343054199</v>
+        <v>-0.1964403027121868</v>
       </c>
     </row>
     <row r="117">
@@ -2757,16 +2757,16 @@
         <v>0.38</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.184662271611</v>
+        <v>-0.1847338664846356</v>
       </c>
       <c r="D117" t="n">
-        <v>0.00297350161411</v>
+        <v>0.002990387866112405</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.189522472099</v>
+        <v>-0.1896404154620601</v>
       </c>
       <c r="F117" t="n">
-        <v>-0.17975501462</v>
+        <v>-0.1798322592343515</v>
       </c>
     </row>
     <row r="118">
@@ -2777,16 +2777,16 @@
         <v>0.4</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.167859172717</v>
+        <v>-0.1679037409446837</v>
       </c>
       <c r="D118" t="n">
-        <v>0.00291206364818</v>
+        <v>0.00293123807036349</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.172623479639</v>
+        <v>-0.1727098610046252</v>
       </c>
       <c r="F118" t="n">
-        <v>-0.163114291062</v>
+        <v>-0.1631598872820064</v>
       </c>
     </row>
     <row r="119">
@@ -2797,16 +2797,16 @@
         <v>0.42</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.151014411825</v>
+        <v>-0.1510576001357298</v>
       </c>
       <c r="D119" t="n">
-        <v>0.00285342955454</v>
+        <v>0.002871688541184856</v>
       </c>
       <c r="E119" t="n">
-        <v>-0.155676484659</v>
+        <v>-0.1557581859577093</v>
       </c>
       <c r="F119" t="n">
-        <v>-0.14642553556</v>
+        <v>-0.1464663615834594</v>
       </c>
     </row>
     <row r="120">
@@ -2817,16 +2817,16 @@
         <v>0.44</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.134137875305</v>
+        <v>-0.1341852806703606</v>
       </c>
       <c r="D120" t="n">
-        <v>0.00279107518551</v>
+        <v>0.002808048192979245</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.138688158331</v>
+        <v>-0.1387707327812775</v>
       </c>
       <c r="F120" t="n">
-        <v>-0.129695419293</v>
+        <v>-0.1297370246084917</v>
       </c>
     </row>
     <row r="121">
@@ -2837,16 +2837,16 @@
         <v>0.46</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.117236239713</v>
+        <v>-0.1172870240263832</v>
       </c>
       <c r="D121" t="n">
-        <v>0.00272752014392</v>
+        <v>0.002741578151221877</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.121679639323</v>
+        <v>-0.1217588635300215</v>
       </c>
       <c r="F121" t="n">
-        <v>-0.112937210495</v>
+        <v>-0.112981818877647</v>
       </c>
     </row>
     <row r="122">
@@ -2857,16 +2857,16 @@
         <v>0.48</v>
       </c>
       <c r="C122" t="n">
-        <v>-0.100305989437</v>
+        <v>-0.1003499306824993</v>
       </c>
       <c r="D122" t="n">
-        <v>0.00266583773318</v>
+        <v>0.002679751176027751</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.104647415446</v>
+        <v>-0.1047143102930406</v>
       </c>
       <c r="F122" t="n">
-        <v>-0.09613833932139999</v>
+        <v>-0.09616847117011584</v>
       </c>
     </row>
     <row r="123">
@@ -2877,16 +2877,16 @@
         <v>0.5</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.08334881015370001</v>
+        <v>-0.08338561666859672</v>
       </c>
       <c r="D123" t="n">
-        <v>0.00260391398902</v>
+        <v>0.002620074822073532</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.0875824069056</v>
+        <v>-0.08764366435032223</v>
       </c>
       <c r="F123" t="n">
-        <v>-0.0793017982019</v>
+        <v>-0.07931692391262857</v>
       </c>
     </row>
     <row r="124">
@@ -2897,16 +2897,16 @@
         <v>0.52</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.06635356487419999</v>
+        <v>-0.06638854679770594</v>
       </c>
       <c r="D124" t="n">
-        <v>0.00253897152397</v>
+        <v>0.002552219641825912</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.070470834059</v>
+        <v>-0.07052275681723508</v>
       </c>
       <c r="F124" t="n">
-        <v>-0.0624191009271</v>
+        <v>-0.0624310550686884</v>
       </c>
     </row>
     <row r="125">
@@ -2917,16 +2917,16 @@
         <v>0.54</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.0493284239406</v>
+        <v>-0.04936917667128382</v>
       </c>
       <c r="D125" t="n">
-        <v>0.00246752754753</v>
+        <v>0.002479402917812849</v>
       </c>
       <c r="E125" t="n">
-        <v>-0.0533138217714</v>
+        <v>-0.05336909366504639</v>
       </c>
       <c r="F125" t="n">
-        <v>-0.045516409584</v>
+        <v>-0.04553688316970561</v>
       </c>
     </row>
     <row r="126">
@@ -2937,16 +2937,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.0322777086042</v>
+        <v>-0.03230457941542042</v>
       </c>
       <c r="D126" t="n">
-        <v>0.0023914536564</v>
+        <v>0.002400727618858118</v>
       </c>
       <c r="E126" t="n">
-        <v>-0.0361250984154</v>
+        <v>-0.03616767079791305</v>
       </c>
       <c r="F126" t="n">
-        <v>-0.0285995210377</v>
+        <v>-0.02861057499880459</v>
       </c>
     </row>
     <row r="127">
@@ -2957,16 +2957,16 @@
         <v>0.58</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.015198595155</v>
+        <v>-0.0152240038729035</v>
       </c>
       <c r="D127" t="n">
-        <v>0.00231248235552</v>
+        <v>0.002320341916966236</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.0189083595476</v>
+        <v>-0.01894572169205144</v>
       </c>
       <c r="F127" t="n">
-        <v>-0.0116582380455</v>
+        <v>-0.01166281177688067</v>
       </c>
     </row>
     <row r="128">
@@ -2977,16 +2977,16 @@
         <v>0.6</v>
       </c>
       <c r="C128" t="n">
-        <v>0.00189361900871</v>
+        <v>0.001870864823120932</v>
       </c>
       <c r="D128" t="n">
-        <v>0.0022321723591</v>
+        <v>0.00223998173934041</v>
       </c>
       <c r="E128" t="n">
-        <v>-0.00167357955062</v>
+        <v>-0.001705692675691317</v>
       </c>
       <c r="F128" t="n">
-        <v>0.00530043326394</v>
+        <v>0.005291965300226131</v>
       </c>
     </row>
     <row r="129">
@@ -2997,16 +2997,16 @@
         <v>0.62</v>
       </c>
       <c r="C129" t="n">
-        <v>0.0190289819003</v>
+        <v>0.01901134117680119</v>
       </c>
       <c r="D129" t="n">
-        <v>0.00215140182605</v>
+        <v>0.00215889708519147</v>
       </c>
       <c r="E129" t="n">
-        <v>0.0156034890422</v>
+        <v>0.01557360726957135</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0222928977837</v>
+        <v>0.02229141017870173</v>
       </c>
     </row>
     <row r="130">
@@ -3017,16 +3017,16 @@
         <v>0.64</v>
       </c>
       <c r="C130" t="n">
-        <v>0.0361931571165</v>
+        <v>0.03617248414433041</v>
       </c>
       <c r="D130" t="n">
-        <v>0.00206845498252</v>
+        <v>0.002074798237566591</v>
       </c>
       <c r="E130" t="n">
-        <v>0.0329044823755</v>
+        <v>0.03287261686712029</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0393128930678</v>
+        <v>0.03930486107010633</v>
       </c>
     </row>
     <row r="131">
@@ -3037,16 +3037,16 @@
         <v>0.66</v>
       </c>
       <c r="C131" t="n">
-        <v>0.0533743695411</v>
+        <v>0.05335211773661355</v>
       </c>
       <c r="D131" t="n">
-        <v>0.00198001359362</v>
+        <v>0.001987072880223069</v>
       </c>
       <c r="E131" t="n">
-        <v>0.0502207302417</v>
+        <v>0.05018752059673481</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0563361626931</v>
+        <v>0.05632875193939402</v>
       </c>
     </row>
     <row r="132">
@@ -3057,16 +3057,16 @@
         <v>0.68</v>
       </c>
       <c r="C132" t="n">
-        <v>0.0705809797158</v>
+        <v>0.07056579515831585</v>
       </c>
       <c r="D132" t="n">
-        <v>0.00188726508197</v>
+        <v>0.001893549143613528</v>
       </c>
       <c r="E132" t="n">
-        <v>0.0675603966767</v>
+        <v>0.06753990620194905</v>
       </c>
       <c r="F132" t="n">
-        <v>0.07337702867900001</v>
+        <v>0.07338059030525201</v>
       </c>
     </row>
     <row r="133">
@@ -3077,16 +3077,16 @@
         <v>0</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.491554969481</v>
+        <v>-0.4917705788821944</v>
       </c>
       <c r="D133" t="n">
-        <v>0.00472675864767</v>
+        <v>0.004736721372251619</v>
       </c>
       <c r="E133" t="n">
-        <v>-0.497172932007</v>
+        <v>-0.4974356794946972</v>
       </c>
       <c r="F133" t="n">
-        <v>-0.484374472055</v>
+        <v>-0.4845144984622873</v>
       </c>
     </row>
     <row r="134">
@@ -3097,16 +3097,16 @@
         <v>0.02</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.47566790967</v>
+        <v>-0.4758877473589779</v>
       </c>
       <c r="D134" t="n">
-        <v>0.00465954159955</v>
+        <v>0.004669761159373472</v>
       </c>
       <c r="E134" t="n">
-        <v>-0.481160238919</v>
+        <v>-0.4814275331586497</v>
       </c>
       <c r="F134" t="n">
-        <v>-0.468686196344</v>
+        <v>-0.4688302174376888</v>
       </c>
     </row>
     <row r="135">
@@ -3117,16 +3117,16 @@
         <v>0.04</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.459759299445</v>
+        <v>-0.4599558434093935</v>
       </c>
       <c r="D135" t="n">
-        <v>0.00459654133252</v>
+        <v>0.004610304395835859</v>
       </c>
       <c r="E135" t="n">
-        <v>-0.46512372844</v>
+        <v>-0.465387465318817</v>
       </c>
       <c r="F135" t="n">
-        <v>-0.452973332411</v>
+        <v>-0.453090267284721</v>
       </c>
     </row>
     <row r="136">
@@ -3137,16 +3137,16 @@
         <v>0.06</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.443806335266</v>
+        <v>-0.4440035691890733</v>
       </c>
       <c r="D136" t="n">
-        <v>0.0045420185845</v>
+        <v>0.004556324985896177</v>
       </c>
       <c r="E136" t="n">
-        <v>-0.449073731251</v>
+        <v>-0.4493407215131651</v>
       </c>
       <c r="F136" t="n">
-        <v>-0.437208718931</v>
+        <v>-0.4373270621446341</v>
       </c>
     </row>
     <row r="137">
@@ -3157,16 +3157,16 @@
         <v>0.08</v>
       </c>
       <c r="C137" t="n">
-        <v>-0.427818234572</v>
+        <v>-0.4279952076848543</v>
       </c>
       <c r="D137" t="n">
-        <v>0.0044799697747</v>
+        <v>0.004492125079444159</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.432970321045</v>
+        <v>-0.4332053979880728</v>
       </c>
       <c r="F137" t="n">
-        <v>-0.421395630187</v>
+        <v>-0.421481006710299</v>
       </c>
     </row>
     <row r="138">
@@ -3177,16 +3177,16 @@
         <v>0.1</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.411759472143</v>
+        <v>-0.4119173716831631</v>
       </c>
       <c r="D138" t="n">
-        <v>0.00440741068628</v>
+        <v>0.004421027633772779</v>
       </c>
       <c r="E138" t="n">
-        <v>-0.416763452835</v>
+        <v>-0.4169716519875042</v>
       </c>
       <c r="F138" t="n">
-        <v>-0.405479566336</v>
+        <v>-0.4055397201081856</v>
       </c>
     </row>
     <row r="139">
@@ -3197,16 +3197,16 @@
         <v>0.12</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.395633762714</v>
+        <v>-0.3957910323450227</v>
       </c>
       <c r="D139" t="n">
-        <v>0.00433977418731</v>
+        <v>0.004349890924310327</v>
       </c>
       <c r="E139" t="n">
-        <v>-0.400611896795</v>
+        <v>-0.400788899967699</v>
       </c>
       <c r="F139" t="n">
-        <v>-0.389475682105</v>
+        <v>-0.3895342476734776</v>
       </c>
     </row>
     <row r="140">
@@ -3217,16 +3217,16 @@
         <v>0.14</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.379451304929</v>
+        <v>-0.3796046392012517</v>
       </c>
       <c r="D140" t="n">
-        <v>0.0042620778221</v>
+        <v>0.004273295629236587</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.384413691949</v>
+        <v>-0.3845838908182611</v>
       </c>
       <c r="F140" t="n">
-        <v>-0.373377616169</v>
+        <v>-0.3734311877177277</v>
       </c>
     </row>
     <row r="141">
@@ -3237,16 +3237,16 @@
         <v>0.16</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.363240112472</v>
+        <v>-0.3633916031447383</v>
       </c>
       <c r="D141" t="n">
-        <v>0.00418492879625</v>
+        <v>0.004197899716924194</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.368171315728</v>
+        <v>-0.368337200085036</v>
       </c>
       <c r="F141" t="n">
-        <v>-0.357248751873</v>
+        <v>-0.3573022831058195</v>
       </c>
     </row>
     <row r="142">
@@ -3257,16 +3257,16 @@
         <v>0.18</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.346998138856</v>
+        <v>-0.3471570589023728</v>
       </c>
       <c r="D142" t="n">
-        <v>0.00411089708654</v>
+        <v>0.00412219553543249</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.351896204682</v>
+        <v>-0.3520683820928427</v>
       </c>
       <c r="F142" t="n">
-        <v>-0.341093829407</v>
+        <v>-0.3411610269924568</v>
       </c>
     </row>
     <row r="143">
@@ -3277,16 +3277,16 @@
         <v>0.2</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.330738800153</v>
+        <v>-0.3308943776084853</v>
       </c>
       <c r="D143" t="n">
-        <v>0.00403874848923</v>
+        <v>0.004055274959875678</v>
       </c>
       <c r="E143" t="n">
-        <v>-0.335613788653</v>
+        <v>-0.3357931446935591</v>
       </c>
       <c r="F143" t="n">
-        <v>-0.324922644858</v>
+        <v>-0.3249837669116022</v>
       </c>
     </row>
     <row r="144">
@@ -3297,16 +3297,16 @@
         <v>0.22</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.314428275497</v>
+        <v>-0.3145657856905882</v>
       </c>
       <c r="D144" t="n">
-        <v>0.00397876855665</v>
+        <v>0.004003140734260247</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.319279157257</v>
+        <v>-0.3194406164664274</v>
       </c>
       <c r="F144" t="n">
-        <v>-0.308671219</v>
+        <v>-0.3086994031348604</v>
       </c>
     </row>
     <row r="145">
@@ -3317,16 +3317,16 @@
         <v>0.24</v>
       </c>
       <c r="C145" t="n">
-        <v>-0.298067320141</v>
+        <v>-0.298197517926981</v>
       </c>
       <c r="D145" t="n">
-        <v>0.00392205525084</v>
+        <v>0.003944908655529996</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.302880277542</v>
+        <v>-0.303028045870656</v>
       </c>
       <c r="F145" t="n">
-        <v>-0.292354618916</v>
+        <v>-0.2923855382191736</v>
       </c>
     </row>
     <row r="146">
@@ -3337,16 +3337,16 @@
         <v>0.26</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.281672683822</v>
+        <v>-0.2817794317582843</v>
       </c>
       <c r="D146" t="n">
-        <v>0.00386149765415</v>
+        <v>0.003887548411458355</v>
       </c>
       <c r="E146" t="n">
-        <v>-0.286442422154</v>
+        <v>-0.2865709647994867</v>
       </c>
       <c r="F146" t="n">
-        <v>-0.276017731674</v>
+        <v>-0.2760201129506674</v>
       </c>
     </row>
     <row r="147">
@@ -3357,16 +3357,16 @@
         <v>0.28</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.265230502779</v>
+        <v>-0.2653285706708169</v>
       </c>
       <c r="D147" t="n">
-        <v>0.00380483980518</v>
+        <v>0.003832336215056504</v>
       </c>
       <c r="E147" t="n">
-        <v>-0.269964004144</v>
+        <v>-0.2700842854768553</v>
       </c>
       <c r="F147" t="n">
-        <v>-0.259624044863</v>
+        <v>-0.2596189434192375</v>
       </c>
     </row>
     <row r="148">
@@ -3377,16 +3377,16 @@
         <v>0.3</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.24875999951</v>
+        <v>-0.2488502638540129</v>
       </c>
       <c r="D148" t="n">
-        <v>0.00375003809404</v>
+        <v>0.003780236759056037</v>
       </c>
       <c r="E148" t="n">
-        <v>-0.253448340569</v>
+        <v>-0.2535670382804875</v>
       </c>
       <c r="F148" t="n">
-        <v>-0.243207267873</v>
+        <v>-0.2431961166632259</v>
       </c>
     </row>
     <row r="149">
@@ -3397,16 +3397,16 @@
         <v>0.32</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.232243690691</v>
+        <v>-0.232316250236861</v>
       </c>
       <c r="D149" t="n">
-        <v>0.00369478669849</v>
+        <v>0.003724892221567955</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.236878572741</v>
+        <v>-0.2369729943375001</v>
       </c>
       <c r="F149" t="n">
-        <v>-0.226748858279</v>
+        <v>-0.2267279320716842</v>
       </c>
     </row>
     <row r="150">
@@ -3417,16 +3417,16 @@
         <v>0.34</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.215680055308</v>
+        <v>-0.2157520673611162</v>
       </c>
       <c r="D150" t="n">
-        <v>0.00364081581419</v>
+        <v>0.00366998429106259</v>
       </c>
       <c r="E150" t="n">
-        <v>-0.220268665338</v>
+        <v>-0.2203635091255132</v>
       </c>
       <c r="F150" t="n">
-        <v>-0.210245319394</v>
+        <v>-0.2102232258054775</v>
       </c>
     </row>
     <row r="151">
@@ -3437,16 +3437,16 @@
         <v>0.36</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.199080367704</v>
+        <v>-0.1991520449729367</v>
       </c>
       <c r="D151" t="n">
-        <v>0.00358563114763</v>
+        <v>0.003612476998968139</v>
       </c>
       <c r="E151" t="n">
-        <v>-0.203630911973</v>
+        <v>-0.2037206818587904</v>
       </c>
       <c r="F151" t="n">
-        <v>-0.193693173505</v>
+        <v>-0.1936735529361187</v>
       </c>
     </row>
     <row r="152">
@@ -3457,16 +3457,16 @@
         <v>0.38</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.182424681298</v>
+        <v>-0.1825094291434914</v>
       </c>
       <c r="D152" t="n">
-        <v>0.00351923544725</v>
+        <v>0.003547853199638283</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.186911484113</v>
+        <v>-0.1870217691236027</v>
       </c>
       <c r="F152" t="n">
-        <v>-0.177117174176</v>
+        <v>-0.1771025112896014</v>
       </c>
     </row>
     <row r="153">
@@ -3477,16 +3477,16 @@
         <v>0.4</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.165747364651</v>
+        <v>-0.1658115351098827</v>
       </c>
       <c r="D153" t="n">
-        <v>0.00345095531042</v>
+        <v>0.003465116858937165</v>
       </c>
       <c r="E153" t="n">
-        <v>-0.170178209238</v>
+        <v>-0.1702386763831996</v>
       </c>
       <c r="F153" t="n">
-        <v>-0.160536399427</v>
+        <v>-0.1605282441473097</v>
       </c>
     </row>
     <row r="154">
@@ -3497,16 +3497,16 @@
         <v>0.42</v>
       </c>
       <c r="C154" t="n">
-        <v>-0.149034017209</v>
+        <v>-0.1491023383372823</v>
       </c>
       <c r="D154" t="n">
-        <v>0.00336686291218</v>
+        <v>0.003380164080876348</v>
       </c>
       <c r="E154" t="n">
-        <v>-0.153378424408</v>
+        <v>-0.1534426569534002</v>
       </c>
       <c r="F154" t="n">
-        <v>-0.143950817248</v>
+        <v>-0.1439493329145414</v>
       </c>
     </row>
     <row r="155">
@@ -3517,16 +3517,16 @@
         <v>0.44</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.132303164564</v>
+        <v>-0.132377032366362</v>
       </c>
       <c r="D155" t="n">
-        <v>0.00328214611388</v>
+        <v>0.003296275577047546</v>
       </c>
       <c r="E155" t="n">
-        <v>-0.136555595062</v>
+        <v>-0.1366250714218014</v>
       </c>
       <c r="F155" t="n">
-        <v>-0.127353623108</v>
+        <v>-0.127355872304479</v>
       </c>
     </row>
     <row r="156">
@@ -3537,16 +3537,16 @@
         <v>0.46</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.115556081653</v>
+        <v>-0.1156264353199376</v>
       </c>
       <c r="D156" t="n">
-        <v>0.00319726530089</v>
+        <v>0.003214044427581194</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.119712015543</v>
+        <v>-0.1197766873888071</v>
       </c>
       <c r="F156" t="n">
-        <v>-0.110737593191</v>
+        <v>-0.1107274294290717</v>
       </c>
     </row>
     <row r="157">
@@ -3557,16 +3557,16 @@
         <v>0.48</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.0987750000303</v>
+        <v>-0.09882090190880657</v>
       </c>
       <c r="D157" t="n">
-        <v>0.00311718177933</v>
+        <v>0.003135781089025127</v>
       </c>
       <c r="E157" t="n">
-        <v>-0.102832882292</v>
+        <v>-0.102866150304421</v>
       </c>
       <c r="F157" t="n">
-        <v>-0.0940777235098</v>
+        <v>-0.09403417964463756</v>
       </c>
     </row>
     <row r="158">
@@ -3577,16 +3577,16 @@
         <v>0.5</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.08193727427190001</v>
+        <v>-0.0819843200861385</v>
       </c>
       <c r="D158" t="n">
-        <v>0.00303873539603</v>
+        <v>0.003056372528648114</v>
       </c>
       <c r="E158" t="n">
-        <v>-0.0858805917342</v>
+        <v>-0.08591140638597228</v>
       </c>
       <c r="F158" t="n">
-        <v>-0.0773474226184</v>
+        <v>-0.07730791178382468</v>
       </c>
     </row>
     <row r="159">
@@ -3597,16 +3597,16 @@
         <v>0.52</v>
       </c>
       <c r="C159" t="n">
-        <v>-0.0650650121956</v>
+        <v>-0.06511413325728857</v>
       </c>
       <c r="D159" t="n">
-        <v>0.0029567446909</v>
+        <v>0.002973929880087958</v>
       </c>
       <c r="E159" t="n">
-        <v>-0.06887889419529999</v>
+        <v>-0.06891072264645981</v>
       </c>
       <c r="F159" t="n">
-        <v>-0.0605755295944</v>
+        <v>-0.06053013648594696</v>
       </c>
     </row>
     <row r="160">
@@ -3617,16 +3617,16 @@
         <v>0.54</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.0481657751391</v>
+        <v>-0.04821524397701023</v>
       </c>
       <c r="D160" t="n">
-        <v>0.00287174447779</v>
+        <v>0.002884209018277097</v>
       </c>
       <c r="E160" t="n">
-        <v>-0.0518523401789</v>
+        <v>-0.05187698936825669</v>
       </c>
       <c r="F160" t="n">
-        <v>-0.0437754045616</v>
+        <v>-0.04374057634673711</v>
       </c>
     </row>
     <row r="161">
@@ -3637,16 +3637,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.0312351527733</v>
+        <v>-0.03127629564491156</v>
       </c>
       <c r="D161" t="n">
-        <v>0.00277814341355</v>
+        <v>0.00279055885447489</v>
       </c>
       <c r="E161" t="n">
-        <v>-0.0347919315003</v>
+        <v>-0.03481244652029503</v>
       </c>
       <c r="F161" t="n">
-        <v>-0.0269736637403</v>
+        <v>-0.02694415149147478</v>
       </c>
     </row>
     <row r="162">
@@ -3657,16 +3657,16 @@
         <v>0.58</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.0142643659984</v>
+        <v>-0.01430536901745496</v>
       </c>
       <c r="D162" t="n">
-        <v>0.00268364410634</v>
+        <v>0.002696863327728304</v>
       </c>
       <c r="E162" t="n">
-        <v>-0.0176937182406</v>
+        <v>-0.01771604765996226</v>
       </c>
       <c r="F162" t="n">
-        <v>-0.0101467337029</v>
+        <v>-0.01011850451236018</v>
       </c>
     </row>
     <row r="163">
@@ -3677,16 +3677,16 @@
         <v>0.6</v>
       </c>
       <c r="C163" t="n">
-        <v>0.00274406285449</v>
+        <v>0.002699726252135637</v>
       </c>
       <c r="D163" t="n">
-        <v>0.00258645923938</v>
+        <v>0.002599584325131988</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.0005503974574210001</v>
+        <v>-0.0005759885838143575</v>
       </c>
       <c r="F163" t="n">
-        <v>0.00670924973413</v>
+        <v>0.006730286806001295</v>
       </c>
     </row>
     <row r="164">
@@ -3697,16 +3697,16 @@
         <v>0.62</v>
       </c>
       <c r="C164" t="n">
-        <v>0.0197846829088</v>
+        <v>0.01974897834632996</v>
       </c>
       <c r="D164" t="n">
-        <v>0.0024882395051</v>
+        <v>0.002498194454571636</v>
       </c>
       <c r="E164" t="n">
-        <v>0.0166233865123</v>
+        <v>0.0166063791365767</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0235940860678</v>
+        <v>0.02362264050799734</v>
       </c>
     </row>
     <row r="165">
@@ -3717,16 +3717,16 @@
         <v>0.64</v>
       </c>
       <c r="C165" t="n">
-        <v>0.0368618434181</v>
+        <v>0.03683102281767887</v>
       </c>
       <c r="D165" t="n">
-        <v>0.00238441590614</v>
+        <v>0.002388647952065334</v>
       </c>
       <c r="E165" t="n">
-        <v>0.0338363204734</v>
+        <v>0.03382901463893084</v>
       </c>
       <c r="F165" t="n">
-        <v>0.040511975813</v>
+        <v>0.04052760406262657</v>
       </c>
     </row>
     <row r="166">
@@ -3737,16 +3737,16 @@
         <v>0.66</v>
       </c>
       <c r="C166" t="n">
-        <v>0.0539575664839</v>
+        <v>0.05393061741650511</v>
       </c>
       <c r="D166" t="n">
-        <v>0.00227503581625</v>
+        <v>0.002278087670112255</v>
       </c>
       <c r="E166" t="n">
-        <v>0.0510750628166</v>
+        <v>0.05107890144730298</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0574286764368</v>
+        <v>0.05743586715118987</v>
       </c>
     </row>
     <row r="167">
@@ -3757,16 +3757,16 @@
         <v>0.68</v>
       </c>
       <c r="C167" t="n">
-        <v>0.07110599077510001</v>
+        <v>0.07107831629720707</v>
       </c>
       <c r="D167" t="n">
-        <v>0.00216730386565</v>
+        <v>0.00216961174243874</v>
       </c>
       <c r="E167" t="n">
-        <v>0.06837042371</v>
+        <v>0.06837088435455296</v>
       </c>
       <c r="F167" t="n">
-        <v>0.07439404715679999</v>
+        <v>0.07440246093065639</v>
       </c>
     </row>
     <row r="168">
@@ -3777,16 +3777,16 @@
         <v>0.7</v>
       </c>
       <c r="C168" t="n">
-        <v>0.0882744807452</v>
+        <v>0.08824107724429195</v>
       </c>
       <c r="D168" t="n">
-        <v>0.00205886068591</v>
+        <v>0.002060532694858174</v>
       </c>
       <c r="E168" t="n">
-        <v>0.08567954829259999</v>
+        <v>0.08567435907694598</v>
       </c>
       <c r="F168" t="n">
-        <v>0.09138807623090001</v>
+        <v>0.09139165404449567</v>
       </c>
     </row>
     <row r="169">
@@ -3797,16 +3797,16 @@
         <v>0</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.480770918124</v>
+        <v>-0.4810148367132623</v>
       </c>
       <c r="D169" t="n">
-        <v>0.00564271847428</v>
+        <v>0.005678772908436145</v>
       </c>
       <c r="E169" t="n">
-        <v>-0.488477328117</v>
+        <v>-0.4888419110493381</v>
       </c>
       <c r="F169" t="n">
-        <v>-0.472130227156</v>
+        <v>-0.4723502567195483</v>
       </c>
     </row>
     <row r="170">
@@ -3817,16 +3817,16 @@
         <v>0.02</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.465257306405</v>
+        <v>-0.4654885109449342</v>
       </c>
       <c r="D170" t="n">
-        <v>0.00556487049355</v>
+        <v>0.005601045341044626</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.473045129787</v>
+        <v>-0.4733933384101139</v>
       </c>
       <c r="F170" t="n">
-        <v>-0.456765287496</v>
+        <v>-0.4569752138939593</v>
       </c>
     </row>
     <row r="171">
@@ -3837,16 +3837,16 @@
         <v>0.04</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.44967460866</v>
+        <v>-0.4498962155368292</v>
       </c>
       <c r="D171" t="n">
-        <v>0.00548543584528</v>
+        <v>0.005525860832192165</v>
       </c>
       <c r="E171" t="n">
-        <v>-0.457516887456</v>
+        <v>-0.4578480749440121</v>
       </c>
       <c r="F171" t="n">
-        <v>-0.441319470102</v>
+        <v>-0.4415023558533751</v>
       </c>
     </row>
     <row r="172">
@@ -3857,16 +3857,16 @@
         <v>0.06</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.434034928152</v>
+        <v>-0.4342194377220589</v>
       </c>
       <c r="D172" t="n">
-        <v>0.00542423615025</v>
+        <v>0.005482025437265676</v>
       </c>
       <c r="E172" t="n">
-        <v>-0.44192889052</v>
+        <v>-0.4422399274031914</v>
       </c>
       <c r="F172" t="n">
-        <v>-0.425781981689</v>
+        <v>-0.4259111372923012</v>
       </c>
     </row>
     <row r="173">
@@ -3877,16 +3877,16 @@
         <v>0.08</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.418330504989</v>
+        <v>-0.4184924938644417</v>
       </c>
       <c r="D173" t="n">
-        <v>0.00538570239728</v>
+        <v>0.005440104049440915</v>
       </c>
       <c r="E173" t="n">
-        <v>-0.426300273798</v>
+        <v>-0.4265838456016917</v>
       </c>
       <c r="F173" t="n">
-        <v>-0.410161462388</v>
+        <v>-0.4102858533652389</v>
       </c>
     </row>
     <row r="174">
@@ -3897,16 +3897,16 @@
         <v>0.1</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.402588508548</v>
+        <v>-0.402738269201749</v>
       </c>
       <c r="D174" t="n">
-        <v>0.0053424661468</v>
+        <v>0.005393250665537244</v>
       </c>
       <c r="E174" t="n">
-        <v>-0.410624435123</v>
+        <v>-0.4108862628812719</v>
       </c>
       <c r="F174" t="n">
-        <v>-0.394530786172</v>
+        <v>-0.3946550270243767</v>
       </c>
     </row>
     <row r="175">
@@ -3917,16 +3917,16 @@
         <v>0.12</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.386796054992</v>
+        <v>-0.3869422940479462</v>
       </c>
       <c r="D175" t="n">
-        <v>0.00528691267354</v>
+        <v>0.005335604299957619</v>
       </c>
       <c r="E175" t="n">
-        <v>-0.394869563654</v>
+        <v>-0.3951285371597759</v>
       </c>
       <c r="F175" t="n">
-        <v>-0.378871933675</v>
+        <v>-0.3789965075700685</v>
       </c>
     </row>
     <row r="176">
@@ -3937,16 +3937,16 @@
         <v>0.14</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.370965905511</v>
+        <v>-0.3711124972230265</v>
       </c>
       <c r="D176" t="n">
-        <v>0.00523085184387</v>
+        <v>0.005279642325822144</v>
       </c>
       <c r="E176" t="n">
-        <v>-0.379091788817</v>
+        <v>-0.3793524914495476</v>
       </c>
       <c r="F176" t="n">
-        <v>-0.363164559701</v>
+        <v>-0.3632922839129771</v>
       </c>
     </row>
     <row r="177">
@@ -3957,16 +3957,16 @@
         <v>0.16</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.355124916752</v>
+        <v>-0.3552755685031505</v>
       </c>
       <c r="D177" t="n">
-        <v>0.00517643311684</v>
+        <v>0.005225461575370423</v>
       </c>
       <c r="E177" t="n">
-        <v>-0.363307790189</v>
+        <v>-0.363574945989475</v>
       </c>
       <c r="F177" t="n">
-        <v>-0.347454744127</v>
+        <v>-0.3475888200031241</v>
       </c>
     </row>
     <row r="178">
@@ -3977,16 +3977,16 @@
         <v>0.18</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.33927351222</v>
+        <v>-0.3394309748376982</v>
       </c>
       <c r="D178" t="n">
-        <v>0.00512439533009</v>
+        <v>0.005173772433065169</v>
       </c>
       <c r="E178" t="n">
-        <v>-0.347520671152</v>
+        <v>-0.347795511209446</v>
       </c>
       <c r="F178" t="n">
-        <v>-0.331738098975</v>
+        <v>-0.3318781052746065</v>
       </c>
     </row>
     <row r="179">
@@ -3997,16 +3997,16 @@
         <v>0.2</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.323403635981</v>
+        <v>-0.3235454772201469</v>
       </c>
       <c r="D179" t="n">
-        <v>0.00507629515986</v>
+        <v>0.005126084806576166</v>
       </c>
       <c r="E179" t="n">
-        <v>-0.33170819018</v>
+        <v>-0.3319802753679237</v>
       </c>
       <c r="F179" t="n">
-        <v>-0.31599245034</v>
+        <v>-0.3161030083113934</v>
       </c>
     </row>
     <row r="180">
@@ -4017,16 +4017,16 @@
         <v>0.22</v>
       </c>
       <c r="C180" t="n">
-        <v>-0.307487072727</v>
+        <v>-0.3076316778237613</v>
       </c>
       <c r="D180" t="n">
-        <v>0.00503191912501</v>
+        <v>0.005081313876189836</v>
       </c>
       <c r="E180" t="n">
-        <v>-0.315869644341</v>
+        <v>-0.3161449750012464</v>
       </c>
       <c r="F180" t="n">
-        <v>-0.300170451729</v>
+        <v>-0.3002812467792264</v>
       </c>
     </row>
     <row r="181">
@@ -4037,16 +4037,16 @@
         <v>0.24</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.291514324852</v>
+        <v>-0.2916317642578025</v>
       </c>
       <c r="D181" t="n">
-        <v>0.00498674426014</v>
+        <v>0.005032438964483073</v>
       </c>
       <c r="E181" t="n">
-        <v>-0.299929669888</v>
+        <v>-0.3001572193021884</v>
       </c>
       <c r="F181" t="n">
-        <v>-0.284329406696</v>
+        <v>-0.284437603140332</v>
       </c>
     </row>
     <row r="182">
@@ -4057,16 +4057,16 @@
         <v>0.26</v>
       </c>
       <c r="C182" t="n">
-        <v>-0.275457364639</v>
+        <v>-0.2755694091278248</v>
       </c>
       <c r="D182" t="n">
-        <v>0.00493547588891</v>
+        <v>0.004983028891287843</v>
       </c>
       <c r="E182" t="n">
-        <v>-0.283864262278</v>
+        <v>-0.2840907852734373</v>
       </c>
       <c r="F182" t="n">
-        <v>-0.268453052973</v>
+        <v>-0.2685430498119272</v>
       </c>
     </row>
     <row r="183">
@@ -4077,16 +4077,16 @@
         <v>0.28</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.259326283065</v>
+        <v>-0.2594387811699198</v>
       </c>
       <c r="D183" t="n">
-        <v>0.0048780658269</v>
+        <v>0.004924205002878611</v>
       </c>
       <c r="E183" t="n">
-        <v>-0.26768475446</v>
+        <v>-0.2679088569555965</v>
       </c>
       <c r="F183" t="n">
-        <v>-0.252504879821</v>
+        <v>-0.2525433858034329</v>
       </c>
     </row>
     <row r="184">
@@ -4097,16 +4097,16 @@
         <v>0.3</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.243154887809</v>
+        <v>-0.2432660882429068</v>
       </c>
       <c r="D184" t="n">
-        <v>0.0048137058974</v>
+        <v>0.004859884572828818</v>
       </c>
       <c r="E184" t="n">
-        <v>-0.251442117507</v>
+        <v>-0.2516697076959833</v>
       </c>
       <c r="F184" t="n">
-        <v>-0.23644489569</v>
+        <v>-0.236385343970765</v>
       </c>
     </row>
     <row r="185">
@@ -4117,16 +4117,16 @@
         <v>0.32</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.226946415622</v>
+        <v>-0.2270679100321089</v>
       </c>
       <c r="D185" t="n">
-        <v>0.00475010485325</v>
+        <v>0.004798292239455131</v>
       </c>
       <c r="E185" t="n">
-        <v>-0.235167975792</v>
+        <v>-0.2354115814397826</v>
       </c>
       <c r="F185" t="n">
-        <v>-0.220265783548</v>
+        <v>-0.2202169377420189</v>
       </c>
     </row>
     <row r="186">
@@ -4137,16 +4137,16 @@
         <v>0.34</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.210719592928</v>
+        <v>-0.2108218526115521</v>
       </c>
       <c r="D186" t="n">
-        <v>0.00468856756172</v>
+        <v>0.004737572534009605</v>
       </c>
       <c r="E186" t="n">
-        <v>-0.218878044678</v>
+        <v>-0.2190788301118882</v>
       </c>
       <c r="F186" t="n">
-        <v>-0.204069057591</v>
+        <v>-0.2039993066873507</v>
       </c>
     </row>
     <row r="187">
@@ -4157,16 +4157,16 @@
         <v>0.36</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.194410356689</v>
+        <v>-0.194513179530632</v>
       </c>
       <c r="D187" t="n">
-        <v>0.00462497007676</v>
+        <v>0.004670831363048508</v>
       </c>
       <c r="E187" t="n">
-        <v>-0.202471441715</v>
+        <v>-0.2026634009871913</v>
       </c>
       <c r="F187" t="n">
-        <v>-0.187773195515</v>
+        <v>-0.1877132408661142</v>
       </c>
     </row>
     <row r="188">
@@ -4177,16 +4177,16 @@
         <v>0.38</v>
       </c>
       <c r="C188" t="n">
-        <v>-0.178062384385</v>
+        <v>-0.1781446934121896</v>
       </c>
       <c r="D188" t="n">
-        <v>0.0045585003788</v>
+        <v>0.004611465571394753</v>
       </c>
       <c r="E188" t="n">
-        <v>-0.18601647547</v>
+        <v>-0.1862032383990782</v>
       </c>
       <c r="F188" t="n">
-        <v>-0.171465233726</v>
+        <v>-0.1713947723099327</v>
       </c>
     </row>
     <row r="189">
@@ -4197,16 +4197,16 @@
         <v>0.4</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.16166131654</v>
+        <v>-0.1617356958748802</v>
       </c>
       <c r="D189" t="n">
-        <v>0.00450495176688</v>
+        <v>0.004559481039403596</v>
       </c>
       <c r="E189" t="n">
-        <v>-0.169523920873</v>
+        <v>-0.1697040324316053</v>
       </c>
       <c r="F189" t="n">
-        <v>-0.155110168695</v>
+        <v>-0.155036294404324</v>
       </c>
     </row>
     <row r="190">
@@ -4217,16 +4217,16 @@
         <v>0.42</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.145223359238</v>
+        <v>-0.1452913869802876</v>
       </c>
       <c r="D190" t="n">
-        <v>0.00444961637099</v>
+        <v>0.004504646882326263</v>
       </c>
       <c r="E190" t="n">
-        <v>-0.152991295701</v>
+        <v>-0.1531607919078688</v>
       </c>
       <c r="F190" t="n">
-        <v>-0.138725216605</v>
+        <v>-0.138646965035039</v>
       </c>
     </row>
     <row r="191">
@@ -4237,16 +4237,16 @@
         <v>0.44</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.128726775113</v>
+        <v>-0.1287851951719306</v>
       </c>
       <c r="D191" t="n">
-        <v>0.00438580113077</v>
+        <v>0.004430680878381718</v>
       </c>
       <c r="E191" t="n">
-        <v>-0.136360455002</v>
+        <v>-0.1365049845581909</v>
       </c>
       <c r="F191" t="n">
-        <v>-0.122298949708</v>
+        <v>-0.1222320011781628</v>
       </c>
     </row>
     <row r="192">
@@ -4257,16 +4257,16 @@
         <v>0.46</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.112187278614</v>
+        <v>-0.1122477717134512</v>
       </c>
       <c r="D192" t="n">
-        <v>0.00431205560465</v>
+        <v>0.004356401793415455</v>
       </c>
       <c r="E192" t="n">
-        <v>-0.119656360154</v>
+        <v>-0.119798055789909</v>
       </c>
       <c r="F192" t="n">
-        <v>-0.105847416882</v>
+        <v>-0.1057829503864305</v>
       </c>
     </row>
     <row r="193">
@@ -4277,16 +4277,16 @@
         <v>0.48</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.0955900584981</v>
+        <v>-0.09565741228984299</v>
       </c>
       <c r="D193" t="n">
-        <v>0.00422559669497</v>
+        <v>0.004271011219614099</v>
       </c>
       <c r="E193" t="n">
-        <v>-0.102880867137</v>
+        <v>-0.103019641606255</v>
       </c>
       <c r="F193" t="n">
-        <v>-0.08934393883610001</v>
+        <v>-0.08928472726955228</v>
       </c>
     </row>
     <row r="194">
@@ -4297,16 +4297,16 @@
         <v>0.5</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.0789534246024</v>
+        <v>-0.079008222513822</v>
       </c>
       <c r="D194" t="n">
-        <v>0.00413032655029</v>
+        <v>0.00416468058444124</v>
       </c>
       <c r="E194" t="n">
-        <v>-0.0860501170928</v>
+        <v>-0.08613962771877492</v>
       </c>
       <c r="F194" t="n">
-        <v>-0.07283036819950001</v>
+        <v>-0.07278243547745777</v>
       </c>
     </row>
     <row r="195">
@@ -4317,16 +4317,16 @@
         <v>0.52</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.0622786187219</v>
+        <v>-0.06233826737432348</v>
       </c>
       <c r="D195" t="n">
-        <v>0.00401888838395</v>
+        <v>0.004052629981302376</v>
       </c>
       <c r="E195" t="n">
-        <v>-0.0691272952991</v>
+        <v>-0.06922289246428903</v>
       </c>
       <c r="F195" t="n">
-        <v>-0.056318614816</v>
+        <v>-0.05628052142303286</v>
       </c>
     </row>
     <row r="196">
@@ -4337,16 +4337,16 @@
         <v>0.54</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.0455816734826</v>
+        <v>-0.04564711426366932</v>
       </c>
       <c r="D196" t="n">
-        <v>0.00390751820343</v>
+        <v>0.003941048451145151</v>
       </c>
       <c r="E196" t="n">
-        <v>-0.0521910018232</v>
+        <v>-0.05229328978834236</v>
       </c>
       <c r="F196" t="n">
-        <v>-0.0397921465273</v>
+        <v>-0.03975784158871587</v>
       </c>
     </row>
     <row r="197">
@@ -4357,16 +4357,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.0288563944508</v>
+        <v>-0.02891367066909058</v>
       </c>
       <c r="D197" t="n">
-        <v>0.00379488454045</v>
+        <v>0.00382903606876045</v>
       </c>
       <c r="E197" t="n">
-        <v>-0.0352204129635</v>
+        <v>-0.03531171300983793</v>
       </c>
       <c r="F197" t="n">
-        <v>-0.0232258893785</v>
+        <v>-0.02317470366544239</v>
       </c>
     </row>
     <row r="198">
@@ -4377,16 +4377,16 @@
         <v>0.58</v>
       </c>
       <c r="C198" t="n">
-        <v>-0.0120802394505</v>
+        <v>-0.01212733286971899</v>
       </c>
       <c r="D198" t="n">
-        <v>0.0036778300313</v>
+        <v>0.003707007418937807</v>
       </c>
       <c r="E198" t="n">
-        <v>-0.0181795900237</v>
+        <v>-0.01825189841800245</v>
       </c>
       <c r="F198" t="n">
-        <v>-0.00659835153433</v>
+        <v>-0.00653705134694782</v>
       </c>
     </row>
     <row r="199">
@@ -4397,16 +4397,16 @@
         <v>0.6</v>
       </c>
       <c r="C199" t="n">
-        <v>0.00474198442745</v>
+        <v>0.004691041277659469</v>
       </c>
       <c r="D199" t="n">
-        <v>0.00355067494433</v>
+        <v>0.003581197145170006</v>
       </c>
       <c r="E199" t="n">
-        <v>-0.00108130337342</v>
+        <v>-0.001160140740446458</v>
       </c>
       <c r="F199" t="n">
-        <v>0.0100599572287</v>
+        <v>0.01012185612450178</v>
       </c>
     </row>
     <row r="200">
@@ -4417,16 +4417,16 @@
         <v>0.62</v>
       </c>
       <c r="C200" t="n">
-        <v>0.0215932784729</v>
+        <v>0.0215450411122462</v>
       </c>
       <c r="D200" t="n">
-        <v>0.00341942408286</v>
+        <v>0.00344175285059338</v>
       </c>
       <c r="E200" t="n">
-        <v>0.0160498779284</v>
+        <v>0.01598451294897707</v>
       </c>
       <c r="F200" t="n">
-        <v>0.0267339413278</v>
+        <v>0.02678389950540705</v>
       </c>
     </row>
     <row r="201">
@@ -4437,16 +4437,16 @@
         <v>0.64</v>
       </c>
       <c r="C201" t="n">
-        <v>0.0384849804265</v>
+        <v>0.03844422732851491</v>
       </c>
       <c r="D201" t="n">
-        <v>0.00327192404294</v>
+        <v>0.003288926419361534</v>
       </c>
       <c r="E201" t="n">
-        <v>0.0332369012855</v>
+        <v>0.03319040345772528</v>
       </c>
       <c r="F201" t="n">
-        <v>0.0434154418594</v>
+        <v>0.04346519735942866</v>
       </c>
     </row>
     <row r="202">
@@ -4457,16 +4457,16 @@
         <v>0.66</v>
       </c>
       <c r="C202" t="n">
-        <v>0.0554308950371</v>
+        <v>0.05538853473060525</v>
       </c>
       <c r="D202" t="n">
-        <v>0.0031109222016</v>
+        <v>0.003126807537554226</v>
       </c>
       <c r="E202" t="n">
-        <v>0.0505051779749</v>
+        <v>0.05045991555843887</v>
       </c>
       <c r="F202" t="n">
-        <v>0.0601413421252</v>
+        <v>0.06018685676044022</v>
       </c>
     </row>
     <row r="203">
@@ -4477,16 +4477,16 @@
         <v>0.68</v>
       </c>
       <c r="C203" t="n">
-        <v>0.0724197074519</v>
+        <v>0.07237960527941852</v>
       </c>
       <c r="D203" t="n">
-        <v>0.00294755302101</v>
+        <v>0.002965210786212667</v>
       </c>
       <c r="E203" t="n">
-        <v>0.0678219473443</v>
+        <v>0.0677791121943585</v>
       </c>
       <c r="F203" t="n">
-        <v>0.076900184457</v>
+        <v>0.07694788599315494</v>
       </c>
     </row>
     <row r="204">
@@ -4497,16 +4497,16 @@
         <v>0.7</v>
       </c>
       <c r="C204" t="n">
-        <v>0.0894592295615</v>
+        <v>0.08942792337001615</v>
       </c>
       <c r="D204" t="n">
-        <v>0.00278594250991</v>
+        <v>0.00279826804213548</v>
       </c>
       <c r="E204" t="n">
-        <v>0.0851891069048</v>
+        <v>0.08516568434507743</v>
       </c>
       <c r="F204" t="n">
-        <v>0.0936982804849</v>
+        <v>0.09373211172748164</v>
       </c>
     </row>
     <row r="205">
@@ -4517,16 +4517,16 @@
         <v>0.72</v>
       </c>
       <c r="C205" t="n">
-        <v>0.106528718251</v>
+        <v>0.1065042600583142</v>
       </c>
       <c r="D205" t="n">
-        <v>0.00261706693885</v>
+        <v>0.002625723384726042</v>
       </c>
       <c r="E205" t="n">
-        <v>0.102598542518</v>
+        <v>0.1025837289484492</v>
       </c>
       <c r="F205" t="n">
-        <v>0.110535357916</v>
+        <v>0.1105281320121261</v>
       </c>
     </row>
     <row r="206">
@@ -4537,16 +4537,16 @@
         <v>0.74</v>
       </c>
       <c r="C206" t="n">
-        <v>0.123664872789</v>
+        <v>0.1236378370007667</v>
       </c>
       <c r="D206" t="n">
-        <v>0.00244729208975</v>
+        <v>0.002455942443773299</v>
       </c>
       <c r="E206" t="n">
-        <v>0.120051192997</v>
+        <v>0.1200278842465616</v>
       </c>
       <c r="F206" t="n">
-        <v>0.127431776488</v>
+        <v>0.1274104466406945</v>
       </c>
     </row>
     <row r="207">
@@ -4557,16 +4557,16 @@
         <v>0</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.463511053659</v>
+        <v>-0.4637764587965676</v>
       </c>
       <c r="D207" t="n">
-        <v>0.009439276878869999</v>
+        <v>0.009449781158227519</v>
       </c>
       <c r="E207" t="n">
-        <v>-0.479553801112</v>
+        <v>-0.4797377632533593</v>
       </c>
       <c r="F207" t="n">
-        <v>-0.447455567901</v>
+        <v>-0.4476230685640195</v>
       </c>
     </row>
     <row r="208">
@@ -4577,16 +4577,16 @@
         <v>0.02</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.448632059639</v>
+        <v>-0.4488881570102203</v>
       </c>
       <c r="D208" t="n">
-        <v>0.009376543635370001</v>
+        <v>0.009387468826418771</v>
       </c>
       <c r="E208" t="n">
-        <v>-0.464532663835</v>
+        <v>-0.4647076953515761</v>
       </c>
       <c r="F208" t="n">
-        <v>-0.43264842539</v>
+        <v>-0.4328145961229044</v>
       </c>
     </row>
     <row r="209">
@@ -4597,16 +4597,16 @@
         <v>0.04</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.433729753724</v>
+        <v>-0.4339861603560102</v>
       </c>
       <c r="D209" t="n">
-        <v>0.009311069563050001</v>
+        <v>0.009320418860626983</v>
       </c>
       <c r="E209" t="n">
-        <v>-0.449479959866</v>
+        <v>-0.4496502278620369</v>
       </c>
       <c r="F209" t="n">
-        <v>-0.41783471572</v>
+        <v>-0.4180037306528677</v>
       </c>
     </row>
     <row r="210">
@@ -4617,16 +4617,16 @@
         <v>0.06</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.418802501938</v>
+        <v>-0.4190484017356829</v>
       </c>
       <c r="D210" t="n">
-        <v>0.009244201523069999</v>
+        <v>0.009257724906394793</v>
       </c>
       <c r="E210" t="n">
-        <v>-0.434399009669</v>
+        <v>-0.434570888106987</v>
       </c>
       <c r="F210" t="n">
-        <v>-0.402999435442</v>
+        <v>-0.4031495596701733</v>
       </c>
     </row>
     <row r="211">
@@ -4637,16 +4637,16 @@
         <v>0.08</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.403827850549</v>
+        <v>-0.4040567889661882</v>
       </c>
       <c r="D211" t="n">
-        <v>0.009190861899710001</v>
+        <v>0.009209715595386738</v>
       </c>
       <c r="E211" t="n">
-        <v>-0.419306742743</v>
+        <v>-0.4194725262492325</v>
       </c>
       <c r="F211" t="n">
-        <v>-0.388099894435</v>
+        <v>-0.388237774769471</v>
       </c>
     </row>
     <row r="212">
@@ -4657,16 +4657,16 @@
         <v>0.1</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.388787033902</v>
+        <v>-0.3890139736413092</v>
       </c>
       <c r="D212" t="n">
-        <v>0.009130868553950001</v>
+        <v>0.00914806202708222</v>
       </c>
       <c r="E212" t="n">
-        <v>-0.404106292672</v>
+        <v>-0.4042640438665162</v>
       </c>
       <c r="F212" t="n">
-        <v>-0.373152933195</v>
+        <v>-0.3732904702485458</v>
       </c>
     </row>
     <row r="213">
@@ -4677,16 +4677,16 @@
         <v>0.12</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.373692797876</v>
+        <v>-0.3739217340238528</v>
       </c>
       <c r="D213" t="n">
-        <v>0.009044953698659999</v>
+        <v>0.00906209770502365</v>
       </c>
       <c r="E213" t="n">
-        <v>-0.38877999702</v>
+        <v>-0.3889396460338128</v>
       </c>
       <c r="F213" t="n">
-        <v>-0.358178627057</v>
+        <v>-0.3583220547846135</v>
       </c>
     </row>
     <row r="214">
@@ -4697,16 +4697,16 @@
         <v>0.14</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.358562309674</v>
+        <v>-0.3587654549493773</v>
       </c>
       <c r="D214" t="n">
-        <v>0.00895742469637</v>
+        <v>0.0089646532293677</v>
       </c>
       <c r="E214" t="n">
-        <v>-0.373434315411</v>
+        <v>-0.373568853170271</v>
       </c>
       <c r="F214" t="n">
-        <v>-0.343195030609</v>
+        <v>-0.3433397071766153</v>
       </c>
     </row>
     <row r="215">
@@ -4717,16 +4717,16 @@
         <v>0.16</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.343310794485</v>
+        <v>-0.3435028366172919</v>
       </c>
       <c r="D215" t="n">
-        <v>0.0088436252157</v>
+        <v>0.008847819828849066</v>
       </c>
       <c r="E215" t="n">
-        <v>-0.357965325075</v>
+        <v>-0.3580880820179084</v>
       </c>
       <c r="F215" t="n">
-        <v>-0.328156145872</v>
+        <v>-0.3282935106322622</v>
       </c>
     </row>
     <row r="216">
@@ -4737,16 +4737,16 @@
         <v>0.18</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.327989161579</v>
+        <v>-0.3281704718696213</v>
       </c>
       <c r="D216" t="n">
-        <v>0.008720260360380001</v>
+        <v>0.008720429549289192</v>
       </c>
       <c r="E216" t="n">
-        <v>-0.342398408117</v>
+        <v>-0.3424956675588939</v>
       </c>
       <c r="F216" t="n">
-        <v>-0.313052433842</v>
+        <v>-0.3131845445912838</v>
       </c>
     </row>
     <row r="217">
@@ -4757,16 +4757,16 @@
         <v>0.2</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.312581700091</v>
+        <v>-0.3127534984704172</v>
       </c>
       <c r="D217" t="n">
-        <v>0.00856145106666</v>
+        <v>0.008563911946435293</v>
       </c>
       <c r="E217" t="n">
-        <v>-0.326664647975</v>
+        <v>-0.3267585189325954</v>
       </c>
       <c r="F217" t="n">
-        <v>-0.297916469486</v>
+        <v>-0.2980380896717474</v>
       </c>
     </row>
     <row r="218">
@@ -4777,16 +4777,16 @@
         <v>0.22</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.297088974749</v>
+        <v>-0.2972497517397169</v>
       </c>
       <c r="D218" t="n">
-        <v>0.00840298743136</v>
+        <v>0.008405899678020964</v>
       </c>
       <c r="E218" t="n">
-        <v>-0.310859073905</v>
+        <v>-0.3109536573975813</v>
       </c>
       <c r="F218" t="n">
-        <v>-0.282700985923</v>
+        <v>-0.2828097043852598</v>
       </c>
     </row>
     <row r="219">
@@ -4797,16 +4797,16 @@
         <v>0.24</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.28153017976</v>
+        <v>-0.2816700659168507</v>
       </c>
       <c r="D219" t="n">
-        <v>0.0082435641503</v>
+        <v>0.008248479457458654</v>
       </c>
       <c r="E219" t="n">
-        <v>-0.295006318904</v>
+        <v>-0.2951037836644961</v>
       </c>
       <c r="F219" t="n">
-        <v>-0.267419085786</v>
+        <v>-0.2675166487450902</v>
       </c>
     </row>
     <row r="220">
@@ -4817,16 +4817,16 @@
         <v>0.26</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.265891623104</v>
+        <v>-0.2660109429249431</v>
       </c>
       <c r="D220" t="n">
-        <v>0.00808988592108</v>
+        <v>0.008097303858879523</v>
       </c>
       <c r="E220" t="n">
-        <v>-0.279125900986</v>
+        <v>-0.2792104151359247</v>
       </c>
       <c r="F220" t="n">
-        <v>-0.252077030376</v>
+        <v>-0.2521434305969725</v>
       </c>
     </row>
     <row r="221">
@@ -4837,16 +4837,16 @@
         <v>0.28</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.25020088593</v>
+        <v>-0.2503094510095901</v>
       </c>
       <c r="D221" t="n">
-        <v>0.007936763952819999</v>
+        <v>0.007939775912622125</v>
       </c>
       <c r="E221" t="n">
-        <v>-0.263201879073</v>
+        <v>-0.2632716708360148</v>
       </c>
       <c r="F221" t="n">
-        <v>-0.236663789591</v>
+        <v>-0.2367181190143484</v>
       </c>
     </row>
     <row r="222">
@@ -4857,16 +4857,16 @@
         <v>0.3</v>
       </c>
       <c r="C222" t="n">
-        <v>-0.234448330576</v>
+        <v>-0.2345562187210816</v>
       </c>
       <c r="D222" t="n">
-        <v>0.00776799143659</v>
+        <v>0.007768061065335483</v>
       </c>
       <c r="E222" t="n">
-        <v>-0.247176031368</v>
+        <v>-0.2472364779605369</v>
       </c>
       <c r="F222" t="n">
-        <v>-0.221193476733</v>
+        <v>-0.2212490614517479</v>
       </c>
     </row>
     <row r="223">
@@ -4877,16 +4877,16 @@
         <v>0.32</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.218665090347</v>
+        <v>-0.2187783971630695</v>
       </c>
       <c r="D223" t="n">
-        <v>0.00759132869664</v>
+        <v>0.007592523109408764</v>
       </c>
       <c r="E223" t="n">
-        <v>-0.231095111515</v>
+        <v>-0.2311641276134875</v>
       </c>
       <c r="F223" t="n">
-        <v>-0.205703029832</v>
+        <v>-0.2057654285698556</v>
       </c>
     </row>
     <row r="224">
@@ -4897,16 +4897,16 @@
         <v>0.34</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.202867701805</v>
+        <v>-0.2029872833786503</v>
       </c>
       <c r="D224" t="n">
-        <v>0.00741934113225</v>
+        <v>0.007423113650265136</v>
       </c>
       <c r="E224" t="n">
-        <v>-0.215001855778</v>
+        <v>-0.215079727663241</v>
       </c>
       <c r="F224" t="n">
-        <v>-0.190200898842</v>
+        <v>-0.1902661462514086</v>
       </c>
     </row>
     <row r="225">
@@ -4917,16 +4917,16 @@
         <v>0.36</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.187051102159</v>
+        <v>-0.1871611119239799</v>
       </c>
       <c r="D225" t="n">
-        <v>0.00725490322059</v>
+        <v>0.007269128895446496</v>
       </c>
       <c r="E225" t="n">
-        <v>-0.198907236105</v>
+        <v>-0.1989891419611913</v>
       </c>
       <c r="F225" t="n">
-        <v>-0.174694603166</v>
+        <v>-0.1747432479318585</v>
       </c>
     </row>
     <row r="226">
@@ -4937,16 +4937,16 @@
         <v>0.38</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.171182205527</v>
+        <v>-0.1712910608734498</v>
       </c>
       <c r="D226" t="n">
-        <v>0.00711643074864</v>
+        <v>0.007129672471698358</v>
       </c>
       <c r="E226" t="n">
-        <v>-0.182787666375</v>
+        <v>-0.1828757857979921</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.159119293922</v>
+        <v>-0.1591722950428558</v>
       </c>
     </row>
     <row r="227">
@@ -4957,16 +4957,16 @@
         <v>0.4</v>
       </c>
       <c r="C227" t="n">
-        <v>-0.155236921919</v>
+        <v>-0.1553319143677355</v>
       </c>
       <c r="D227" t="n">
-        <v>0.00695907902464</v>
+        <v>0.006971978989995065</v>
       </c>
       <c r="E227" t="n">
-        <v>-0.166642213666</v>
+        <v>-0.1667243879627769</v>
       </c>
       <c r="F227" t="n">
-        <v>-0.143527801026</v>
+        <v>-0.1435722849438426</v>
       </c>
     </row>
     <row r="228">
@@ -4977,16 +4977,16 @@
         <v>0.42</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.139192883565</v>
+        <v>-0.1392881196140457</v>
       </c>
       <c r="D228" t="n">
-        <v>0.0067841020153</v>
+        <v>0.006792795284098084</v>
       </c>
       <c r="E228" t="n">
-        <v>-0.150362249309</v>
+        <v>-0.1504299771300426</v>
       </c>
       <c r="F228" t="n">
-        <v>-0.127856531103</v>
+        <v>-0.1279116957811155</v>
       </c>
     </row>
     <row r="229">
@@ -4997,16 +4997,16 @@
         <v>0.44</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.123087144729</v>
+        <v>-0.123181490488697</v>
       </c>
       <c r="D229" t="n">
-        <v>0.00657442032417</v>
+        <v>0.00658300594623837</v>
       </c>
       <c r="E229" t="n">
-        <v>-0.133928212924</v>
+        <v>-0.1339876244457807</v>
       </c>
       <c r="F229" t="n">
-        <v>-0.112161912185</v>
+        <v>-0.1122158006170997</v>
       </c>
     </row>
     <row r="230">
@@ -5017,16 +5017,16 @@
         <v>0.46</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.106932012031</v>
+        <v>-0.1070391489883407</v>
       </c>
       <c r="D230" t="n">
-        <v>0.00637402203265</v>
+        <v>0.006381549852969398</v>
       </c>
       <c r="E230" t="n">
-        <v>-0.117432350673</v>
+        <v>-0.1175010697502428</v>
       </c>
       <c r="F230" t="n">
-        <v>-0.0963861121324</v>
+        <v>-0.09645924814970641</v>
       </c>
     </row>
     <row r="231">
@@ -5037,16 +5037,16 @@
         <v>0.48</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.0907327204267</v>
+        <v>-0.09082106151641627</v>
       </c>
       <c r="D231" t="n">
-        <v>0.00618698864771</v>
+        <v>0.006209934894581841</v>
       </c>
       <c r="E231" t="n">
-        <v>-0.10090620286</v>
+        <v>-0.1009866045896999</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.0805490943919</v>
+        <v>-0.08059393147260252</v>
       </c>
     </row>
     <row r="232">
@@ -5057,16 +5057,16 @@
         <v>0.5</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.07445590929779999</v>
+        <v>-0.07453789615766597</v>
       </c>
       <c r="D232" t="n">
-        <v>0.006020702032</v>
+        <v>0.006048919641803431</v>
       </c>
       <c r="E232" t="n">
-        <v>-0.0843225696277</v>
+        <v>-0.08437689036276907</v>
       </c>
       <c r="F232" t="n">
-        <v>-0.0646286950244</v>
+        <v>-0.06464666988873358</v>
       </c>
     </row>
     <row r="233">
@@ -5077,16 +5077,16 @@
         <v>0.52</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.0581196857549</v>
+        <v>-0.05819084809051756</v>
       </c>
       <c r="D233" t="n">
-        <v>0.00587025288192</v>
+        <v>0.005903240049198921</v>
       </c>
       <c r="E233" t="n">
-        <v>-0.0676563329295</v>
+        <v>-0.06771323807929619</v>
       </c>
       <c r="F233" t="n">
-        <v>-0.0486069849166</v>
+        <v>-0.0486033504189054</v>
       </c>
     </row>
     <row r="234">
@@ -5097,16 +5097,16 @@
         <v>0.54</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.0417280996496</v>
+        <v>-0.04179010980831351</v>
       </c>
       <c r="D234" t="n">
-        <v>0.00572008738249</v>
+        <v>0.005756603225950573</v>
       </c>
       <c r="E234" t="n">
-        <v>-0.0509402323019</v>
+        <v>-0.0509944380773053</v>
       </c>
       <c r="F234" t="n">
-        <v>-0.0325269076473</v>
+        <v>-0.03249898902113912</v>
       </c>
     </row>
     <row r="235">
@@ -5117,16 +5117,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.0252665517172</v>
+        <v>-0.0253262345241545</v>
       </c>
       <c r="D235" t="n">
-        <v>0.00556657709202</v>
+        <v>0.005598260637955044</v>
       </c>
       <c r="E235" t="n">
-        <v>-0.0341506734336</v>
+        <v>-0.034192948228009</v>
       </c>
       <c r="F235" t="n">
-        <v>-0.0163431739922</v>
+        <v>-0.01631681468310209</v>
       </c>
     </row>
     <row r="236">
@@ -5137,16 +5137,16 @@
         <v>0.58</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.008752881377099999</v>
+        <v>-0.00881936131035257</v>
       </c>
       <c r="D236" t="n">
-        <v>0.00539779311162</v>
+        <v>0.005430552933557676</v>
       </c>
       <c r="E236" t="n">
-        <v>-0.0173107278357</v>
+        <v>-0.01736651583490456</v>
       </c>
       <c r="F236" t="n">
-        <v>-0.000139410410442</v>
+        <v>-0.0001250242085868436</v>
       </c>
     </row>
     <row r="237">
@@ -5157,16 +5157,16 @@
         <v>0.6</v>
       </c>
       <c r="C237" t="n">
-        <v>0.00781608106032</v>
+        <v>0.007755290458387609</v>
       </c>
       <c r="D237" t="n">
-        <v>0.00521893767449</v>
+        <v>0.005244744578925422</v>
       </c>
       <c r="E237" t="n">
-        <v>-0.000415308193415</v>
+        <v>-0.0004739190602291998</v>
       </c>
       <c r="F237" t="n">
-        <v>0.0160916220728</v>
+        <v>0.01610057771680662</v>
       </c>
     </row>
     <row r="238">
@@ -5177,16 +5177,16 @@
         <v>0.62</v>
       </c>
       <c r="C238" t="n">
-        <v>0.024428984246</v>
+        <v>0.02436274584872482</v>
       </c>
       <c r="D238" t="n">
-        <v>0.00503006618665</v>
+        <v>0.005055591023061928</v>
       </c>
       <c r="E238" t="n">
-        <v>0.0165058680639</v>
+        <v>0.01644445285694118</v>
       </c>
       <c r="F238" t="n">
-        <v>0.0323552820192</v>
+        <v>0.03235819645313409</v>
       </c>
     </row>
     <row r="239">
@@ -5197,16 +5197,16 @@
         <v>0.64</v>
       </c>
       <c r="C239" t="n">
-        <v>0.0410718815018</v>
+        <v>0.04100152730835989</v>
       </c>
       <c r="D239" t="n">
-        <v>0.0048407079198</v>
+        <v>0.004864387937044122</v>
       </c>
       <c r="E239" t="n">
-        <v>0.0334722916668</v>
+        <v>0.03340792590924213</v>
       </c>
       <c r="F239" t="n">
-        <v>0.0486518119871</v>
+        <v>0.04863912689331507</v>
       </c>
     </row>
     <row r="240">
@@ -5217,16 +5217,16 @@
         <v>0.66</v>
       </c>
       <c r="C240" t="n">
-        <v>0.0577661622335</v>
+        <v>0.05771162770246434</v>
       </c>
       <c r="D240" t="n">
-        <v>0.00463772539911</v>
+        <v>0.004651826644024015</v>
       </c>
       <c r="E240" t="n">
-        <v>0.0505070967961</v>
+        <v>0.05047934153765432</v>
       </c>
       <c r="F240" t="n">
-        <v>0.0649667037721</v>
+        <v>0.06495053172574039</v>
       </c>
     </row>
     <row r="241">
@@ -5237,16 +5237,16 @@
         <v>0.68</v>
       </c>
       <c r="C241" t="n">
-        <v>0.07452734016610001</v>
+        <v>0.07446978044799453</v>
       </c>
       <c r="D241" t="n">
-        <v>0.00441413979489</v>
+        <v>0.004428268442093323</v>
       </c>
       <c r="E241" t="n">
-        <v>0.067663921175</v>
+        <v>0.06763050121393288</v>
       </c>
       <c r="F241" t="n">
-        <v>0.0813239347087</v>
+        <v>0.08130323273118023</v>
       </c>
     </row>
     <row r="242">
@@ -5257,16 +5257,16 @@
         <v>0.7</v>
       </c>
       <c r="C242" t="n">
-        <v>0.09133068901249999</v>
+        <v>0.09127375040465457</v>
       </c>
       <c r="D242" t="n">
-        <v>0.00418114521309</v>
+        <v>0.004185302476932061</v>
       </c>
       <c r="E242" t="n">
-        <v>0.08488110163900001</v>
+        <v>0.08486128523290937</v>
       </c>
       <c r="F242" t="n">
-        <v>0.0977511251781</v>
+        <v>0.09771432632319588</v>
       </c>
     </row>
     <row r="243">
@@ -5277,16 +5277,16 @@
         <v>0.72</v>
       </c>
       <c r="C243" t="n">
-        <v>0.108188541632</v>
+        <v>0.1081360936630584</v>
       </c>
       <c r="D243" t="n">
-        <v>0.00393109492892</v>
+        <v>0.00393574837920735</v>
       </c>
       <c r="E243" t="n">
-        <v>0.102161136531</v>
+        <v>0.1021401006105229</v>
       </c>
       <c r="F243" t="n">
-        <v>0.114226763342</v>
+        <v>0.1141981019803771</v>
       </c>
     </row>
     <row r="244">
@@ -5297,16 +5297,16 @@
         <v>0.74</v>
       </c>
       <c r="C244" t="n">
-        <v>0.125107510683</v>
+        <v>0.1250529693552026</v>
       </c>
       <c r="D244" t="n">
-        <v>0.00367937340658</v>
+        <v>0.003684876714335808</v>
       </c>
       <c r="E244" t="n">
-        <v>0.119477724646</v>
+        <v>0.1194492414944621</v>
       </c>
       <c r="F244" t="n">
-        <v>0.130741993466</v>
+        <v>0.1307095817982047</v>
       </c>
     </row>
     <row r="245">
@@ -5317,16 +5317,16 @@
         <v>0.76</v>
       </c>
       <c r="C245" t="n">
-        <v>0.142085065419</v>
+        <v>0.1420413993128074</v>
       </c>
       <c r="D245" t="n">
-        <v>0.00342530987924</v>
+        <v>0.00342240594134671</v>
       </c>
       <c r="E245" t="n">
-        <v>0.136835947421</v>
+        <v>0.136823522257858</v>
       </c>
       <c r="F245" t="n">
-        <v>0.147298723866</v>
+        <v>0.1472575307233059</v>
       </c>
     </row>
     <row r="246">
@@ -5337,16 +5337,16 @@
         <v>0.78</v>
       </c>
       <c r="C246" t="n">
-        <v>0.159112763595</v>
+        <v>0.1590724367664419</v>
       </c>
       <c r="D246" t="n">
-        <v>0.00315799746367</v>
+        <v>0.003155043723895695</v>
       </c>
       <c r="E246" t="n">
-        <v>0.154265765485</v>
+        <v>0.1542583374594866</v>
       </c>
       <c r="F246" t="n">
-        <v>0.163889215921</v>
+        <v>0.1638616802868222</v>
       </c>
     </row>
     <row r="247">
@@ -5357,16 +5357,16 @@
         <v>0</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.442163964755</v>
+        <v>-0.4423799253760275</v>
       </c>
       <c r="D247" t="n">
-        <v>0.0135933650158</v>
+        <v>0.01359836119234155</v>
       </c>
       <c r="E247" t="n">
-        <v>-0.472847493247</v>
+        <v>-0.4730436239382252</v>
       </c>
       <c r="F247" t="n">
-        <v>-0.423789450861</v>
+        <v>-0.4239242370534129</v>
       </c>
     </row>
     <row r="248">
@@ -5377,16 +5377,16 @@
         <v>0.02</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.428070891304</v>
+        <v>-0.4282805162085568</v>
       </c>
       <c r="D248" t="n">
-        <v>0.0134552210206</v>
+        <v>0.01345403137931164</v>
       </c>
       <c r="E248" t="n">
-        <v>-0.458481798139</v>
+        <v>-0.4586539545435748</v>
       </c>
       <c r="F248" t="n">
-        <v>-0.409879509224</v>
+        <v>-0.4100203507637428</v>
       </c>
     </row>
     <row r="249">
@@ -5397,16 +5397,16 @@
         <v>0.04</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.41391232988</v>
+        <v>-0.4141184537545373</v>
       </c>
       <c r="D249" t="n">
-        <v>0.0132879418115</v>
+        <v>0.01328899640389997</v>
       </c>
       <c r="E249" t="n">
-        <v>-0.443959421572</v>
+        <v>-0.4441353082337898</v>
       </c>
       <c r="F249" t="n">
-        <v>-0.39593112351</v>
+        <v>-0.3960805972254251</v>
       </c>
     </row>
     <row r="250">
@@ -5417,16 +5417,16 @@
         <v>0.06</v>
       </c>
       <c r="C250" t="n">
-        <v>-0.399678512865</v>
+        <v>-0.3998842144723899</v>
       </c>
       <c r="D250" t="n">
-        <v>0.0131258119246</v>
+        <v>0.01312819043829387</v>
       </c>
       <c r="E250" t="n">
-        <v>-0.429412962713</v>
+        <v>-0.4295938756018947</v>
       </c>
       <c r="F250" t="n">
-        <v>-0.381958249965</v>
+        <v>-0.3821125829489809</v>
       </c>
     </row>
     <row r="251">
@@ -5437,16 +5437,16 @@
         <v>0.08</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.385420146551</v>
+        <v>-0.3856290568052547</v>
       </c>
       <c r="D251" t="n">
-        <v>0.0129657902513</v>
+        <v>0.01296975260564712</v>
       </c>
       <c r="E251" t="n">
-        <v>-0.414855134928</v>
+        <v>-0.4150428864898643</v>
       </c>
       <c r="F251" t="n">
-        <v>-0.367980177689</v>
+        <v>-0.3681373422365928</v>
       </c>
     </row>
     <row r="252">
@@ -5457,16 +5457,16 @@
         <v>0.1</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.37112555789</v>
+        <v>-0.3713271778516429</v>
       </c>
       <c r="D252" t="n">
-        <v>0.0128023935099</v>
+        <v>0.01280902644621922</v>
       </c>
       <c r="E252" t="n">
-        <v>-0.400244884214</v>
+        <v>-0.4004280047445112</v>
       </c>
       <c r="F252" t="n">
-        <v>-0.353976564411</v>
+        <v>-0.3541260847989101</v>
       </c>
     </row>
     <row r="253">
@@ -5477,16 +5477,16 @@
         <v>0.12</v>
       </c>
       <c r="C253" t="n">
-        <v>-0.356771156979</v>
+        <v>-0.3569670870138545</v>
       </c>
       <c r="D253" t="n">
-        <v>0.0126522872519</v>
+        <v>0.01266264473851867</v>
       </c>
       <c r="E253" t="n">
-        <v>-0.385596469502</v>
+        <v>-0.38578002269987</v>
       </c>
       <c r="F253" t="n">
-        <v>-0.33988847693</v>
+        <v>-0.3400245692686283</v>
       </c>
     </row>
     <row r="254">
@@ -5497,16 +5497,16 @@
         <v>0.14</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.342345554641</v>
+        <v>-0.3425343990395958</v>
       </c>
       <c r="D254" t="n">
-        <v>0.0125051971839</v>
+        <v>0.01251375390110003</v>
       </c>
       <c r="E254" t="n">
-        <v>-0.370859916083</v>
+        <v>-0.3710300249414544</v>
       </c>
       <c r="F254" t="n">
-        <v>-0.325687752903</v>
+        <v>-0.3258246191606347</v>
       </c>
     </row>
     <row r="255">
@@ -5517,16 +5517,16 @@
         <v>0.16</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.32779354266</v>
+        <v>-0.3279753732114019</v>
       </c>
       <c r="D255" t="n">
-        <v>0.0123542713708</v>
+        <v>0.01236398016431908</v>
       </c>
       <c r="E255" t="n">
-        <v>-0.356023743976</v>
+        <v>-0.3561967814472107</v>
       </c>
       <c r="F255" t="n">
-        <v>-0.311376868073</v>
+        <v>-0.3115048477739357</v>
       </c>
     </row>
     <row r="256">
@@ -5537,16 +5537,16 @@
         <v>0.18</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.313103020201</v>
+        <v>-0.3132733213389364</v>
       </c>
       <c r="D256" t="n">
-        <v>0.012220264717</v>
+        <v>0.0122305404530198</v>
       </c>
       <c r="E256" t="n">
-        <v>-0.341121000971</v>
+        <v>-0.3412820060983339</v>
       </c>
       <c r="F256" t="n">
-        <v>-0.296864824277</v>
+        <v>-0.2969688157156662</v>
       </c>
     </row>
     <row r="257">
@@ -5557,16 +5557,16 @@
         <v>0.2</v>
       </c>
       <c r="C257" t="n">
-        <v>-0.298365933456</v>
+        <v>-0.2985351523899382</v>
       </c>
       <c r="D257" t="n">
-        <v>0.0120967891762</v>
+        <v>0.01210707798291995</v>
       </c>
       <c r="E257" t="n">
-        <v>-0.326187744975</v>
+        <v>-0.3263500068777638</v>
       </c>
       <c r="F257" t="n">
-        <v>-0.282285102965</v>
+        <v>-0.2823914965611518</v>
       </c>
     </row>
     <row r="258">
@@ -5577,16 +5577,16 @@
         <v>0.22</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.283588383061</v>
+        <v>-0.2837609249536803</v>
       </c>
       <c r="D258" t="n">
-        <v>0.0119661041236</v>
+        <v>0.01197293109030087</v>
       </c>
       <c r="E258" t="n">
-        <v>-0.311206791939</v>
+        <v>-0.3113662817235632</v>
       </c>
       <c r="F258" t="n">
-        <v>-0.267673239194</v>
+        <v>-0.2677879211905863</v>
       </c>
     </row>
     <row r="259">
@@ -5597,16 +5597,16 @@
         <v>0.24</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.268760738867</v>
+        <v>-0.268935625385364</v>
       </c>
       <c r="D259" t="n">
-        <v>0.0118102239072</v>
+        <v>0.01181662249520287</v>
       </c>
       <c r="E259" t="n">
-        <v>-0.296091144484</v>
+        <v>-0.2962525683312531</v>
       </c>
       <c r="F259" t="n">
-        <v>-0.253018541664</v>
+        <v>-0.2531398004372916</v>
       </c>
     </row>
     <row r="260">
@@ -5617,16 +5617,16 @@
         <v>0.26</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.253904971244</v>
+        <v>-0.254070284987411</v>
       </c>
       <c r="D260" t="n">
-        <v>0.0116559730861</v>
+        <v>0.01166399378286204</v>
       </c>
       <c r="E260" t="n">
-        <v>-0.280942400581</v>
+        <v>-0.2810892324343826</v>
       </c>
       <c r="F260" t="n">
-        <v>-0.238335084527</v>
+        <v>-0.2384428289183402</v>
       </c>
     </row>
     <row r="261">
@@ -5637,16 +5637,16 @@
         <v>0.28</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.239007647449</v>
+        <v>-0.2391748090561046</v>
       </c>
       <c r="D261" t="n">
-        <v>0.0114997733466</v>
+        <v>0.0115056476630748</v>
       </c>
       <c r="E261" t="n">
-        <v>-0.265729077538</v>
+        <v>-0.2658702970366562</v>
       </c>
       <c r="F261" t="n">
-        <v>-0.223624132829</v>
+        <v>-0.2237374180142533</v>
       </c>
     </row>
     <row r="262">
@@ -5657,16 +5657,16 @@
         <v>0.3</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.224075744042</v>
+        <v>-0.2242330432077201</v>
       </c>
       <c r="D262" t="n">
-        <v>0.0113427897719</v>
+        <v>0.01135428082497553</v>
       </c>
       <c r="E262" t="n">
-        <v>-0.250469077937</v>
+        <v>-0.2506140999972004</v>
       </c>
       <c r="F262" t="n">
-        <v>-0.208870567918</v>
+        <v>-0.2089601119691391</v>
       </c>
     </row>
     <row r="263">
@@ -5677,16 +5677,16 @@
         <v>0.32</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.209067862486</v>
+        <v>-0.2092142837633935</v>
       </c>
       <c r="D263" t="n">
-        <v>0.0111980238052</v>
+        <v>0.01120862641687003</v>
       </c>
       <c r="E263" t="n">
-        <v>-0.235154194007</v>
+        <v>-0.2352837636672911</v>
       </c>
       <c r="F263" t="n">
-        <v>-0.19401360532</v>
+        <v>-0.1941003625045088</v>
       </c>
     </row>
     <row r="264">
@@ -5697,16 +5697,16 @@
         <v>0.34</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.193981858984</v>
+        <v>-0.1941331205173173</v>
       </c>
       <c r="D264" t="n">
-        <v>0.0110053501487</v>
+        <v>0.01101614378779983</v>
       </c>
       <c r="E264" t="n">
-        <v>-0.219571257558</v>
+        <v>-0.2197038661097768</v>
       </c>
       <c r="F264" t="n">
-        <v>-0.179121314632</v>
+        <v>-0.1792164983058457</v>
       </c>
     </row>
     <row r="265">
@@ -5717,16 +5717,16 @@
         <v>0.36</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.178847096849</v>
+        <v>-0.1789887828500246</v>
       </c>
       <c r="D265" t="n">
-        <v>0.0108075781528</v>
+        <v>0.01081273032613771</v>
       </c>
       <c r="E265" t="n">
-        <v>-0.203939610736</v>
+        <v>-0.2040634110125188</v>
       </c>
       <c r="F265" t="n">
-        <v>-0.164226853787</v>
+        <v>-0.1643308126088057</v>
       </c>
     </row>
     <row r="266">
@@ -5737,16 +5737,16 @@
         <v>0.38</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.163600751847</v>
+        <v>-0.1637267889904699</v>
       </c>
       <c r="D266" t="n">
-        <v>0.0105830329714</v>
+        <v>0.01058272423566924</v>
       </c>
       <c r="E266" t="n">
-        <v>-0.188171034624</v>
+        <v>-0.1882646072050642</v>
       </c>
       <c r="F266" t="n">
-        <v>-0.149299258362</v>
+        <v>-0.1493928395370174</v>
       </c>
     </row>
     <row r="267">
@@ -5757,16 +5757,16 @@
         <v>0.4</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.148222225818</v>
+        <v>-0.1483426806784976</v>
       </c>
       <c r="D267" t="n">
-        <v>0.0103149367563</v>
+        <v>0.01031469627403563</v>
       </c>
       <c r="E267" t="n">
-        <v>-0.172153543521</v>
+        <v>-0.172242748888074</v>
       </c>
       <c r="F267" t="n">
-        <v>-0.134297634334</v>
+        <v>-0.134386550071266</v>
       </c>
     </row>
     <row r="268">
@@ -5777,16 +5777,16 @@
         <v>0.42</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.132717850679</v>
+        <v>-0.1328338888456532</v>
       </c>
       <c r="D268" t="n">
-        <v>0.0100351323715</v>
+        <v>0.01003472544723181</v>
       </c>
       <c r="E268" t="n">
-        <v>-0.155980552617</v>
+        <v>-0.1560748788467547</v>
       </c>
       <c r="F268" t="n">
-        <v>-0.11918148233</v>
+        <v>-0.1192649920522664</v>
       </c>
     </row>
     <row r="269">
@@ -5797,16 +5797,16 @@
         <v>0.44</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.117121758683</v>
+        <v>-0.1172094655167922</v>
       </c>
       <c r="D269" t="n">
-        <v>0.009758675875610001</v>
+        <v>0.009761818582802374</v>
       </c>
       <c r="E269" t="n">
-        <v>-0.139749469172</v>
+        <v>-0.1398339818810976</v>
       </c>
       <c r="F269" t="n">
-        <v>-0.103969671866</v>
+        <v>-0.1040262223753787</v>
       </c>
     </row>
     <row r="270">
@@ -5817,16 +5817,16 @@
         <v>0.46</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.101430339089</v>
+        <v>-0.101505456543832</v>
       </c>
       <c r="D270" t="n">
-        <v>0.0094877601976</v>
+        <v>0.009485391110667448</v>
       </c>
       <c r="E270" t="n">
-        <v>-0.123448116372</v>
+        <v>-0.1235119684308978</v>
       </c>
       <c r="F270" t="n">
-        <v>-0.0886623333338</v>
+        <v>-0.08870185212708925</v>
       </c>
     </row>
     <row r="271">
@@ -5837,16 +5837,16 @@
         <v>0.48</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.0856529000098</v>
+        <v>-0.08572952082991572</v>
       </c>
       <c r="D271" t="n">
-        <v>0.009190775734399999</v>
+        <v>0.009186228418877741</v>
       </c>
       <c r="E271" t="n">
-        <v>-0.106986700217</v>
+        <v>-0.1070467274666829</v>
       </c>
       <c r="F271" t="n">
-        <v>-0.07326359840339999</v>
+        <v>-0.07330717142860799</v>
       </c>
     </row>
     <row r="272">
@@ -5857,16 +5857,16 @@
         <v>0.5</v>
       </c>
       <c r="C272" t="n">
-        <v>-0.06984126424709999</v>
+        <v>-0.06992523921570921</v>
       </c>
       <c r="D272" t="n">
-        <v>0.00889026791269</v>
+        <v>0.008888363802690367</v>
       </c>
       <c r="E272" t="n">
-        <v>-0.0904712131343</v>
+        <v>-0.09054397708412498</v>
       </c>
       <c r="F272" t="n">
-        <v>-0.0578400699811</v>
+        <v>-0.0578874938489955</v>
       </c>
     </row>
     <row r="273">
@@ -5877,16 +5877,16 @@
         <v>0.52</v>
       </c>
       <c r="C273" t="n">
-        <v>-0.0540108289428</v>
+        <v>-0.05409418950457016</v>
       </c>
       <c r="D273" t="n">
-        <v>0.00859894384299</v>
+        <v>0.008603173656292979</v>
       </c>
       <c r="E273" t="n">
-        <v>-0.0739474430337</v>
+        <v>-0.07402645016241483</v>
       </c>
       <c r="F273" t="n">
-        <v>-0.0424005185838</v>
+        <v>-0.0424335011986452</v>
       </c>
     </row>
     <row r="274">
@@ -5897,16 +5897,16 @@
         <v>0.54</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.0381185571317</v>
+        <v>-0.03819714492050474</v>
       </c>
       <c r="D274" t="n">
-        <v>0.0083310094723</v>
+        <v>0.008337304251192825</v>
       </c>
       <c r="E274" t="n">
-        <v>-0.0573865534495</v>
+        <v>-0.05747315770733596</v>
       </c>
       <c r="F274" t="n">
-        <v>-0.0268656692405</v>
+        <v>-0.02690270679804563</v>
       </c>
     </row>
     <row r="275">
@@ -5917,16 +5917,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.0220989053767</v>
+        <v>-0.02217027529500193</v>
       </c>
       <c r="D275" t="n">
-        <v>0.008059854633019999</v>
+        <v>0.008066375118734632</v>
       </c>
       <c r="E275" t="n">
-        <v>-0.0407338674422</v>
+        <v>-0.040810589282545</v>
       </c>
       <c r="F275" t="n">
-        <v>-0.01125542194</v>
+        <v>-0.01128827039781122</v>
       </c>
     </row>
     <row r="276">
@@ -5937,16 +5937,16 @@
         <v>0.58</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.00595556314644</v>
+        <v>-0.006027934273510649</v>
       </c>
       <c r="D276" t="n">
-        <v>0.00772642431644</v>
+        <v>0.007729592512183176</v>
       </c>
       <c r="E276" t="n">
-        <v>-0.02382411975</v>
+        <v>-0.02389306426647053</v>
       </c>
       <c r="F276" t="n">
-        <v>0.00441397042557</v>
+        <v>0.004369581540820455</v>
       </c>
     </row>
     <row r="277">
@@ -5957,16 +5957,16 @@
         <v>0.6</v>
       </c>
       <c r="C277" t="n">
-        <v>0.0102392493449</v>
+        <v>0.01016061939738284</v>
       </c>
       <c r="D277" t="n">
-        <v>0.00740014164445</v>
+        <v>0.007406810067448005</v>
       </c>
       <c r="E277" t="n">
-        <v>-0.00686155676905</v>
+        <v>-0.006943169279920447</v>
       </c>
       <c r="F277" t="n">
-        <v>0.0201353880748</v>
+        <v>0.02009229596400974</v>
       </c>
     </row>
     <row r="278">
@@ -5977,16 +5977,16 @@
         <v>0.62</v>
       </c>
       <c r="C278" t="n">
-        <v>0.0265322732699</v>
+        <v>0.02646580177683582</v>
       </c>
       <c r="D278" t="n">
-        <v>0.00709112062737</v>
+        <v>0.007105788840939041</v>
       </c>
       <c r="E278" t="n">
-        <v>0.010175814407</v>
+        <v>0.01009284161538737</v>
       </c>
       <c r="F278" t="n">
-        <v>0.0359917652052</v>
+        <v>0.03596530747192173</v>
       </c>
     </row>
     <row r="279">
@@ -5997,16 +5997,16 @@
         <v>0.64</v>
       </c>
       <c r="C279" t="n">
-        <v>0.0429105588651</v>
+        <v>0.04285077386874425</v>
       </c>
       <c r="D279" t="n">
-        <v>0.00679440782107</v>
+        <v>0.006808906350287729</v>
       </c>
       <c r="E279" t="n">
-        <v>0.0273066998467</v>
+        <v>0.02723943295406084</v>
       </c>
       <c r="F279" t="n">
-        <v>0.0519407161832</v>
+        <v>0.05193661353631285</v>
       </c>
     </row>
     <row r="280">
@@ -6017,16 +6017,16 @@
         <v>0.66</v>
       </c>
       <c r="C280" t="n">
-        <v>0.059365634689</v>
+        <v>0.05931511635129265</v>
       </c>
       <c r="D280" t="n">
-        <v>0.00649804605459</v>
+        <v>0.006509918097563587</v>
       </c>
       <c r="E280" t="n">
-        <v>0.0445100552994</v>
+        <v>0.04445593996250086</v>
       </c>
       <c r="F280" t="n">
-        <v>0.0679922017218</v>
+        <v>0.0679895115671334</v>
       </c>
     </row>
     <row r="281">
@@ -6037,16 +6037,16 @@
         <v>0.68</v>
       </c>
       <c r="C281" t="n">
-        <v>0.07590564636619999</v>
+        <v>0.07585081791543224</v>
       </c>
       <c r="D281" t="n">
-        <v>0.00619336607445</v>
+        <v>0.006201730623054945</v>
       </c>
       <c r="E281" t="n">
-        <v>0.061791689801</v>
+        <v>0.06174283615749321</v>
       </c>
       <c r="F281" t="n">
-        <v>0.0841035789789</v>
+        <v>0.08408767968396624</v>
       </c>
     </row>
     <row r="282">
@@ -6057,16 +6057,16 @@
         <v>0.7</v>
       </c>
       <c r="C282" t="n">
-        <v>0.0925169008077</v>
+        <v>0.0924635556107762</v>
       </c>
       <c r="D282" t="n">
-        <v>0.00587559902212</v>
+        <v>0.005885572821006052</v>
       </c>
       <c r="E282" t="n">
-        <v>0.0791817132341</v>
+        <v>0.07911498192292843</v>
       </c>
       <c r="F282" t="n">
-        <v>0.100246027795</v>
+        <v>0.1002232957454963</v>
       </c>
     </row>
     <row r="283">
@@ -6077,16 +6077,16 @@
         <v>0.72</v>
       </c>
       <c r="C283" t="n">
-        <v>0.109193837868</v>
+        <v>0.1091330497493262</v>
       </c>
       <c r="D283" t="n">
-        <v>0.00555844755269</v>
+        <v>0.005568511476823067</v>
       </c>
       <c r="E283" t="n">
-        <v>0.09661141518419999</v>
+        <v>0.0965369172791517</v>
       </c>
       <c r="F283" t="n">
-        <v>0.116451086836</v>
+        <v>0.1164215310953463</v>
       </c>
     </row>
     <row r="284">
@@ -6097,16 +6097,16 @@
         <v>0.74</v>
       </c>
       <c r="C284" t="n">
-        <v>0.125912078683</v>
+        <v>0.1258603235503185</v>
       </c>
       <c r="D284" t="n">
-        <v>0.00524103799032</v>
+        <v>0.005245958761988459</v>
       </c>
       <c r="E284" t="n">
-        <v>0.114070648554</v>
+        <v>0.1140132567873433</v>
       </c>
       <c r="F284" t="n">
-        <v>0.132683263937</v>
+        <v>0.1326463861327332</v>
       </c>
     </row>
     <row r="285">
@@ -6117,16 +6117,16 @@
         <v>0.76</v>
       </c>
       <c r="C285" t="n">
-        <v>0.142716111816</v>
+        <v>0.1426628780690728</v>
       </c>
       <c r="D285" t="n">
-        <v>0.00489990629445</v>
+        <v>0.004902547688523337</v>
       </c>
       <c r="E285" t="n">
-        <v>0.131669671525</v>
+        <v>0.1316163775467398</v>
       </c>
       <c r="F285" t="n">
-        <v>0.148956233182</v>
+        <v>0.1489166268288908</v>
       </c>
     </row>
     <row r="286">
@@ -6137,16 +6137,16 @@
         <v>0.78</v>
       </c>
       <c r="C286" t="n">
-        <v>0.159589601209</v>
+        <v>0.1595373834128715</v>
       </c>
       <c r="D286" t="n">
-        <v>0.00453579316808</v>
+        <v>0.004530672308232215</v>
       </c>
       <c r="E286" t="n">
-        <v>0.149389718651</v>
+        <v>0.1493486777569073</v>
       </c>
       <c r="F286" t="n">
-        <v>0.165342775549</v>
+        <v>0.1652844073884054</v>
       </c>
     </row>
     <row r="287">
@@ -6157,16 +6157,16 @@
         <v>0.8</v>
       </c>
       <c r="C287" t="n">
-        <v>0.176536322185</v>
+        <v>0.1764797097076445</v>
       </c>
       <c r="D287" t="n">
-        <v>0.0041626506726</v>
+        <v>0.004158911716572442</v>
       </c>
       <c r="E287" t="n">
-        <v>0.167174408336</v>
+        <v>0.1671196398942998</v>
       </c>
       <c r="F287" t="n">
-        <v>0.181770228817</v>
+        <v>0.1817053824331349</v>
       </c>
     </row>
     <row r="288">
@@ -6177,16 +6177,16 @@
         <v>0.82</v>
       </c>
       <c r="C288" t="n">
-        <v>0.193549013135</v>
+        <v>0.1934981331696611</v>
       </c>
       <c r="D288" t="n">
-        <v>0.00379051915805</v>
+        <v>0.003781245333432729</v>
       </c>
       <c r="E288" t="n">
-        <v>0.185009477236</v>
+        <v>0.1849719832261076</v>
       </c>
       <c r="F288" t="n">
-        <v>0.198262553793</v>
+        <v>0.1981943568966296</v>
       </c>
     </row>
     <row r="289">
@@ -6197,16 +6197,16 @@
         <v>0</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.392795796508</v>
+        <v>-0.3930522357182649</v>
       </c>
       <c r="D289" t="n">
-        <v>0.0143401114491</v>
+        <v>0.01434046078308526</v>
       </c>
       <c r="E289" t="n">
-        <v>-0.420860068426</v>
+        <v>-0.4210604602524421</v>
       </c>
       <c r="F289" t="n">
-        <v>-0.376503789651</v>
+        <v>-0.3767527199179268</v>
       </c>
     </row>
     <row r="290">
@@ -6217,16 +6217,16 @@
         <v>0.02</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.380655864207</v>
+        <v>-0.3809082410730011</v>
       </c>
       <c r="D290" t="n">
-        <v>0.0142516976451</v>
+        <v>0.01425539015795085</v>
       </c>
       <c r="E290" t="n">
-        <v>-0.408576231635</v>
+        <v>-0.4087778718990442</v>
       </c>
       <c r="F290" t="n">
-        <v>-0.364533066698</v>
+        <v>-0.3647866437687117</v>
       </c>
     </row>
     <row r="291">
@@ -6237,16 +6237,16 @@
         <v>0.04</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.368423452623</v>
+        <v>-0.3686745116344063</v>
       </c>
       <c r="D291" t="n">
-        <v>0.0141641192976</v>
+        <v>0.01416565593750643</v>
       </c>
       <c r="E291" t="n">
-        <v>-0.396145712056</v>
+        <v>-0.3963349581126003</v>
       </c>
       <c r="F291" t="n">
-        <v>-0.352453219724</v>
+        <v>-0.3527054777646068</v>
       </c>
     </row>
     <row r="292">
@@ -6257,16 +6257,16 @@
         <v>0.06</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.356054011037</v>
+        <v>-0.3562915728484782</v>
       </c>
       <c r="D292" t="n">
-        <v>0.0140338975386</v>
+        <v>0.01402949442564272</v>
       </c>
       <c r="E292" t="n">
-        <v>-0.383600388825</v>
+        <v>-0.3837830254564469</v>
       </c>
       <c r="F292" t="n">
-        <v>-0.340286345121</v>
+        <v>-0.3405383114433729</v>
       </c>
     </row>
     <row r="293">
@@ -6277,16 +6277,16 @@
         <v>0.08</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.343593533714</v>
+        <v>-0.3438297422029409</v>
       </c>
       <c r="D293" t="n">
-        <v>0.0138743059381</v>
+        <v>0.01386778795188688</v>
       </c>
       <c r="E293" t="n">
-        <v>-0.370938244876</v>
+        <v>-0.3711151213348556</v>
       </c>
       <c r="F293" t="n">
-        <v>-0.328081240483</v>
+        <v>-0.3283410557386768</v>
       </c>
     </row>
     <row r="294">
@@ -6297,16 +6297,16 @@
         <v>0.1</v>
       </c>
       <c r="C294" t="n">
-        <v>-0.331029071577</v>
+        <v>-0.3312516831357951</v>
       </c>
       <c r="D294" t="n">
-        <v>0.0137015860704</v>
+        <v>0.01370186205231144</v>
       </c>
       <c r="E294" t="n">
-        <v>-0.358091830891</v>
+        <v>-0.3582560141728637</v>
       </c>
       <c r="F294" t="n">
-        <v>-0.315808096619</v>
+        <v>-0.3160461731691884</v>
       </c>
     </row>
     <row r="295">
@@ -6317,16 +6317,16 @@
         <v>0.12</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.318346298554</v>
+        <v>-0.3185564786972373</v>
       </c>
       <c r="D295" t="n">
-        <v>0.0135534112766</v>
+        <v>0.01355307346148398</v>
       </c>
       <c r="E295" t="n">
-        <v>-0.345152702064</v>
+        <v>-0.3453033301335404</v>
       </c>
       <c r="F295" t="n">
-        <v>-0.303451580999</v>
+        <v>-0.3036950446824846</v>
       </c>
     </row>
     <row r="296">
@@ -6337,16 +6337,16 @@
         <v>0.14</v>
       </c>
       <c r="C296" t="n">
-        <v>-0.30557080122</v>
+        <v>-0.3057848153855321</v>
       </c>
       <c r="D296" t="n">
-        <v>0.0134039629456</v>
+        <v>0.01340372117899703</v>
       </c>
       <c r="E296" t="n">
-        <v>-0.332084495215</v>
+        <v>-0.3322317166079101</v>
       </c>
       <c r="F296" t="n">
-        <v>-0.291059402846</v>
+        <v>-0.2913060201912137</v>
       </c>
     </row>
     <row r="297">
@@ -6357,16 +6357,16 @@
         <v>0.16</v>
       </c>
       <c r="C297" t="n">
-        <v>-0.29267860569</v>
+        <v>-0.292864461290568</v>
       </c>
       <c r="D297" t="n">
-        <v>0.013217633347</v>
+        <v>0.01320287366477229</v>
       </c>
       <c r="E297" t="n">
-        <v>-0.318977324493</v>
+        <v>-0.3191187794151675</v>
       </c>
       <c r="F297" t="n">
-        <v>-0.278636792222</v>
+        <v>-0.2788889836532249</v>
       </c>
     </row>
     <row r="298">
@@ -6377,16 +6377,16 @@
         <v>0.18</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.279662928028</v>
+        <v>-0.2798380230518225</v>
       </c>
       <c r="D298" t="n">
-        <v>0.0130112737738</v>
+        <v>0.01299183381997252</v>
       </c>
       <c r="E298" t="n">
-        <v>-0.305717830621</v>
+        <v>-0.3058470685457371</v>
       </c>
       <c r="F298" t="n">
-        <v>-0.266162704338</v>
+        <v>-0.2664072791589369</v>
       </c>
     </row>
     <row r="299">
@@ -6397,16 +6397,16 @@
         <v>0.2</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.266552017698</v>
+        <v>-0.2667191628843614</v>
       </c>
       <c r="D299" t="n">
-        <v>0.0128047007197</v>
+        <v>0.0127850606297502</v>
       </c>
       <c r="E299" t="n">
-        <v>-0.292411815626</v>
+        <v>-0.2925386173409645</v>
       </c>
       <c r="F299" t="n">
-        <v>-0.253586798852</v>
+        <v>-0.2538226574166638</v>
       </c>
     </row>
     <row r="300">
@@ -6417,16 +6417,16 @@
         <v>0.22</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.253360353017</v>
+        <v>-0.2535203136320467</v>
       </c>
       <c r="D300" t="n">
-        <v>0.0126123653415</v>
+        <v>0.01259707411379995</v>
       </c>
       <c r="E300" t="n">
-        <v>-0.279061512034</v>
+        <v>-0.2791874336972207</v>
       </c>
       <c r="F300" t="n">
-        <v>-0.240935032988</v>
+        <v>-0.2411768368464324</v>
       </c>
     </row>
     <row r="301">
@@ -6437,16 +6437,16 @@
         <v>0.24</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.240013658494</v>
+        <v>-0.240161416209208</v>
       </c>
       <c r="D301" t="n">
-        <v>0.012454699739</v>
+        <v>0.01244349280053481</v>
       </c>
       <c r="E301" t="n">
-        <v>-0.265615901462</v>
+        <v>-0.2657365398951814</v>
       </c>
       <c r="F301" t="n">
-        <v>-0.22801769268</v>
+        <v>-0.2280640079784666</v>
       </c>
     </row>
     <row r="302">
@@ -6457,16 +6457,16 @@
         <v>0.26</v>
       </c>
       <c r="C302" t="n">
-        <v>-0.22653915606</v>
+        <v>-0.2266887057686656</v>
       </c>
       <c r="D302" t="n">
-        <v>0.0123419507433</v>
+        <v>0.01233375410044396</v>
       </c>
       <c r="E302" t="n">
-        <v>-0.252125560719</v>
+        <v>-0.2522533137461958</v>
       </c>
       <c r="F302" t="n">
-        <v>-0.214668766296</v>
+        <v>-0.2147195898403682</v>
       </c>
     </row>
     <row r="303">
@@ -6477,16 +6477,16 @@
         <v>0.28</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.212974290582</v>
+        <v>-0.213118954179612</v>
       </c>
       <c r="D303" t="n">
-        <v>0.0122498003291</v>
+        <v>0.01224798121991623</v>
       </c>
       <c r="E303" t="n">
-        <v>-0.238596733374</v>
+        <v>-0.2387312823535508</v>
       </c>
       <c r="F303" t="n">
-        <v>-0.201263987303</v>
+        <v>-0.2013114645106171</v>
       </c>
     </row>
     <row r="304">
@@ -6497,16 +6497,16 @@
         <v>0.3</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.199345700471</v>
+        <v>-0.1994927905648224</v>
       </c>
       <c r="D304" t="n">
-        <v>0.0121728294511</v>
+        <v>0.01217339365221009</v>
       </c>
       <c r="E304" t="n">
-        <v>-0.225006699583</v>
+        <v>-0.2251457761486844</v>
       </c>
       <c r="F304" t="n">
-        <v>-0.187811119387</v>
+        <v>-0.1878599984859717</v>
       </c>
     </row>
     <row r="305">
@@ -6517,16 +6517,16 @@
         <v>0.32</v>
       </c>
       <c r="C305" t="n">
-        <v>-0.185594286915</v>
+        <v>-0.185719342090793</v>
       </c>
       <c r="D305" t="n">
-        <v>0.0120473078793</v>
+        <v>0.01204957533231835</v>
       </c>
       <c r="E305" t="n">
-        <v>-0.211141386733</v>
+        <v>-0.2112629559543535</v>
       </c>
       <c r="F305" t="n">
-        <v>-0.174274069927</v>
+        <v>-0.1743164722449793</v>
       </c>
     </row>
     <row r="306">
@@ -6537,16 +6537,16 @@
         <v>0.34</v>
       </c>
       <c r="C306" t="n">
-        <v>-0.171644649819</v>
+        <v>-0.1717626161656446</v>
       </c>
       <c r="D306" t="n">
-        <v>0.0119436060008</v>
+        <v>0.01194111690607229</v>
       </c>
       <c r="E306" t="n">
-        <v>-0.197165495486</v>
+        <v>-0.1972627394405038</v>
       </c>
       <c r="F306" t="n">
-        <v>-0.160546977565</v>
+        <v>-0.160595089940859</v>
       </c>
     </row>
     <row r="307">
@@ -6557,16 +6557,16 @@
         <v>0.36</v>
       </c>
       <c r="C307" t="n">
-        <v>-0.157571927597</v>
+        <v>-0.1576902687729738</v>
       </c>
       <c r="D307" t="n">
-        <v>0.0117628530721</v>
+        <v>0.01176149351721044</v>
       </c>
       <c r="E307" t="n">
-        <v>-0.182774055865</v>
+        <v>-0.1828810392003861</v>
       </c>
       <c r="F307" t="n">
-        <v>-0.146730429918</v>
+        <v>-0.1467741634613251</v>
       </c>
     </row>
     <row r="308">
@@ -6577,16 +6577,16 @@
         <v>0.38</v>
       </c>
       <c r="C308" t="n">
-        <v>-0.143432411199</v>
+        <v>-0.1435554289586376</v>
       </c>
       <c r="D308" t="n">
-        <v>0.0116100018006</v>
+        <v>0.01161052474594277</v>
       </c>
       <c r="E308" t="n">
-        <v>-0.168378819944</v>
+        <v>-0.1684973232267497</v>
       </c>
       <c r="F308" t="n">
-        <v>-0.132785042873</v>
+        <v>-0.1328333005401294</v>
       </c>
     </row>
     <row r="309">
@@ -6597,16 +6597,16 @@
         <v>0.4</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.129241928027</v>
+        <v>-0.1293638831157787</v>
       </c>
       <c r="D309" t="n">
-        <v>0.0114556495066</v>
+        <v>0.01145736342607533</v>
       </c>
       <c r="E309" t="n">
-        <v>-0.153920168262</v>
+        <v>-0.1540369995615887</v>
       </c>
       <c r="F309" t="n">
-        <v>-0.118790056062</v>
+        <v>-0.1188415534224569</v>
       </c>
     </row>
     <row r="310">
@@ -6617,16 +6617,16 @@
         <v>0.42</v>
       </c>
       <c r="C310" t="n">
-        <v>-0.114951546342</v>
+        <v>-0.1150737923390548</v>
       </c>
       <c r="D310" t="n">
-        <v>0.011311231355</v>
+        <v>0.01131635961062465</v>
       </c>
       <c r="E310" t="n">
-        <v>-0.139371270139</v>
+        <v>-0.1394931696260091</v>
       </c>
       <c r="F310" t="n">
-        <v>-0.104720759913</v>
+        <v>-0.1047753265924314</v>
       </c>
     </row>
     <row r="311">
@@ -6637,16 +6637,16 @@
         <v>0.44</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.100519897786</v>
+        <v>-0.100632386374946</v>
       </c>
       <c r="D311" t="n">
-        <v>0.0111487173104</v>
+        <v>0.01114687422968705</v>
       </c>
       <c r="E311" t="n">
-        <v>-0.124665668369</v>
+        <v>-0.124774310791218</v>
       </c>
       <c r="F311" t="n">
-        <v>-0.0905218930209</v>
+        <v>-0.09058300307903089</v>
       </c>
     </row>
     <row r="312">
@@ -6657,16 +6657,16 @@
         <v>0.46</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.0859054139586</v>
+        <v>-0.08601349454899472</v>
       </c>
       <c r="D312" t="n">
-        <v>0.0109511563299</v>
+        <v>0.01095034381140256</v>
       </c>
       <c r="E312" t="n">
-        <v>-0.109805431627</v>
+        <v>-0.1099052353607348</v>
       </c>
       <c r="F312" t="n">
-        <v>-0.07625185761599999</v>
+        <v>-0.07632045336710913</v>
       </c>
     </row>
     <row r="313">
@@ -6677,16 +6677,16 @@
         <v>0.48</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.0712161887631</v>
+        <v>-0.07132807059336158</v>
       </c>
       <c r="D313" t="n">
-        <v>0.0107609787827</v>
+        <v>0.01075616300452354</v>
       </c>
       <c r="E313" t="n">
-        <v>-0.0948843059115</v>
+        <v>-0.09498474768573306</v>
       </c>
       <c r="F313" t="n">
-        <v>-0.0618391073579</v>
+        <v>-0.06189913913775236</v>
       </c>
     </row>
     <row r="314">
@@ -6697,16 +6697,16 @@
         <v>0.5</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.0564568269409</v>
+        <v>-0.05656982269164947</v>
       </c>
       <c r="D314" t="n">
-        <v>0.0105364220174</v>
+        <v>0.01053225384176415</v>
       </c>
       <c r="E314" t="n">
-        <v>-0.0797793583338</v>
+        <v>-0.07988348428145464</v>
       </c>
       <c r="F314" t="n">
-        <v>-0.0473938798461</v>
+        <v>-0.04746374753864568</v>
       </c>
     </row>
     <row r="315">
@@ -6717,16 +6717,16 @@
         <v>0.52</v>
       </c>
       <c r="C315" t="n">
-        <v>-0.0416384471082</v>
+        <v>-0.04175176943238981</v>
       </c>
       <c r="D315" t="n">
-        <v>0.0103066447028</v>
+        <v>0.01030098979337079</v>
       </c>
       <c r="E315" t="n">
-        <v>-0.0645964616599</v>
+        <v>-0.06469652564239059</v>
       </c>
       <c r="F315" t="n">
-        <v>-0.0329246824942</v>
+        <v>-0.03300004414585445</v>
       </c>
     </row>
     <row r="316">
@@ -6737,16 +6737,16 @@
         <v>0.54</v>
       </c>
       <c r="C316" t="n">
-        <v>-0.0267643535374</v>
+        <v>-0.02687390281486799</v>
       </c>
       <c r="D316" t="n">
-        <v>0.0100847086632</v>
+        <v>0.01008254274224907</v>
       </c>
       <c r="E316" t="n">
-        <v>-0.0493723647262</v>
+        <v>-0.04947152701854929</v>
       </c>
       <c r="F316" t="n">
-        <v>-0.0183464251845</v>
+        <v>-0.01845557526564967</v>
       </c>
     </row>
     <row r="317">
@@ -6757,16 +6757,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C317" t="n">
-        <v>-0.0117907309785</v>
+        <v>-0.01190525315925317</v>
       </c>
       <c r="D317" t="n">
-        <v>0.009814276242749999</v>
+        <v>0.009811163489427833</v>
       </c>
       <c r="E317" t="n">
-        <v>-0.0338283354412</v>
+        <v>-0.03392465042655424</v>
       </c>
       <c r="F317" t="n">
-        <v>-0.00356694905111</v>
+        <v>-0.003730463605362111</v>
       </c>
     </row>
     <row r="318">
@@ -6777,16 +6777,16 @@
         <v>0.58</v>
       </c>
       <c r="C318" t="n">
-        <v>0.003275924488</v>
+        <v>0.003166970129533553</v>
       </c>
       <c r="D318" t="n">
-        <v>0.00952407121357</v>
+        <v>0.009520196745203362</v>
       </c>
       <c r="E318" t="n">
-        <v>-0.0181287012143</v>
+        <v>-0.01822238501056006</v>
       </c>
       <c r="F318" t="n">
-        <v>0.0112999021131</v>
+        <v>0.01114359393349229</v>
       </c>
     </row>
     <row r="319">
@@ -6797,16 +6797,16 @@
         <v>0.6</v>
       </c>
       <c r="C319" t="n">
-        <v>0.0185281893427</v>
+        <v>0.01842866471515823</v>
       </c>
       <c r="D319" t="n">
-        <v>0.00916846037827</v>
+        <v>0.009160319933224699</v>
       </c>
       <c r="E319" t="n">
-        <v>-0.00205964849586</v>
+        <v>-0.002131151761243899</v>
       </c>
       <c r="F319" t="n">
-        <v>0.0263470758498</v>
+        <v>0.02620337195270128</v>
       </c>
     </row>
     <row r="320">
@@ -6817,16 +6817,16 @@
         <v>0.62</v>
       </c>
       <c r="C320" t="n">
-        <v>0.0339853059845</v>
+        <v>0.03389956741379078</v>
       </c>
       <c r="D320" t="n">
-        <v>0.00876686385462</v>
+        <v>0.008757071852455525</v>
       </c>
       <c r="E320" t="n">
-        <v>0.0143169755335</v>
+        <v>0.01424730610941882</v>
       </c>
       <c r="F320" t="n">
-        <v>0.0416066838179</v>
+        <v>0.04148672244280949</v>
       </c>
     </row>
     <row r="321">
@@ -6837,16 +6837,16 @@
         <v>0.64</v>
       </c>
       <c r="C321" t="n">
-        <v>0.0495938525104</v>
+        <v>0.04952391730803089</v>
       </c>
       <c r="D321" t="n">
-        <v>0.00836572610734</v>
+        <v>0.008355955082508932</v>
       </c>
       <c r="E321" t="n">
-        <v>0.0307829697137</v>
+        <v>0.03072541418720398</v>
       </c>
       <c r="F321" t="n">
-        <v>0.0569955991406</v>
+        <v>0.0568787342532362</v>
       </c>
     </row>
     <row r="322">
@@ -6857,16 +6857,16 @@
         <v>0.66</v>
       </c>
       <c r="C322" t="n">
-        <v>0.0653205237409</v>
+        <v>0.06524493494069343</v>
       </c>
       <c r="D322" t="n">
-        <v>0.007935226906280001</v>
+        <v>0.007925712450099895</v>
       </c>
       <c r="E322" t="n">
-        <v>0.0474218770967</v>
+        <v>0.04735868346136929</v>
       </c>
       <c r="F322" t="n">
-        <v>0.0724192171052</v>
+        <v>0.07229195112121189</v>
       </c>
     </row>
     <row r="323">
@@ -6877,16 +6877,16 @@
         <v>0.68</v>
       </c>
       <c r="C323" t="n">
-        <v>0.0810877976224</v>
+        <v>0.08100866506473547</v>
       </c>
       <c r="D323" t="n">
-        <v>0.00750799050655</v>
+        <v>0.007505741357725196</v>
       </c>
       <c r="E323" t="n">
-        <v>0.06411958871329999</v>
+        <v>0.06404611403575089</v>
       </c>
       <c r="F323" t="n">
-        <v>0.0878740233199</v>
+        <v>0.08776733424164451</v>
       </c>
     </row>
     <row r="324">
@@ -6897,16 +6897,16 @@
         <v>0.7</v>
       </c>
       <c r="C324" t="n">
-        <v>0.09695157528999999</v>
+        <v>0.09687412041105707</v>
       </c>
       <c r="D324" t="n">
-        <v>0.00710830848856</v>
+        <v>0.007109636160569152</v>
       </c>
       <c r="E324" t="n">
-        <v>0.0808647017228</v>
+        <v>0.08077574889855033</v>
       </c>
       <c r="F324" t="n">
-        <v>0.103466943977</v>
+        <v>0.103356845678328</v>
       </c>
     </row>
     <row r="325">
@@ -6917,16 +6917,16 @@
         <v>0.72</v>
       </c>
       <c r="C325" t="n">
-        <v>0.11300827831</v>
+        <v>0.1129298533182817</v>
       </c>
       <c r="D325" t="n">
-        <v>0.00665169443273</v>
+        <v>0.006648786980249481</v>
       </c>
       <c r="E325" t="n">
-        <v>0.0979298933815</v>
+        <v>0.09785494639206593</v>
       </c>
       <c r="F325" t="n">
-        <v>0.119120709842</v>
+        <v>0.1190148246691729</v>
       </c>
     </row>
     <row r="326">
@@ -6937,16 +6937,16 @@
         <v>0.74</v>
       </c>
       <c r="C326" t="n">
-        <v>0.129178250474</v>
+        <v>0.1291086843345473</v>
       </c>
       <c r="D326" t="n">
-        <v>0.00618894931844</v>
+        <v>0.006197733621341818</v>
       </c>
       <c r="E326" t="n">
-        <v>0.115156038474</v>
+        <v>0.1150701609722606</v>
       </c>
       <c r="F326" t="n">
-        <v>0.134940048633</v>
+        <v>0.1348870472476387</v>
       </c>
     </row>
     <row r="327">
@@ -6957,16 +6957,16 @@
         <v>0.76</v>
       </c>
       <c r="C327" t="n">
-        <v>0.145516062985</v>
+        <v>0.1454505190178277</v>
       </c>
       <c r="D327" t="n">
-        <v>0.00578737112558</v>
+        <v>0.005801193018111673</v>
       </c>
       <c r="E327" t="n">
-        <v>0.132449149703</v>
+        <v>0.1323514654017766</v>
       </c>
       <c r="F327" t="n">
-        <v>0.151064490739</v>
+        <v>0.1510046395060094</v>
       </c>
     </row>
     <row r="328">
@@ -6977,16 +6977,16 @@
         <v>0.78</v>
       </c>
       <c r="C328" t="n">
-        <v>0.16198176515</v>
+        <v>0.161922716190872</v>
       </c>
       <c r="D328" t="n">
-        <v>0.00537880375759</v>
+        <v>0.005390076613087369</v>
       </c>
       <c r="E328" t="n">
-        <v>0.149842995824</v>
+        <v>0.1497560270921294</v>
       </c>
       <c r="F328" t="n">
-        <v>0.167270175105</v>
+        <v>0.1672267016524351</v>
       </c>
     </row>
     <row r="329">
@@ -6997,16 +6997,16 @@
         <v>0.8</v>
       </c>
       <c r="C329" t="n">
-        <v>0.178566230047</v>
+        <v>0.1785072232685323</v>
       </c>
       <c r="D329" t="n">
-        <v>0.00497181632567</v>
+        <v>0.004979752261958022</v>
       </c>
       <c r="E329" t="n">
-        <v>0.167332324393</v>
+        <v>0.1672500672338169</v>
       </c>
       <c r="F329" t="n">
-        <v>0.183532672904</v>
+        <v>0.1834844828352118</v>
       </c>
     </row>
     <row r="330">
@@ -7017,16 +7017,16 @@
         <v>0.82</v>
       </c>
       <c r="C330" t="n">
-        <v>0.195241903295</v>
+        <v>0.1951776341622836</v>
       </c>
       <c r="D330" t="n">
-        <v>0.00457511867253</v>
+        <v>0.004583044992958316</v>
       </c>
       <c r="E330" t="n">
-        <v>0.184892274877</v>
+        <v>0.1848054469366227</v>
       </c>
       <c r="F330" t="n">
-        <v>0.199869156284</v>
+        <v>0.1998232229735022</v>
       </c>
     </row>
     <row r="331">
@@ -7037,16 +7037,16 @@
         <v>0.84</v>
       </c>
       <c r="C331" t="n">
-        <v>0.212013523308</v>
+        <v>0.2119523399233609</v>
       </c>
       <c r="D331" t="n">
-        <v>0.00415500086915</v>
+        <v>0.00415725794553293</v>
       </c>
       <c r="E331" t="n">
-        <v>0.202599876364</v>
+        <v>0.2025307191673331</v>
       </c>
       <c r="F331" t="n">
-        <v>0.216326428713</v>
+        <v>0.2162760197858296</v>
       </c>
     </row>
     <row r="332">
@@ -7057,16 +7057,16 @@
         <v>0.86</v>
       </c>
       <c r="C332" t="n">
-        <v>0.228900962164</v>
+        <v>0.2288395337454239</v>
       </c>
       <c r="D332" t="n">
-        <v>0.00367983783507</v>
+        <v>0.003677791111846229</v>
       </c>
       <c r="E332" t="n">
-        <v>0.220517808099</v>
+        <v>0.2204583999385186</v>
       </c>
       <c r="F332" t="n">
-        <v>0.232822866646</v>
+        <v>0.2327616531444887</v>
       </c>
     </row>
     <row r="333">
@@ -7077,16 +7077,16 @@
         <v>0.88</v>
       </c>
       <c r="C333" t="n">
-        <v>0.245900209157</v>
+        <v>0.245835330646397</v>
       </c>
       <c r="D333" t="n">
-        <v>0.00319155370352</v>
+        <v>0.003188400584871942</v>
       </c>
       <c r="E333" t="n">
-        <v>0.238540341294</v>
+        <v>0.2384709609869429</v>
       </c>
       <c r="F333" t="n">
-        <v>0.249338677493</v>
+        <v>0.2492621410143174</v>
       </c>
     </row>
     <row r="334">
@@ -7097,16 +7097,16 @@
         <v>0</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.271277548134</v>
+        <v>-0.2715355451405535</v>
       </c>
       <c r="D334" t="n">
-        <v>0.0233956892698</v>
+        <v>0.02333829577022714</v>
       </c>
       <c r="E334" t="n">
-        <v>-0.313717510045</v>
+        <v>-0.3138639992220877</v>
       </c>
       <c r="F334" t="n">
-        <v>-0.232193049286</v>
+        <v>-0.2325625339254875</v>
       </c>
     </row>
     <row r="335">
@@ -7117,16 +7117,16 @@
         <v>0.02</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.263273546803</v>
+        <v>-0.2635232159058863</v>
       </c>
       <c r="D335" t="n">
-        <v>0.0227753431137</v>
+        <v>0.02271899409413285</v>
       </c>
       <c r="E335" t="n">
-        <v>-0.305101363949</v>
+        <v>-0.30523577443362</v>
       </c>
       <c r="F335" t="n">
-        <v>-0.225566198366</v>
+        <v>-0.2259307976130875</v>
       </c>
     </row>
     <row r="336">
@@ -7137,16 +7137,16 @@
         <v>0.04</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.255132692079</v>
+        <v>-0.2553721879725896</v>
       </c>
       <c r="D336" t="n">
-        <v>0.022138779457</v>
+        <v>0.02208130624487071</v>
       </c>
       <c r="E336" t="n">
-        <v>-0.296209929791</v>
+        <v>-0.2963300431297888</v>
       </c>
       <c r="F336" t="n">
-        <v>-0.218880461875</v>
+        <v>-0.2192471017957862</v>
       </c>
     </row>
     <row r="337">
@@ -7157,16 +7157,16 @@
         <v>0.06</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.246801975622</v>
+        <v>-0.2470324344655312</v>
       </c>
       <c r="D337" t="n">
-        <v>0.0214826899901</v>
+        <v>0.0214232427413036</v>
       </c>
       <c r="E337" t="n">
-        <v>-0.287077211982</v>
+        <v>-0.2871827790675834</v>
       </c>
       <c r="F337" t="n">
-        <v>-0.212161753271</v>
+        <v>-0.2125246810122841</v>
       </c>
     </row>
     <row r="338">
@@ -7177,16 +7177,16 @@
         <v>0.08</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.238286029497</v>
+        <v>-0.2385106369805388</v>
       </c>
       <c r="D338" t="n">
-        <v>0.0208521612264</v>
+        <v>0.0207976889334318</v>
       </c>
       <c r="E338" t="n">
-        <v>-0.277634471048</v>
+        <v>-0.2777386853575683</v>
       </c>
       <c r="F338" t="n">
-        <v>-0.205220861875</v>
+        <v>-0.2055774863696556</v>
       </c>
     </row>
     <row r="339">
@@ -7197,16 +7197,16 @@
         <v>0.1</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.229617898931</v>
+        <v>-0.2298376769418719</v>
       </c>
       <c r="D339" t="n">
-        <v>0.0202188389912</v>
+        <v>0.02016397848922633</v>
       </c>
       <c r="E339" t="n">
-        <v>-0.268116477746</v>
+        <v>-0.2682227205501677</v>
       </c>
       <c r="F339" t="n">
-        <v>-0.19815869516</v>
+        <v>-0.1985193173279827</v>
       </c>
     </row>
     <row r="340">
@@ -7217,16 +7217,16 @@
         <v>0.12</v>
       </c>
       <c r="C340" t="n">
-        <v>-0.22081613404</v>
+        <v>-0.221032308274875</v>
       </c>
       <c r="D340" t="n">
-        <v>0.0195538651782</v>
+        <v>0.01950007866074732</v>
       </c>
       <c r="E340" t="n">
-        <v>-0.258513924041</v>
+        <v>-0.2586246866168374</v>
       </c>
       <c r="F340" t="n">
-        <v>-0.191009501553</v>
+        <v>-0.1913684778581821</v>
       </c>
     </row>
     <row r="341">
@@ -7237,16 +7237,16 @@
         <v>0.14</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.211912655187</v>
+        <v>-0.212124867718103</v>
       </c>
       <c r="D341" t="n">
-        <v>0.0188920235173</v>
+        <v>0.01883994491869077</v>
       </c>
       <c r="E341" t="n">
-        <v>-0.248892536331</v>
+        <v>-0.2490047188703626</v>
       </c>
       <c r="F341" t="n">
-        <v>-0.183768742913</v>
+        <v>-0.1841198165521307</v>
       </c>
     </row>
     <row r="342">
@@ -7257,16 +7257,16 @@
         <v>0.16</v>
       </c>
       <c r="C342" t="n">
-        <v>-0.202859245869</v>
+        <v>-0.2030594166156025</v>
       </c>
       <c r="D342" t="n">
-        <v>0.0182689181885</v>
+        <v>0.01822924847988933</v>
       </c>
       <c r="E342" t="n">
-        <v>-0.239112803039</v>
+        <v>-0.2392295318152673</v>
       </c>
       <c r="F342" t="n">
-        <v>-0.176211485714</v>
+        <v>-0.1765217457720158</v>
       </c>
     </row>
     <row r="343">
@@ -7277,16 +7277,16 @@
         <v>0.18</v>
       </c>
       <c r="C343" t="n">
-        <v>-0.193591090894</v>
+        <v>-0.1937762661501586</v>
       </c>
       <c r="D343" t="n">
-        <v>0.0176943039109</v>
+        <v>0.017659229237403</v>
       </c>
       <c r="E343" t="n">
-        <v>-0.229156062725</v>
+        <v>-0.2292678760355882</v>
       </c>
       <c r="F343" t="n">
-        <v>-0.16838199208</v>
+        <v>-0.1686814246674375</v>
       </c>
     </row>
     <row r="344">
@@ -7297,16 +7297,16 @@
         <v>0.2</v>
       </c>
       <c r="C344" t="n">
-        <v>-0.184074054211</v>
+        <v>-0.1842529658231404</v>
       </c>
       <c r="D344" t="n">
-        <v>0.0171734739456</v>
+        <v>0.01713671007215574</v>
       </c>
       <c r="E344" t="n">
-        <v>-0.219032053856</v>
+        <v>-0.2191366404092054</v>
       </c>
       <c r="F344" t="n">
-        <v>-0.160354785973</v>
+        <v>-0.1606529188672123</v>
       </c>
     </row>
     <row r="345">
@@ -7317,16 +7317,16 @@
         <v>0.22</v>
       </c>
       <c r="C345" t="n">
-        <v>-0.174402543282</v>
+        <v>-0.1745829188010472</v>
       </c>
       <c r="D345" t="n">
-        <v>0.0166682117078</v>
+        <v>0.01663466354700194</v>
       </c>
       <c r="E345" t="n">
-        <v>-0.208771524131</v>
+        <v>-0.2088813984904627</v>
       </c>
       <c r="F345" t="n">
-        <v>-0.15206080104</v>
+        <v>-0.1523673571897577</v>
       </c>
     </row>
     <row r="346">
@@ -7337,16 +7337,16 @@
         <v>0.24</v>
       </c>
       <c r="C346" t="n">
-        <v>-0.164590312852</v>
+        <v>-0.1647675872724241</v>
       </c>
       <c r="D346" t="n">
-        <v>0.0161890605242</v>
+        <v>0.01615661240985778</v>
       </c>
       <c r="E346" t="n">
-        <v>-0.198407500299</v>
+        <v>-0.1985048434689158</v>
       </c>
       <c r="F346" t="n">
-        <v>-0.143546631324</v>
+        <v>-0.1438409305860722</v>
       </c>
     </row>
     <row r="347">
@@ -7357,16 +7357,16 @@
         <v>0.26</v>
       </c>
       <c r="C347" t="n">
-        <v>-0.154662584851</v>
+        <v>-0.1548365919788365</v>
       </c>
       <c r="D347" t="n">
-        <v>0.0157270768625</v>
+        <v>0.01569822231725867</v>
       </c>
       <c r="E347" t="n">
-        <v>-0.18789372293</v>
+        <v>-0.1879892595356303</v>
       </c>
       <c r="F347" t="n">
-        <v>-0.134871626221</v>
+        <v>-0.135159721354837</v>
       </c>
     </row>
     <row r="348">
@@ -7377,16 +7377,16 @@
         <v>0.28</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.144543706849</v>
+        <v>-0.1447065646590832</v>
       </c>
       <c r="D348" t="n">
-        <v>0.0153240761349</v>
+        <v>0.01530173561839214</v>
       </c>
       <c r="E348" t="n">
-        <v>-0.177260734514</v>
+        <v>-0.1773573366765309</v>
       </c>
       <c r="F348" t="n">
-        <v>-0.125836110811</v>
+        <v>-0.1260881084296441</v>
       </c>
     </row>
     <row r="349">
@@ -7397,16 +7397,16 @@
         <v>0.3</v>
       </c>
       <c r="C349" t="n">
-        <v>-0.134258261138</v>
+        <v>-0.1344127289791689</v>
       </c>
       <c r="D349" t="n">
-        <v>0.0149457762776</v>
+        <v>0.01492249965152267</v>
       </c>
       <c r="E349" t="n">
-        <v>-0.166508599421</v>
+        <v>-0.1665865359873058</v>
       </c>
       <c r="F349" t="n">
-        <v>-0.116580162178</v>
+        <v>-0.1168194442087804</v>
       </c>
     </row>
     <row r="350">
@@ -7417,16 +7417,16 @@
         <v>0.32</v>
       </c>
       <c r="C350" t="n">
-        <v>-0.123783377984</v>
+        <v>-0.1239368441728188</v>
       </c>
       <c r="D350" t="n">
-        <v>0.0145552844219</v>
+        <v>0.01453668176729341</v>
       </c>
       <c r="E350" t="n">
-        <v>-0.155424090338</v>
+        <v>-0.1555067878385552</v>
       </c>
       <c r="F350" t="n">
-        <v>-0.10713030299</v>
+        <v>-0.1073610012680062</v>
       </c>
     </row>
     <row r="351">
@@ -7437,16 +7437,16 @@
         <v>0.34</v>
       </c>
       <c r="C351" t="n">
-        <v>-0.113163231329</v>
+        <v>-0.1133162601842128</v>
       </c>
       <c r="D351" t="n">
-        <v>0.0141924844601</v>
+        <v>0.01417538973794507</v>
       </c>
       <c r="E351" t="n">
-        <v>-0.144288481908</v>
+        <v>-0.144370544817102</v>
       </c>
       <c r="F351" t="n">
-        <v>-0.0975115173444</v>
+        <v>-0.09774072643666809</v>
       </c>
     </row>
     <row r="352">
@@ -7457,16 +7457,16 @@
         <v>0.36</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.102386361899</v>
+        <v>-0.1025220942410996</v>
       </c>
       <c r="D352" t="n">
-        <v>0.0138199723862</v>
+        <v>0.01379450844409575</v>
       </c>
       <c r="E352" t="n">
-        <v>-0.132888732071</v>
+        <v>-0.132907842999721</v>
       </c>
       <c r="F352" t="n">
-        <v>-0.0877347531766</v>
+        <v>-0.08794720675719869</v>
       </c>
     </row>
     <row r="353">
@@ -7477,16 +7477,16 @@
         <v>0.38</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.0914196468161</v>
+        <v>-0.0915592130590361</v>
       </c>
       <c r="D353" t="n">
-        <v>0.0133997856953</v>
+        <v>0.01337426568854065</v>
       </c>
       <c r="E353" t="n">
-        <v>-0.12101397978</v>
+        <v>-0.1210332335516089</v>
       </c>
       <c r="F353" t="n">
-        <v>-0.07777279399129999</v>
+        <v>-0.07786751372988032</v>
       </c>
     </row>
     <row r="354">
@@ -7497,16 +7497,16 @@
         <v>0.4</v>
       </c>
       <c r="C354" t="n">
-        <v>-0.0802699295598</v>
+        <v>-0.08039574761940864</v>
       </c>
       <c r="D354" t="n">
-        <v>0.0129383969456</v>
+        <v>0.01291325845939974</v>
       </c>
       <c r="E354" t="n">
-        <v>-0.10890746575</v>
+        <v>-0.1089120458816533</v>
       </c>
       <c r="F354" t="n">
-        <v>-0.0670280322378</v>
+        <v>-0.06711331055968284</v>
       </c>
     </row>
     <row r="355">
@@ -7517,16 +7517,16 @@
         <v>0.42</v>
       </c>
       <c r="C355" t="n">
-        <v>-0.0689294620033</v>
+        <v>-0.06905177740715303</v>
       </c>
       <c r="D355" t="n">
-        <v>0.0124865039419</v>
+        <v>0.01246420350052893</v>
       </c>
       <c r="E355" t="n">
-        <v>-0.0965702144725</v>
+        <v>-0.09657039423482416</v>
       </c>
       <c r="F355" t="n">
-        <v>-0.056159270538</v>
+        <v>-0.05624144422804456</v>
       </c>
     </row>
     <row r="356">
@@ -7537,16 +7537,16 @@
         <v>0.44</v>
       </c>
       <c r="C356" t="n">
-        <v>-0.057392061491</v>
+        <v>-0.05751659099663433</v>
       </c>
       <c r="D356" t="n">
-        <v>0.0120452234559</v>
+        <v>0.01202304394154287</v>
       </c>
       <c r="E356" t="n">
-        <v>-0.08398877871340001</v>
+        <v>-0.0839844563171912</v>
       </c>
       <c r="F356" t="n">
-        <v>-0.0451740815232</v>
+        <v>-0.04526113946087484</v>
       </c>
     </row>
     <row r="357">
@@ -7557,16 +7557,16 @@
         <v>0.46</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.0456958290749</v>
+        <v>-0.0458156600056868</v>
       </c>
       <c r="D357" t="n">
-        <v>0.0116391047128</v>
+        <v>0.01162060474023616</v>
       </c>
       <c r="E357" t="n">
-        <v>-0.07128177067499999</v>
+        <v>-0.07127913877617864</v>
       </c>
       <c r="F357" t="n">
-        <v>-0.0340676653762</v>
+        <v>-0.03414550485819756</v>
       </c>
     </row>
     <row r="358">
@@ -7577,16 +7577,16 @@
         <v>0.48</v>
       </c>
       <c r="C358" t="n">
-        <v>-0.0338153262621</v>
+        <v>-0.03392680903253247</v>
       </c>
       <c r="D358" t="n">
-        <v>0.0112846866621</v>
+        <v>0.01127327693862525</v>
       </c>
       <c r="E358" t="n">
-        <v>-0.0585290563528</v>
+        <v>-0.05853523070071276</v>
       </c>
       <c r="F358" t="n">
-        <v>-0.0227423290754</v>
+        <v>-0.02282485753339092</v>
       </c>
     </row>
     <row r="359">
@@ -7597,16 +7597,16 @@
         <v>0.5</v>
       </c>
       <c r="C359" t="n">
-        <v>-0.0217265422448</v>
+        <v>-0.02183590561467401</v>
       </c>
       <c r="D359" t="n">
-        <v>0.0110218221324</v>
+        <v>0.01101484225765111</v>
       </c>
       <c r="E359" t="n">
-        <v>-0.0457777431197</v>
+        <v>-0.04579290513305079</v>
       </c>
       <c r="F359" t="n">
-        <v>-0.0112502319265</v>
+        <v>-0.01134077606187933</v>
       </c>
     </row>
     <row r="360">
@@ -7617,16 +7617,16 @@
         <v>0.52</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.009483649862250001</v>
+        <v>-0.009591923714677009</v>
       </c>
       <c r="D360" t="n">
-        <v>0.010784615028</v>
+        <v>0.01077720100882888</v>
       </c>
       <c r="E360" t="n">
-        <v>-0.0328424072905</v>
+        <v>-0.03284473314938108</v>
       </c>
       <c r="F360" t="n">
-        <v>0.000452533669354</v>
+        <v>0.0003781822775019705</v>
       </c>
     </row>
     <row r="361">
@@ -7637,16 +7637,16 @@
         <v>0.54</v>
       </c>
       <c r="C361" t="n">
-        <v>0.0029397627324</v>
+        <v>0.002833353823454132</v>
       </c>
       <c r="D361" t="n">
-        <v>0.0104835730193</v>
+        <v>0.01047409825443305</v>
       </c>
       <c r="E361" t="n">
-        <v>-0.0194854364909</v>
+        <v>-0.01947910498085381</v>
       </c>
       <c r="F361" t="n">
-        <v>0.0125086614354</v>
+        <v>0.01245464281806008</v>
       </c>
     </row>
     <row r="362">
@@ -7657,16 +7657,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C362" t="n">
-        <v>0.0155438628336</v>
+        <v>0.01544578156507042</v>
       </c>
       <c r="D362" t="n">
-        <v>0.0101996671246</v>
+        <v>0.01019601890401404</v>
       </c>
       <c r="E362" t="n">
-        <v>-0.00596380197313</v>
+        <v>-0.005953110643408088</v>
       </c>
       <c r="F362" t="n">
-        <v>0.0250847819706</v>
+        <v>0.0250449741213874</v>
       </c>
     </row>
     <row r="363">
@@ -7677,16 +7677,16 @@
         <v>0.58</v>
       </c>
       <c r="C363" t="n">
-        <v>0.02834985732</v>
+        <v>0.02826433749867885</v>
       </c>
       <c r="D363" t="n">
-        <v>0.009932060832939999</v>
+        <v>0.009927223183274644</v>
       </c>
       <c r="E363" t="n">
-        <v>0.00775774222822</v>
+        <v>0.00777054001563382</v>
       </c>
       <c r="F363" t="n">
-        <v>0.0377265780977</v>
+        <v>0.03767706155079598</v>
       </c>
     </row>
     <row r="364">
@@ -7697,16 +7697,16 @@
         <v>0.6</v>
       </c>
       <c r="C364" t="n">
-        <v>0.0414340193469</v>
+        <v>0.04135760178543464</v>
       </c>
       <c r="D364" t="n">
-        <v>0.00965420840585</v>
+        <v>0.009649385570953371</v>
       </c>
       <c r="E364" t="n">
-        <v>0.0217648877722</v>
+        <v>0.02177860284802691</v>
       </c>
       <c r="F364" t="n">
-        <v>0.0505113102338</v>
+        <v>0.05045736090191877</v>
       </c>
     </row>
     <row r="365">
@@ -7717,16 +7717,16 @@
         <v>0.62</v>
       </c>
       <c r="C365" t="n">
-        <v>0.0547356717659</v>
+        <v>0.05466294860412484</v>
       </c>
       <c r="D365" t="n">
-        <v>0.009398275278480001</v>
+        <v>0.009393497335410377</v>
       </c>
       <c r="E365" t="n">
-        <v>0.0358250103293</v>
+        <v>0.03582768518433532</v>
       </c>
       <c r="F365" t="n">
-        <v>0.0635055935329</v>
+        <v>0.06344459512563283</v>
       </c>
     </row>
     <row r="366">
@@ -7737,16 +7737,16 @@
         <v>0.64</v>
       </c>
       <c r="C366" t="n">
-        <v>0.0682846671229</v>
+        <v>0.0682141307918438</v>
       </c>
       <c r="D366" t="n">
-        <v>0.0091894344597</v>
+        <v>0.009189192312653584</v>
       </c>
       <c r="E366" t="n">
-        <v>0.0499061740393</v>
+        <v>0.04989492093320269</v>
       </c>
       <c r="F366" t="n">
-        <v>0.07680163218240001</v>
+        <v>0.07676846861549347</v>
       </c>
     </row>
     <row r="367">
@@ -7757,16 +7757,16 @@
         <v>0.66</v>
       </c>
       <c r="C367" t="n">
-        <v>0.0820453389304</v>
+        <v>0.08197569066074628</v>
       </c>
       <c r="D367" t="n">
-        <v>0.008984338843659999</v>
+        <v>0.008980743187925933</v>
       </c>
       <c r="E367" t="n">
-        <v>0.0642392395291</v>
+        <v>0.06421315168629604</v>
       </c>
       <c r="F367" t="n">
-        <v>0.09089801132899999</v>
+        <v>0.09086003421400868</v>
       </c>
     </row>
     <row r="368">
@@ -7777,16 +7777,16 @@
         <v>0.68</v>
       </c>
       <c r="C368" t="n">
-        <v>0.09609241961209999</v>
+        <v>0.09602217601664557</v>
       </c>
       <c r="D368" t="n">
-        <v>0.008722002867330001</v>
+        <v>0.008716305736207871</v>
       </c>
       <c r="E368" t="n">
-        <v>0.07879499097870001</v>
+        <v>0.07876366241030386</v>
       </c>
       <c r="F368" t="n">
-        <v>0.105090059217</v>
+        <v>0.105046785935782</v>
       </c>
     </row>
     <row r="369">
@@ -7797,16 +7797,16 @@
         <v>0.7</v>
       </c>
       <c r="C369" t="n">
-        <v>0.110291376766</v>
+        <v>0.1102144112264157</v>
       </c>
       <c r="D369" t="n">
-        <v>0.008452674819219999</v>
+        <v>0.008446137609959218</v>
       </c>
       <c r="E369" t="n">
-        <v>0.0934474283655</v>
+        <v>0.09340151417272313</v>
       </c>
       <c r="F369" t="n">
-        <v>0.119290173172</v>
+        <v>0.1192352728800747</v>
       </c>
     </row>
     <row r="370">
@@ -7817,16 +7817,16 @@
         <v>0.72</v>
       </c>
       <c r="C370" t="n">
-        <v>0.124646976596</v>
+        <v>0.1245710429693055</v>
       </c>
       <c r="D370" t="n">
-        <v>0.00816045275191</v>
+        <v>0.008155339994155351</v>
       </c>
       <c r="E370" t="n">
-        <v>0.108236490476</v>
+        <v>0.108180999628984</v>
       </c>
       <c r="F370" t="n">
-        <v>0.133493049912</v>
+        <v>0.1334233148074127</v>
       </c>
     </row>
     <row r="371">
@@ -7837,16 +7837,16 @@
         <v>0.74</v>
       </c>
       <c r="C371" t="n">
-        <v>0.139262576931</v>
+        <v>0.139179901397514</v>
       </c>
       <c r="D371" t="n">
-        <v>0.007880694003319999</v>
+        <v>0.007877386770174953</v>
       </c>
       <c r="E371" t="n">
-        <v>0.123141147812</v>
+        <v>0.1230768518287162</v>
       </c>
       <c r="F371" t="n">
-        <v>0.147742618964</v>
+        <v>0.1476565606249665</v>
       </c>
     </row>
     <row r="372">
@@ -7857,16 +7857,16 @@
         <v>0.76</v>
       </c>
       <c r="C372" t="n">
-        <v>0.154028838818</v>
+        <v>0.1539459287062455</v>
       </c>
       <c r="D372" t="n">
-        <v>0.00755479635179</v>
+        <v>0.007552811803224283</v>
       </c>
       <c r="E372" t="n">
-        <v>0.138399774207</v>
+        <v>0.1383369231215825</v>
       </c>
       <c r="F372" t="n">
-        <v>0.162204466079</v>
+        <v>0.1621230927911474</v>
       </c>
     </row>
     <row r="373">
@@ -7877,16 +7877,16 @@
         <v>0.78</v>
       </c>
       <c r="C373" t="n">
-        <v>0.168972387589</v>
+        <v>0.1688882594734958</v>
       </c>
       <c r="D373" t="n">
-        <v>0.00720088251811</v>
+        <v>0.00720090424052112</v>
       </c>
       <c r="E373" t="n">
-        <v>0.153994137311</v>
+        <v>0.1539322429644558</v>
       </c>
       <c r="F373" t="n">
-        <v>0.176777676343</v>
+        <v>0.176686601169326</v>
       </c>
     </row>
     <row r="374">
@@ -7897,16 +7897,16 @@
         <v>0.8</v>
       </c>
       <c r="C374" t="n">
-        <v>0.184195189109</v>
+        <v>0.1841153441749149</v>
       </c>
       <c r="D374" t="n">
-        <v>0.00674689206403</v>
+        <v>0.006743746636076929</v>
       </c>
       <c r="E374" t="n">
-        <v>0.170376091329</v>
+        <v>0.1703402280050286</v>
       </c>
       <c r="F374" t="n">
-        <v>0.191636563069</v>
+        <v>0.1915571240452731</v>
       </c>
     </row>
     <row r="375">
@@ -7917,16 +7917,16 @@
         <v>0.82</v>
       </c>
       <c r="C375" t="n">
-        <v>0.199796531086</v>
+        <v>0.1997277143835071</v>
       </c>
       <c r="D375" t="n">
-        <v>0.00607523620003</v>
+        <v>0.006065098914843297</v>
       </c>
       <c r="E375" t="n">
-        <v>0.18758708565</v>
+        <v>0.1875654887958733</v>
       </c>
       <c r="F375" t="n">
-        <v>0.206687525594</v>
+        <v>0.2065990049832607</v>
       </c>
     </row>
     <row r="376">
@@ -7937,16 +7937,16 @@
         <v>0.84</v>
       </c>
       <c r="C376" t="n">
-        <v>0.215641126004</v>
+        <v>0.2155677921574243</v>
       </c>
       <c r="D376" t="n">
-        <v>0.00535862517435</v>
+        <v>0.005355740163417685</v>
       </c>
       <c r="E376" t="n">
-        <v>0.205020567268</v>
+        <v>0.2049839028067542</v>
       </c>
       <c r="F376" t="n">
-        <v>0.221816540702</v>
+        <v>0.2217456779272258</v>
       </c>
     </row>
     <row r="377">
@@ -7957,16 +7957,16 @@
         <v>0.86</v>
       </c>
       <c r="C377" t="n">
-        <v>0.23165188853</v>
+        <v>0.2315740182941926</v>
       </c>
       <c r="D377" t="n">
-        <v>0.00470661259914</v>
+        <v>0.004705484496093719</v>
       </c>
       <c r="E377" t="n">
-        <v>0.222575526539</v>
+        <v>0.2225409409949357</v>
       </c>
       <c r="F377" t="n">
-        <v>0.237251057609</v>
+        <v>0.237182811982799</v>
       </c>
     </row>
     <row r="378">
@@ -7977,16 +7977,16 @@
         <v>0.88</v>
       </c>
       <c r="C378" t="n">
-        <v>0.247883898944</v>
+        <v>0.2478014891781872</v>
       </c>
       <c r="D378" t="n">
-        <v>0.0040935191717</v>
+        <v>0.004098737074902528</v>
       </c>
       <c r="E378" t="n">
-        <v>0.240320940765</v>
+        <v>0.2402754372208795</v>
       </c>
       <c r="F378" t="n">
-        <v>0.25291705965</v>
+        <v>0.2528406692428726</v>
       </c>
     </row>
     <row r="379">
@@ -7997,16 +7997,16 @@
         <v>0.9</v>
       </c>
       <c r="C379" t="n">
-        <v>0.264377515073</v>
+        <v>0.2643050125587346</v>
       </c>
       <c r="D379" t="n">
-        <v>0.00348312290897</v>
+        <v>0.003482723629078184</v>
       </c>
       <c r="E379" t="n">
-        <v>0.258269705695</v>
+        <v>0.2582218903122024</v>
       </c>
       <c r="F379" t="n">
-        <v>0.268728322547</v>
+        <v>0.2686640679081664</v>
       </c>
     </row>
     <row r="380">
@@ -8017,16 +8017,16 @@
         <v>0.92</v>
       </c>
       <c r="C380" t="n">
-        <v>0.28109792684</v>
+        <v>0.2810214270968917</v>
       </c>
       <c r="D380" t="n">
-        <v>0.00284540448202</v>
+        <v>0.002843581220607218</v>
       </c>
       <c r="E380" t="n">
-        <v>0.276372818553</v>
+        <v>0.2763176983866709</v>
       </c>
       <c r="F380" t="n">
-        <v>0.284751025478</v>
+        <v>0.2846813817929386</v>
       </c>
     </row>
     <row r="381">
@@ -8037,16 +8037,16 @@
         <v>0</v>
       </c>
       <c r="C381" t="n">
-        <v>-0.0469720878877</v>
+        <v>-0.04727241386273695</v>
       </c>
       <c r="D381" t="n">
-        <v>0.027433946294</v>
+        <v>0.02741003420912541</v>
       </c>
       <c r="E381" t="n">
-        <v>-0.0946426085482</v>
+        <v>-0.0948632262759741</v>
       </c>
       <c r="F381" t="n">
-        <v>0.00850198834373</v>
+        <v>0.008162613692112686</v>
       </c>
     </row>
     <row r="382">
@@ -8057,16 +8057,16 @@
         <v>0.02</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.0459598770586</v>
+        <v>-0.04625928403640467</v>
       </c>
       <c r="D382" t="n">
-        <v>0.0272916413934</v>
+        <v>0.02726755185757232</v>
       </c>
       <c r="E382" t="n">
-        <v>-0.0930329353413</v>
+        <v>-0.09325564797465269</v>
       </c>
       <c r="F382" t="n">
-        <v>0.009359843733970001</v>
+        <v>0.009018539242080514</v>
       </c>
     </row>
     <row r="383">
@@ -8077,16 +8077,16 @@
         <v>0.04</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.0448714012303</v>
+        <v>-0.04516906983281253</v>
       </c>
       <c r="D383" t="n">
-        <v>0.0271712274366</v>
+        <v>0.02714810434763959</v>
       </c>
       <c r="E383" t="n">
-        <v>-0.0914234401245</v>
+        <v>-0.09164827054875424</v>
       </c>
       <c r="F383" t="n">
-        <v>0.0102616088203</v>
+        <v>0.009922029133423216</v>
       </c>
     </row>
     <row r="384">
@@ -8097,16 +8097,16 @@
         <v>0.06</v>
       </c>
       <c r="C384" t="n">
-        <v>-0.0436839441384</v>
+        <v>-0.04398327136525131</v>
       </c>
       <c r="D384" t="n">
-        <v>0.0270930221807</v>
+        <v>0.02707038348538551</v>
       </c>
       <c r="E384" t="n">
-        <v>-0.0898141228464</v>
+        <v>-0.09004109393931525</v>
       </c>
       <c r="F384" t="n">
-        <v>0.0112857760314</v>
+        <v>0.01094586292735045</v>
       </c>
     </row>
     <row r="385">
@@ -8117,16 +8117,16 @@
         <v>0.08</v>
       </c>
       <c r="C385" t="n">
-        <v>-0.0424148933237</v>
+        <v>-0.04271093571898001</v>
       </c>
       <c r="D385" t="n">
-        <v>0.0269015289617</v>
+        <v>0.02687219752593947</v>
       </c>
       <c r="E385" t="n">
-        <v>-0.0875773456219</v>
+        <v>-0.08777556280664367</v>
       </c>
       <c r="F385" t="n">
-        <v>0.0123123041438</v>
+        <v>0.0119703876101438</v>
       </c>
     </row>
     <row r="386">
@@ -8137,16 +8137,16 @@
         <v>0.1</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.0408665007028</v>
+        <v>-0.041152097044617</v>
       </c>
       <c r="D386" t="n">
-        <v>0.0264611618257</v>
+        <v>0.02642175393702364</v>
       </c>
       <c r="E386" t="n">
-        <v>-0.0841505471963</v>
+        <v>-0.08430284540179755</v>
       </c>
       <c r="F386" t="n">
-        <v>0.013338719607</v>
+        <v>0.01299478515260244</v>
       </c>
     </row>
     <row r="387">
@@ -8157,16 +8157,16 @@
         <v>0.12</v>
       </c>
       <c r="C387" t="n">
-        <v>-0.0390642890265</v>
+        <v>-0.039347702142316</v>
       </c>
       <c r="D387" t="n">
-        <v>0.0258479889814</v>
+        <v>0.02580978031001233</v>
       </c>
       <c r="E387" t="n">
-        <v>-0.07994418897400001</v>
+        <v>-0.080095167894636</v>
       </c>
       <c r="F387" t="n">
-        <v>0.0144425216644</v>
+        <v>0.01410683760137843</v>
       </c>
     </row>
     <row r="388">
@@ -8177,16 +8177,16 @@
         <v>0.14</v>
       </c>
       <c r="C388" t="n">
-        <v>-0.0370552032888</v>
+        <v>-0.0373334352608186</v>
       </c>
       <c r="D388" t="n">
-        <v>0.0252437633996</v>
+        <v>0.02520717263875248</v>
       </c>
       <c r="E388" t="n">
-        <v>-0.0756193563093</v>
+        <v>-0.07576554869869767</v>
       </c>
       <c r="F388" t="n">
-        <v>0.0156309368021</v>
+        <v>0.0152965794087887</v>
       </c>
     </row>
     <row r="389">
@@ -8197,16 +8197,16 @@
         <v>0.16</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.0349200739909</v>
+        <v>-0.03519879853566517</v>
       </c>
       <c r="D389" t="n">
-        <v>0.0246560738085</v>
+        <v>0.02462017851234356</v>
       </c>
       <c r="E389" t="n">
-        <v>-0.07110155003430001</v>
+        <v>-0.071245756381491</v>
       </c>
       <c r="F389" t="n">
-        <v>0.0168987816868</v>
+        <v>0.01656226277192197</v>
       </c>
     </row>
     <row r="390">
@@ -8217,16 +8217,16 @@
         <v>0.18</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.0324875767021</v>
+        <v>-0.03275593807407819</v>
       </c>
       <c r="D390" t="n">
-        <v>0.0241202179731</v>
+        <v>0.02408814536325059</v>
       </c>
       <c r="E390" t="n">
-        <v>-0.0664372061909</v>
+        <v>-0.06658161687197151</v>
       </c>
       <c r="F390" t="n">
-        <v>0.0183769950111</v>
+        <v>0.01805057692991596</v>
       </c>
     </row>
     <row r="391">
@@ -8237,16 +8237,16 @@
         <v>0.2</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.0297076082844</v>
+        <v>-0.02996264180689714</v>
       </c>
       <c r="D391" t="n">
-        <v>0.0236605123609</v>
+        <v>0.0236354800633181</v>
       </c>
       <c r="E391" t="n">
-        <v>-0.0613071398829</v>
+        <v>-0.0614475328309787</v>
       </c>
       <c r="F391" t="n">
-        <v>0.0202086153397</v>
+        <v>0.01990261528872939</v>
       </c>
     </row>
     <row r="392">
@@ -8257,16 +8257,16 @@
         <v>0.22</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.0266190409491</v>
+        <v>-0.02687408248421672</v>
       </c>
       <c r="D392" t="n">
-        <v>0.0232763783613</v>
+        <v>0.02325206751039198</v>
       </c>
       <c r="E392" t="n">
-        <v>-0.0561220051074</v>
+        <v>-0.05626493237168972</v>
       </c>
       <c r="F392" t="n">
-        <v>0.0224819571371</v>
+        <v>0.02217333359137719</v>
       </c>
     </row>
     <row r="393">
@@ -8277,16 +8277,16 @@
         <v>0.24</v>
       </c>
       <c r="C393" t="n">
-        <v>-0.0234407826234</v>
+        <v>-0.02369140363391438</v>
       </c>
       <c r="D393" t="n">
-        <v>0.0229451494148</v>
+        <v>0.02292351673737054</v>
       </c>
       <c r="E393" t="n">
-        <v>-0.0509148466704</v>
+        <v>-0.05106006836803889</v>
       </c>
       <c r="F393" t="n">
-        <v>0.0248441774618</v>
+        <v>0.0245426401519282</v>
       </c>
     </row>
     <row r="394">
@@ -8297,16 +8297,16 @@
         <v>0.26</v>
       </c>
       <c r="C394" t="n">
-        <v>-0.0200105849553</v>
+        <v>-0.02025623422409994</v>
       </c>
       <c r="D394" t="n">
-        <v>0.0226550483771</v>
+        <v>0.02263440569907246</v>
       </c>
       <c r="E394" t="n">
-        <v>-0.0456981035957</v>
+        <v>-0.04584706201070432</v>
       </c>
       <c r="F394" t="n">
-        <v>0.0274232855279</v>
+        <v>0.02712079711746895</v>
       </c>
     </row>
     <row r="395">
@@ -8317,16 +8317,16 @@
         <v>0.28</v>
       </c>
       <c r="C395" t="n">
-        <v>-0.0163614613245</v>
+        <v>-0.01660212231444689</v>
       </c>
       <c r="D395" t="n">
-        <v>0.0223997882887</v>
+        <v>0.02238078967707033</v>
       </c>
       <c r="E395" t="n">
-        <v>-0.0403865374398</v>
+        <v>-0.04053414169015035</v>
       </c>
       <c r="F395" t="n">
-        <v>0.0300696453921</v>
+        <v>0.02976518625862212</v>
       </c>
     </row>
     <row r="396">
@@ -8337,16 +8337,16 @@
         <v>0.3</v>
       </c>
       <c r="C396" t="n">
-        <v>-0.0124242682892</v>
+        <v>-0.01266014423331487</v>
       </c>
       <c r="D396" t="n">
-        <v>0.0221320511321</v>
+        <v>0.02211124080693034</v>
       </c>
       <c r="E396" t="n">
-        <v>-0.0350022552333</v>
+        <v>-0.03515086397028533</v>
       </c>
       <c r="F396" t="n">
-        <v>0.032764875051</v>
+        <v>0.03245896124760606</v>
       </c>
     </row>
     <row r="397">
@@ -8357,16 +8357,16 @@
         <v>0.32</v>
       </c>
       <c r="C397" t="n">
-        <v>-0.008208758119309999</v>
+        <v>-0.008439770373592915</v>
       </c>
       <c r="D397" t="n">
-        <v>0.0217445397181</v>
+        <v>0.02172094046300718</v>
       </c>
       <c r="E397" t="n">
-        <v>-0.0297871425763</v>
+        <v>-0.02998676908295383</v>
       </c>
       <c r="F397" t="n">
-        <v>0.0354976514381</v>
+        <v>0.03519100321464563</v>
       </c>
     </row>
     <row r="398">
@@ -8377,16 +8377,16 @@
         <v>0.34</v>
       </c>
       <c r="C398" t="n">
-        <v>-0.00375186994393</v>
+        <v>-0.003983546260391968</v>
       </c>
       <c r="D398" t="n">
-        <v>0.0212531074921</v>
+        <v>0.02122884354394054</v>
       </c>
       <c r="E398" t="n">
-        <v>-0.0257353901799</v>
+        <v>-0.02592333624464338</v>
       </c>
       <c r="F398" t="n">
-        <v>0.0382723485687</v>
+        <v>0.03796291734775359</v>
       </c>
     </row>
     <row r="399">
@@ -8397,16 +8397,16 @@
         <v>0.36</v>
       </c>
       <c r="C399" t="n">
-        <v>0.000818364353282</v>
+        <v>0.0005874189504820216</v>
       </c>
       <c r="D399" t="n">
-        <v>0.0207553789755</v>
+        <v>0.02073373344765796</v>
       </c>
       <c r="E399" t="n">
-        <v>-0.021372273224</v>
+        <v>-0.02156155705346219</v>
       </c>
       <c r="F399" t="n">
-        <v>0.0411026987162</v>
+        <v>0.04079622333979405</v>
       </c>
     </row>
     <row r="400">
@@ -8417,16 +8417,16 @@
         <v>0.38</v>
       </c>
       <c r="C400" t="n">
-        <v>0.00558936855639</v>
+        <v>0.005359607179384352</v>
       </c>
       <c r="D400" t="n">
-        <v>0.0202652057654</v>
+        <v>0.02024309997517492</v>
       </c>
       <c r="E400" t="n">
-        <v>-0.016739095444</v>
+        <v>-0.01692601415433703</v>
       </c>
       <c r="F400" t="n">
-        <v>0.0440677517837</v>
+        <v>0.04376020407425596</v>
       </c>
     </row>
     <row r="401">
@@ -8437,16 +8437,16 @@
         <v>0.4</v>
       </c>
       <c r="C401" t="n">
-        <v>0.0110292967237</v>
+        <v>0.01083184451299344</v>
       </c>
       <c r="D401" t="n">
-        <v>0.0194935079882</v>
+        <v>0.01946256596872945</v>
       </c>
       <c r="E401" t="n">
-        <v>-0.0114555891378</v>
+        <v>-0.01161256381270093</v>
       </c>
       <c r="F401" t="n">
-        <v>0.0475724325589</v>
+        <v>0.0473126673779749</v>
       </c>
     </row>
     <row r="402">
@@ -8457,16 +8457,16 @@
         <v>0.42</v>
       </c>
       <c r="C402" t="n">
-        <v>0.0168386991624</v>
+        <v>0.01664304266295993</v>
       </c>
       <c r="D402" t="n">
-        <v>0.0187592297844</v>
+        <v>0.01872609991243342</v>
       </c>
       <c r="E402" t="n">
-        <v>-0.00578874910094</v>
+        <v>-0.005941380034305332</v>
       </c>
       <c r="F402" t="n">
-        <v>0.0515625025529</v>
+        <v>0.0513037741561515</v>
       </c>
     </row>
     <row r="403">
@@ -8477,16 +8477,16 @@
         <v>0.44</v>
       </c>
       <c r="C403" t="n">
-        <v>0.0229134211875</v>
+        <v>0.02272062914905355</v>
       </c>
       <c r="D403" t="n">
-        <v>0.0180493205619</v>
+        <v>0.01802236495930197</v>
       </c>
       <c r="E403" t="n">
-        <v>4.13262418828e-05</v>
+        <v>-0.0001151953366180791</v>
       </c>
       <c r="F403" t="n">
-        <v>0.0557413929537</v>
+        <v>0.05547955862332721</v>
       </c>
     </row>
     <row r="404">
@@ -8497,16 +8497,16 @@
         <v>0.46</v>
       </c>
       <c r="C404" t="n">
-        <v>0.0294323174119</v>
+        <v>0.02926610766579918</v>
       </c>
       <c r="D404" t="n">
-        <v>0.0172817914595</v>
+        <v>0.01724125812111421</v>
       </c>
       <c r="E404" t="n">
-        <v>0.00669395384902</v>
+        <v>0.006594619903720123</v>
       </c>
       <c r="F404" t="n">
-        <v>0.0600397161466</v>
+        <v>0.05978280107263689</v>
       </c>
     </row>
     <row r="405">
@@ -8517,16 +8517,16 @@
         <v>0.48</v>
       </c>
       <c r="C405" t="n">
-        <v>0.0363670765982</v>
+        <v>0.03621137721362509</v>
       </c>
       <c r="D405" t="n">
-        <v>0.0164851809594</v>
+        <v>0.01644760852765857</v>
       </c>
       <c r="E405" t="n">
-        <v>0.0138275627821</v>
+        <v>0.01375943251701717</v>
       </c>
       <c r="F405" t="n">
-        <v>0.064779289181</v>
+        <v>0.06454972655780011</v>
       </c>
     </row>
     <row r="406">
@@ -8537,16 +8537,16 @@
         <v>0.5</v>
       </c>
       <c r="C406" t="n">
-        <v>0.0437690036642</v>
+        <v>0.04361955770967327</v>
       </c>
       <c r="D406" t="n">
-        <v>0.0157122233336</v>
+        <v>0.01567749409610703</v>
       </c>
       <c r="E406" t="n">
-        <v>0.0218346464982</v>
+        <v>0.0217736645538773</v>
       </c>
       <c r="F406" t="n">
-        <v>0.0702412319781</v>
+        <v>0.07003172253837686</v>
       </c>
     </row>
     <row r="407">
@@ -8557,16 +8557,16 @@
         <v>0.52</v>
       </c>
       <c r="C407" t="n">
-        <v>0.0515757054614</v>
+        <v>0.05143544756877221</v>
       </c>
       <c r="D407" t="n">
-        <v>0.0150656067001</v>
+        <v>0.01503208509719237</v>
       </c>
       <c r="E407" t="n">
-        <v>0.0302453473034</v>
+        <v>0.03019678051189523</v>
       </c>
       <c r="F407" t="n">
-        <v>0.0765434444568</v>
+        <v>0.07635318131216984</v>
       </c>
     </row>
     <row r="408">
@@ -8577,16 +8577,16 @@
         <v>0.54</v>
       </c>
       <c r="C408" t="n">
-        <v>0.0597719238752</v>
+        <v>0.05963282607012647</v>
       </c>
       <c r="D408" t="n">
-        <v>0.0143263460734</v>
+        <v>0.0142906038960249</v>
       </c>
       <c r="E408" t="n">
-        <v>0.039211994373</v>
+        <v>0.03917112167721015</v>
       </c>
       <c r="F408" t="n">
-        <v>0.08321761444090001</v>
+        <v>0.08302343512275101</v>
       </c>
     </row>
     <row r="409">
@@ -8597,16 +8597,16 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="C409" t="n">
-        <v>0.06825111490080001</v>
+        <v>0.06811689125100022</v>
       </c>
       <c r="D409" t="n">
-        <v>0.0135048104304</v>
+        <v>0.0134714230983794</v>
       </c>
       <c r="E409" t="n">
-        <v>0.0484726954008</v>
+        <v>0.04842422521027157</v>
       </c>
       <c r="F409" t="n">
-        <v>0.0901702640644</v>
+        <v>0.08998413547432893</v>
       </c>
     </row>
     <row r="410">
@@ -8617,16 +8617,16 @@
         <v>0.58</v>
       </c>
       <c r="C410" t="n">
-        <v>0.0770314471821</v>
+        <v>0.07690683205366486</v>
       </c>
       <c r="D410" t="n">
-        <v>0.0127062306657</v>
+        <v>0.01268429888767162</v>
       </c>
       <c r="E410" t="n">
-        <v>0.05792874686</v>
+        <v>0.05787983484168713</v>
       </c>
       <c r="F410" t="n">
-        <v>0.097262506081</v>
+        <v>0.09708662009686364</v>
       </c>
     </row>
     <row r="411">
@@ -8637,16 +8637,16 @@
         <v>0.6</v>
       </c>
       <c r="C411" t="n">
-        <v>0.0862142968144</v>
+        <v>0.08609475999472904</v>
       </c>
       <c r="D411" t="n">
-        <v>0.0120936376754</v>
+        <v>0.01207286149375057</v>
       </c>
       <c r="E411" t="n">
-        <v>0.06760281996130001</v>
+        <v>0.06755322933990193</v>
       </c>
       <c r="F411" t="n">
-        <v>0.104948613557</v>
+        <v>0.1047767180563159</v>
       </c>
     </row>
     <row r="412">
@@ -8657,16 +8657,16 @@
         <v>0.62</v>
       </c>
       <c r="C412" t="n">
-        <v>0.0956881588907</v>
+        <v>0.09556819053155996</v>
       </c>
       <c r="D412" t="n">
-        <v>0.0115445535329</v>
+        <v>0.01152530283159235</v>
       </c>
       <c r="E412" t="n">
-        <v>0.0775317755738</v>
+        <v>0.07749408739122465</v>
       </c>
       <c r="F412" t="n">
-        <v>0.112970666654</v>
+        <v>0.112805495146107</v>
       </c>
     </row>
     <row r="413">
@@ -8677,16 +8677,16 @@
         <v>0.64</v>
       </c>
       <c r="C413" t="n">
-        <v>0.105470818707</v>
+        <v>0.1053577181277185</v>
       </c>
       <c r="D413" t="n">
-        <v>0.0110288160724</v>
+        <v>0.011014471921829</v>
       </c>
       <c r="E413" t="n">
-        <v>0.0879559634125</v>
+        <v>0.08792190942078992</v>
       </c>
       <c r="F413" t="n">
-        <v>0.121168150622</v>
+        <v>0.1210025439872258</v>
       </c>
     </row>
     <row r="414">
@@ -8697,16 +8697,16 @@
         <v>0.66</v>
       </c>
       <c r="C414" t="n">
-        <v>0.115597387659</v>
+        <v>0.1154867087047262</v>
       </c>
       <c r="D414" t="n">
-        <v>0.0105655639931</v>
+        <v>0.01055343349662943</v>
       </c>
       <c r="E414" t="n">
-        <v>0.09906427523609999</v>
+        <v>0.09904931699406117</v>
       </c>
       <c r="F414" t="n">
-        <v>0.130167245234</v>
+        <v>0.1300270376986923</v>
       </c>
     </row>
     <row r="415">
@@ -8717,16 +8717,16 @@
         <v>0.68</v>
       </c>
       <c r="C415" t="n">
-        <v>0.126059691546</v>
+        <v>0.125956596101378</v>
       </c>
       <c r="D415" t="n">
-        <v>0.0101082315902</v>
+        <v>0.01009973436932842</v>
       </c>
       <c r="E415" t="n">
-        <v>0.110626022788</v>
+        <v>0.1106109623757368</v>
       </c>
       <c r="F415" t="n">
-        <v>0.13964662556</v>
+        <v>0.1395256984531752</v>
       </c>
     </row>
     <row r="416">
@@ -8737,16 +8737,16 @@
         <v>0.7</v>
       </c>
       <c r="C416" t="n">
-        <v>0.136898622732</v>
+        <v>0.1367981297758299</v>
       </c>
       <c r="D416" t="n">
-        <v>0.00965558759558</v>
+        <v>0.009645838592277297</v>
       </c>
       <c r="E416" t="n">
-        <v>0.122419644269</v>
+        <v>0.1223973587018374</v>
       </c>
       <c r="F416" t="n">
-        <v>0.149606062005</v>
+        <v>0.1494794706583633</v>
       </c>
     </row>
     <row r="417">
@@ -8757,16 +8757,16 @@
         <v>0.72</v>
       </c>
       <c r="C417" t="n">
-        <v>0.148092640922</v>
+        <v>0.1479881332523988</v>
       </c>
       <c r="D417" t="n">
-        <v>0.00915857995723</v>
+        <v>0.009151092663699793</v>
       </c>
       <c r="E417" t="n">
-        <v>0.134525694106</v>
+        <v>0.1345009074622556</v>
       </c>
       <c r="F417" t="n">
-        <v>0.159769533696</v>
+        <v>0.1596453666688662</v>
       </c>
     </row>
     <row r="418">
@@ -8777,16 +8777,16 @@
         <v>0.74</v>
       </c>
       <c r="C418" t="n">
-        <v>0.159637251096</v>
+        <v>0.1595424739553505</v>
       </c>
       <c r="D418" t="n">
-        <v>0.00863336575749</v>
+        <v>0.008624296386961432</v>
       </c>
       <c r="E418" t="n">
-        <v>0.146895236051</v>
+        <v>0.1468666789402597</v>
       </c>
       <c r="F418" t="n">
-        <v>0.170095276492</v>
+        <v>0.1699666455042452</v>
       </c>
     </row>
     <row r="419">
@@ -8797,16 +8797,16 @@
         <v>0.76</v>
       </c>
       <c r="C419" t="n">
-        <v>0.171589671855</v>
+        <v>0.1714954828271158</v>
       </c>
       <c r="D419" t="n">
-        <v>0.008231940698520001</v>
+        <v>0.008229415561628402</v>
       </c>
       <c r="E419" t="n">
-        <v>0.159248948957</v>
+        <v>0.1591351340542007</v>
       </c>
       <c r="F419" t="n">
-        <v>0.180912857896</v>
+        <v>0.1807997963292367</v>
       </c>
     </row>
     <row r="420">
@@ -8817,16 +8817,16 @@
         <v>0.78</v>
       </c>
       <c r="C420" t="n">
-        <v>0.183911369824</v>
+        <v>0.1838209058342832</v>
       </c>
       <c r="D420" t="n">
-        <v>0.007948335878240001</v>
+        <v>0.007944140188708305</v>
       </c>
       <c r="E420" t="n">
-        <v>0.171715876374</v>
+        <v>0.1716167164200613</v>
       </c>
       <c r="F420" t="n">
-        <v>0.192212097082</v>
+        <v>0.1920917047271091</v>
       </c>
     </row>
     <row r="421">
@@ -8837,16 +8837,16 @@
         <v>0.8</v>
       </c>
       <c r="C421" t="n">
-        <v>0.196732046387</v>
+        <v>0.1966573490362766</v>
       </c>
       <c r="D421" t="n">
-        <v>0.0075103632465</v>
+        <v>0.007495530055933505</v>
       </c>
       <c r="E421" t="n">
-        <v>0.184885202875</v>
+        <v>0.1848232550685651</v>
       </c>
       <c r="F421" t="n">
-        <v>0.204250848607</v>
+        <v>0.2041731201571322</v>
       </c>
     </row>
     <row r="422">
@@ -8857,16 +8857,16 @@
         <v>0.82</v>
       </c>
       <c r="C422" t="n">
-        <v>0.210136587708</v>
+        <v>0.2100670153433378</v>
       </c>
       <c r="D422" t="n">
-        <v>0.0070542244333</v>
+        <v>0.007046083001913987</v>
       </c>
       <c r="E422" t="n">
-        <v>0.198982303358</v>
+        <v>0.198919168834454</v>
       </c>
       <c r="F422" t="n">
-        <v>0.217375098178</v>
+        <v>0.217289826346919</v>
       </c>
     </row>
     <row r="423">
@@ -8877,16 +8877,16 @@
         <v>0.84</v>
       </c>
       <c r="C423" t="n">
-        <v>0.224066552261</v>
+        <v>0.2239930989397102</v>
       </c>
       <c r="D423" t="n">
-        <v>0.00665382394939</v>
+        <v>0.006644814541069582</v>
       </c>
       <c r="E423" t="n">
-        <v>0.213406582324</v>
+        <v>0.2133345247143961</v>
       </c>
       <c r="F423" t="n">
-        <v>0.230814683258</v>
+        <v>0.2307252324485409</v>
       </c>
     </row>
     <row r="424">
@@ -8897,16 +8897,16 @@
         <v>0.86</v>
       </c>
       <c r="C424" t="n">
-        <v>0.238292891596</v>
+        <v>0.2382149461870356</v>
       </c>
       <c r="D424" t="n">
-        <v>0.00616908024006</v>
+        <v>0.006162562499930838</v>
       </c>
       <c r="E424" t="n">
-        <v>0.228199914026</v>
+        <v>0.2281240992961528</v>
       </c>
       <c r="F424" t="n">
-        <v>0.244424618002</v>
+        <v>0.2443457813346575</v>
       </c>
     </row>
     <row r="425">
@@ -8917,16 +8917,16 @@
         <v>0.88</v>
       </c>
       <c r="C425" t="n">
-        <v>0.252859944628</v>
+        <v>0.2527759419337618</v>
       </c>
       <c r="D425" t="n">
-        <v>0.00567657398853</v>
+        <v>0.00566900129879157</v>
       </c>
       <c r="E425" t="n">
-        <v>0.243136128638</v>
+        <v>0.2430460958801044</v>
       </c>
       <c r="F425" t="n">
-        <v>0.25838744216</v>
+        <v>0.2583003836111963</v>
       </c>
     </row>
     <row r="426">
@@ -8937,16 +8937,16 @@
         <v>0.9</v>
       </c>
       <c r="C426" t="n">
-        <v>0.267769847657</v>
+        <v>0.2676817313687792</v>
       </c>
       <c r="D426" t="n">
-        <v>0.00505499168646</v>
+        <v>0.005047064400305192</v>
       </c>
       <c r="E426" t="n">
-        <v>0.258234922551</v>
+        <v>0.2581378145403388</v>
       </c>
       <c r="F426" t="n">
-        <v>0.272492909058</v>
+        <v>0.27240238985791</v>
       </c>
     </row>
     <row r="427">
@@ -8957,16 +8957,16 @@
         <v>0.92</v>
       </c>
       <c r="C427" t="n">
-        <v>0.283297466182</v>
+        <v>0.2832087481757082</v>
       </c>
       <c r="D427" t="n">
-        <v>0.00400764946024</v>
+        <v>0.003991814729413413</v>
       </c>
       <c r="E427" t="n">
-        <v>0.27562353447</v>
+        <v>0.2755745886659549</v>
       </c>
       <c r="F427" t="n">
-        <v>0.287380956548</v>
+        <v>0.2872818803699522</v>
       </c>
     </row>
     <row r="428">
@@ -8977,16 +8977,16 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="C428" t="n">
-        <v>0.29927610376</v>
+        <v>0.2991832877676931</v>
       </c>
       <c r="D428" t="n">
-        <v>0.00297994589185</v>
+        <v>0.002965664321758257</v>
       </c>
       <c r="E428" t="n">
-        <v>0.293532506992</v>
+        <v>0.2934655789470844</v>
       </c>
       <c r="F428" t="n">
-        <v>0.302566379265</v>
+        <v>0.3024579997301382</v>
       </c>
     </row>
   </sheetData>
